--- a/build/Sample.xlsx
+++ b/build/Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/Documents/Repos/golang/generateTables/build/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F3558D-1E8F-D548-8B7B-BF1380D41D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF04866C-BD97-CF44-8670-3C88AE5012D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-440" yWindow="600" windowWidth="26400" windowHeight="22340" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
+    <workbookView xWindow="920" yWindow="600" windowWidth="26400" windowHeight="22340" activeTab="1" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="#SAMPLE" sheetId="14" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="125">
   <si>
     <t>False</t>
     <phoneticPr fontId="1"/>
@@ -404,13 +404,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>数字型</t>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">スウジ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>通常タイプ</t>
     <rPh sb="0" eb="2">
       <t xml:space="preserve">ツウジョウ </t>
@@ -574,11 +567,132 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>test</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>test2</t>
+    <t>集計タイプのフィールド</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">シュウケイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計タイプのフィールド</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ケイサン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Individually.Average</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Individually.Count</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Individually.Total</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Individually.List</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Together.Average</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Together.Count</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Together.Total</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Together.List</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.Hoge</t>
+  </si>
+  <si>
+    <t>1.Hoge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.Fuga</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S8</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1188,7 +1302,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L1" s="22"/>
       <c r="M1" s="8"/>
@@ -1258,7 +1372,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="23"/>
       <c r="M2" s="4"/>
@@ -1326,7 +1440,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L3"/>
       <c r="M3" s="13"/>
@@ -1529,7 +1643,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
@@ -1609,7 +1723,7 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
@@ -1654,12 +1768,12 @@
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="19"/>
       <c r="AR9" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="19"/>
@@ -1691,7 +1805,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="5"/>
@@ -1781,7 +1895,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
@@ -1844,7 +1958,7 @@
       <c r="AY11" s="4"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
@@ -1865,7 +1979,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="5"/>
@@ -1947,7 +2061,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
@@ -1996,7 +2110,7 @@
       <c r="AY13" s="4"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
@@ -2017,7 +2131,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="5"/>
@@ -2085,7 +2199,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="5"/>
@@ -2153,7 +2267,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="5"/>
@@ -2184,12 +2298,12 @@
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
       <c r="AL16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
@@ -2206,7 +2320,7 @@
       <c r="AY16" s="4"/>
       <c r="AZ16" s="5"/>
       <c r="BA16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB16" s="4"/>
       <c r="BC16" s="4"/>
@@ -2227,7 +2341,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
@@ -2258,12 +2372,12 @@
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
       <c r="AL17" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
@@ -2280,7 +2394,7 @@
       <c r="AY17" s="4"/>
       <c r="AZ17" s="5"/>
       <c r="BA17" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
@@ -2301,7 +2415,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="5"/>
@@ -2350,7 +2464,7 @@
       <c r="AY18" s="4"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
@@ -2371,7 +2485,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
@@ -2420,7 +2534,7 @@
       <c r="AY19" s="4"/>
       <c r="AZ19" s="5"/>
       <c r="BA19" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB19" s="4"/>
       <c r="BC19" s="4"/>
@@ -2441,7 +2555,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
@@ -2490,7 +2604,7 @@
       <c r="AY20" s="4"/>
       <c r="AZ20" s="5"/>
       <c r="BA20" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
@@ -2511,7 +2625,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="5"/>
@@ -2560,7 +2674,7 @@
       <c r="AY21" s="4"/>
       <c r="AZ21" s="5"/>
       <c r="BA21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
@@ -2575,25 +2689,29 @@
         <v>39</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
       <c r="K22" s="4" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="3"/>
       <c r="O22" s="4"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5"/>
       <c r="T22" s="3"/>
@@ -2630,7 +2748,7 @@
       <c r="AY22" s="4"/>
       <c r="AZ22" s="5"/>
       <c r="BA22" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
@@ -2645,25 +2763,29 @@
         <v>40</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="5"/>
       <c r="K23" s="4" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="3"/>
       <c r="O23" s="4"/>
       <c r="P23" s="5"/>
-      <c r="Q23" s="3"/>
+      <c r="Q23" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5"/>
       <c r="T23" s="3"/>
@@ -2700,7 +2822,7 @@
       <c r="AY23" s="4"/>
       <c r="AZ23" s="5"/>
       <c r="BA23" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
@@ -2715,25 +2837,29 @@
         <v>41</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="5"/>
       <c r="K24" s="4" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="3"/>
       <c r="O24" s="4"/>
       <c r="P24" s="5"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5"/>
       <c r="T24" s="3"/>
@@ -2770,7 +2896,7 @@
       <c r="AY24" s="4"/>
       <c r="AZ24" s="5"/>
       <c r="BA24" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
@@ -2781,23 +2907,33 @@
       <c r="BH24" s="5"/>
     </row>
     <row r="25" spans="1:60" ht="14" customHeight="1">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="5"/>
-      <c r="K25" s="4"/>
+      <c r="K25" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="3"/>
       <c r="O25" s="4"/>
       <c r="P25" s="5"/>
-      <c r="Q25" s="3"/>
+      <c r="Q25" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5"/>
       <c r="T25" s="3"/>
@@ -2833,7 +2969,9 @@
       <c r="AX25" s="3"/>
       <c r="AY25" s="4"/>
       <c r="AZ25" s="5"/>
-      <c r="BA25" s="4"/>
+      <c r="BA25" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
@@ -2843,23 +2981,33 @@
       <c r="BH25" s="5"/>
     </row>
     <row r="26" spans="1:60" ht="14" customHeight="1">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="5"/>
-      <c r="K26" s="4"/>
+      <c r="K26" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="3"/>
       <c r="O26" s="4"/>
       <c r="P26" s="5"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5"/>
       <c r="T26" s="3"/>
@@ -2895,7 +3043,9 @@
       <c r="AX26" s="3"/>
       <c r="AY26" s="4"/>
       <c r="AZ26" s="5"/>
-      <c r="BA26" s="4"/>
+      <c r="BA26" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
       <c r="BD26" s="4"/>
@@ -2905,23 +3055,33 @@
       <c r="BH26" s="5"/>
     </row>
     <row r="27" spans="1:60" ht="14" customHeight="1">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
-      <c r="K27" s="4"/>
+      <c r="K27" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="3"/>
       <c r="O27" s="4"/>
       <c r="P27" s="5"/>
-      <c r="Q27" s="3"/>
+      <c r="Q27" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5"/>
       <c r="T27" s="3"/>
@@ -2945,11 +3105,11 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
-      <c r="AO27" s="3"/>
-      <c r="AP27" s="4"/>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="21"/>
       <c r="AQ27" s="5"/>
-      <c r="AR27" s="3"/>
-      <c r="AS27" s="4"/>
+      <c r="AR27" s="25"/>
+      <c r="AS27" s="21"/>
       <c r="AT27" s="5"/>
       <c r="AU27" s="4"/>
       <c r="AV27" s="4"/>
@@ -2957,7 +3117,9 @@
       <c r="AX27" s="3"/>
       <c r="AY27" s="4"/>
       <c r="AZ27" s="5"/>
-      <c r="BA27" s="4"/>
+      <c r="BA27" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4"/>
@@ -2967,23 +3129,33 @@
       <c r="BH27" s="5"/>
     </row>
     <row r="28" spans="1:60" ht="14" customHeight="1">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="3"/>
+      <c r="H28" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="5"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="3"/>
       <c r="O28" s="4"/>
       <c r="P28" s="5"/>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5"/>
       <c r="T28" s="3"/>
@@ -3019,7 +3191,9 @@
       <c r="AX28" s="3"/>
       <c r="AY28" s="4"/>
       <c r="AZ28" s="5"/>
-      <c r="BA28" s="4"/>
+      <c r="BA28" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
       <c r="BD28" s="4"/>
@@ -3029,23 +3203,33 @@
       <c r="BH28" s="5"/>
     </row>
     <row r="29" spans="1:60" ht="14" customHeight="1">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="3"/>
+      <c r="H29" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5"/>
-      <c r="K29" s="4"/>
+      <c r="K29" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="3"/>
       <c r="O29" s="4"/>
       <c r="P29" s="5"/>
-      <c r="Q29" s="3"/>
+      <c r="Q29" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5"/>
       <c r="T29" s="3"/>
@@ -3081,7 +3265,9 @@
       <c r="AX29" s="3"/>
       <c r="AY29" s="4"/>
       <c r="AZ29" s="5"/>
-      <c r="BA29" s="4"/>
+      <c r="BA29" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
       <c r="BD29" s="4"/>
@@ -3749,7 +3935,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L1" s="22"/>
       <c r="M1" s="8"/>
@@ -3819,7 +4005,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="23"/>
       <c r="M2" s="4"/>
@@ -3887,7 +4073,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L3"/>
       <c r="M3" s="13"/>
@@ -4090,7 +4276,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
@@ -4170,7 +4356,7 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
@@ -4215,12 +4401,12 @@
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="19"/>
@@ -4252,7 +4438,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="5"/>
@@ -4338,7 +4524,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
@@ -4397,7 +4583,7 @@
       <c r="AY11" s="4"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
@@ -4418,7 +4604,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="5"/>
@@ -4494,7 +4680,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
@@ -4545,7 +4731,7 @@
       <c r="AY13" s="4"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
@@ -4566,7 +4752,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="5"/>
@@ -4634,7 +4820,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="5"/>
@@ -4696,15 +4882,13 @@
         <v>34</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="3" t="s">
-        <v>100</v>
-      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="5"/>
@@ -4717,7 +4901,7 @@
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="5"/>
@@ -4755,7 +4939,7 @@
       <c r="AY16" s="4"/>
       <c r="AZ16" s="5"/>
       <c r="BA16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB16" s="4"/>
       <c r="BC16" s="4"/>
@@ -4770,15 +4954,13 @@
         <v>35</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
@@ -4791,7 +4973,7 @@
       <c r="O17" s="4"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="5"/>
@@ -4829,7 +5011,7 @@
       <c r="AY17" s="4"/>
       <c r="AZ17" s="5"/>
       <c r="BA17" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
@@ -4850,7 +5032,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="5"/>
@@ -4899,7 +5081,7 @@
       <c r="AY18" s="4"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
@@ -4920,7 +5102,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
@@ -4969,7 +5151,7 @@
       <c r="AY19" s="4"/>
       <c r="AZ19" s="5"/>
       <c r="BA19" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB19" s="4"/>
       <c r="BC19" s="4"/>
@@ -4990,7 +5172,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
@@ -5039,7 +5221,7 @@
       <c r="AY20" s="4"/>
       <c r="AZ20" s="5"/>
       <c r="BA20" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
@@ -5060,7 +5242,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="5"/>
@@ -5109,7 +5291,7 @@
       <c r="AY21" s="4"/>
       <c r="AZ21" s="5"/>
       <c r="BA21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
@@ -5124,25 +5306,29 @@
         <v>39</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
       <c r="K22" s="4" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="3"/>
       <c r="O22" s="4"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5"/>
       <c r="T22" s="3"/>
@@ -5168,7 +5354,7 @@
       <c r="AN22" s="4"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="4"/>
-      <c r="AQ22" s="4"/>
+      <c r="AQ22" s="5"/>
       <c r="AR22" s="3"/>
       <c r="AS22" s="4"/>
       <c r="AT22" s="5"/>
@@ -5179,7 +5365,7 @@
       <c r="AY22" s="4"/>
       <c r="AZ22" s="5"/>
       <c r="BA22" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
@@ -5194,25 +5380,29 @@
         <v>40</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="5"/>
       <c r="K23" s="4" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="3"/>
       <c r="O23" s="4"/>
       <c r="P23" s="5"/>
-      <c r="Q23" s="3"/>
+      <c r="Q23" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5"/>
       <c r="T23" s="3"/>
@@ -5236,9 +5426,9 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
-      <c r="AO23" s="3"/>
-      <c r="AP23" s="4"/>
-      <c r="AQ23" s="4"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="21"/>
+      <c r="AQ23" s="5"/>
       <c r="AR23" s="25"/>
       <c r="AS23" s="21"/>
       <c r="AT23" s="5"/>
@@ -5249,7 +5439,7 @@
       <c r="AY23" s="4"/>
       <c r="AZ23" s="5"/>
       <c r="BA23" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
@@ -5264,25 +5454,29 @@
         <v>41</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="5"/>
       <c r="K24" s="4" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="3"/>
       <c r="O24" s="4"/>
       <c r="P24" s="5"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5"/>
       <c r="T24" s="3"/>
@@ -5308,7 +5502,7 @@
       <c r="AN24" s="4"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="4"/>
-      <c r="AQ24" s="4"/>
+      <c r="AQ24" s="5"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="4"/>
       <c r="AT24" s="5"/>
@@ -5319,7 +5513,7 @@
       <c r="AY24" s="4"/>
       <c r="AZ24" s="5"/>
       <c r="BA24" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
@@ -5330,23 +5524,33 @@
       <c r="BH24" s="5"/>
     </row>
     <row r="25" spans="1:60" ht="14" customHeight="1">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="5"/>
-      <c r="K25" s="4"/>
+      <c r="K25" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="3"/>
       <c r="O25" s="4"/>
       <c r="P25" s="5"/>
-      <c r="Q25" s="3"/>
+      <c r="Q25" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5"/>
       <c r="T25" s="3"/>
@@ -5372,7 +5576,7 @@
       <c r="AN25" s="4"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="4"/>
-      <c r="AQ25" s="4"/>
+      <c r="AQ25" s="5"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="4"/>
       <c r="AT25" s="5"/>
@@ -5382,7 +5586,9 @@
       <c r="AX25" s="3"/>
       <c r="AY25" s="4"/>
       <c r="AZ25" s="5"/>
-      <c r="BA25" s="4"/>
+      <c r="BA25" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
       <c r="BD25" s="4"/>
@@ -5392,23 +5598,33 @@
       <c r="BH25" s="5"/>
     </row>
     <row r="26" spans="1:60" ht="14" customHeight="1">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="5"/>
-      <c r="K26" s="4"/>
+      <c r="K26" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="3"/>
       <c r="O26" s="4"/>
       <c r="P26" s="5"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5"/>
       <c r="T26" s="3"/>
@@ -5434,7 +5650,7 @@
       <c r="AN26" s="4"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="4"/>
-      <c r="AQ26" s="4"/>
+      <c r="AQ26" s="5"/>
       <c r="AR26" s="3"/>
       <c r="AS26" s="4"/>
       <c r="AT26" s="5"/>
@@ -5444,7 +5660,9 @@
       <c r="AX26" s="3"/>
       <c r="AY26" s="4"/>
       <c r="AZ26" s="5"/>
-      <c r="BA26" s="4"/>
+      <c r="BA26" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
       <c r="BD26" s="4"/>
@@ -5454,23 +5672,33 @@
       <c r="BH26" s="5"/>
     </row>
     <row r="27" spans="1:60" ht="14" customHeight="1">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
-      <c r="K27" s="4"/>
+      <c r="K27" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="3"/>
       <c r="O27" s="4"/>
       <c r="P27" s="5"/>
-      <c r="Q27" s="3"/>
+      <c r="Q27" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5"/>
       <c r="T27" s="3"/>
@@ -5494,11 +5722,11 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
-      <c r="AO27" s="3"/>
-      <c r="AP27" s="4"/>
-      <c r="AQ27" s="4"/>
-      <c r="AR27" s="3"/>
-      <c r="AS27" s="4"/>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="21"/>
+      <c r="AQ27" s="5"/>
+      <c r="AR27" s="25"/>
+      <c r="AS27" s="21"/>
       <c r="AT27" s="5"/>
       <c r="AU27" s="4"/>
       <c r="AV27" s="4"/>
@@ -5506,7 +5734,9 @@
       <c r="AX27" s="3"/>
       <c r="AY27" s="4"/>
       <c r="AZ27" s="5"/>
-      <c r="BA27" s="4"/>
+      <c r="BA27" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
       <c r="BD27" s="4"/>
@@ -5516,23 +5746,33 @@
       <c r="BH27" s="5"/>
     </row>
     <row r="28" spans="1:60" ht="14" customHeight="1">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="3"/>
+      <c r="H28" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="5"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="3"/>
       <c r="O28" s="4"/>
       <c r="P28" s="5"/>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5"/>
       <c r="T28" s="3"/>
@@ -5558,7 +5798,7 @@
       <c r="AN28" s="4"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="4"/>
-      <c r="AQ28" s="4"/>
+      <c r="AQ28" s="5"/>
       <c r="AR28" s="3"/>
       <c r="AS28" s="4"/>
       <c r="AT28" s="5"/>
@@ -5568,7 +5808,9 @@
       <c r="AX28" s="3"/>
       <c r="AY28" s="4"/>
       <c r="AZ28" s="5"/>
-      <c r="BA28" s="4"/>
+      <c r="BA28" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
       <c r="BD28" s="4"/>
@@ -5578,23 +5820,33 @@
       <c r="BH28" s="5"/>
     </row>
     <row r="29" spans="1:60" ht="14" customHeight="1">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="3"/>
+      <c r="H29" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5"/>
-      <c r="K29" s="4"/>
+      <c r="K29" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="3"/>
       <c r="O29" s="4"/>
       <c r="P29" s="5"/>
-      <c r="Q29" s="3"/>
+      <c r="Q29" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5"/>
       <c r="T29" s="3"/>
@@ -5620,7 +5872,7 @@
       <c r="AN29" s="4"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="4"/>
-      <c r="AQ29" s="4"/>
+      <c r="AQ29" s="5"/>
       <c r="AR29" s="3"/>
       <c r="AS29" s="4"/>
       <c r="AT29" s="5"/>
@@ -5630,7 +5882,9 @@
       <c r="AX29" s="3"/>
       <c r="AY29" s="4"/>
       <c r="AZ29" s="5"/>
-      <c r="BA29" s="4"/>
+      <c r="BA29" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
       <c r="BD29" s="4"/>
@@ -6298,7 +6552,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L1" s="22"/>
       <c r="M1" s="8"/>
@@ -6368,7 +6622,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="23"/>
       <c r="M2" s="4"/>
@@ -6639,7 +6893,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
@@ -6719,7 +6973,7 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
@@ -6764,12 +7018,12 @@
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="19"/>
@@ -6801,7 +7055,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="5"/>
@@ -6838,7 +7092,7 @@
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5"/>
@@ -6881,7 +7135,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
@@ -6959,7 +7213,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="5"/>
@@ -6996,7 +7250,7 @@
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
@@ -7039,7 +7293,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
@@ -7074,7 +7328,7 @@
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5"/>
@@ -7117,7 +7371,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="5"/>
@@ -7199,7 +7453,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="5"/>
@@ -7281,7 +7535,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="5"/>
@@ -7355,7 +7609,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
@@ -7437,7 +7691,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="5"/>
@@ -7502,7 +7756,7 @@
     </row>
     <row r="19" spans="1:60" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -7511,7 +7765,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
@@ -7570,7 +7824,7 @@
     </row>
     <row r="20" spans="1:60" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -7579,7 +7833,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
@@ -7638,7 +7892,7 @@
     </row>
     <row r="21" spans="1:60" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -7647,7 +7901,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="5"/>
@@ -7706,7 +7960,7 @@
     </row>
     <row r="22" spans="1:60" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
@@ -7715,7 +7969,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
@@ -7774,7 +8028,7 @@
     </row>
     <row r="23" spans="1:60" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
@@ -7783,7 +8037,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="5"/>
@@ -7842,7 +8096,7 @@
     </row>
     <row r="24" spans="1:60" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="3"/>
@@ -7851,7 +8105,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="5"/>

--- a/build/Sample.xlsx
+++ b/build/Sample.xlsx
@@ -8,18 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/Documents/Repos/golang/generateTables/build/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF04866C-BD97-CF44-8670-3C88AE5012D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D9946F-E269-6F45-9043-1207EEA65EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="600" windowWidth="26400" windowHeight="22340" activeTab="1" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
+    <workbookView xWindow="140" yWindow="600" windowWidth="27880" windowHeight="17400" activeTab="1" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="#SAMPLE" sheetId="14" r:id="rId1"/>
     <sheet name="SAMPLE" sheetId="12" r:id="rId2"/>
-    <sheet name="顧客マスタ" sheetId="13" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">顧客マスタ!$A:$BH</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="103">
   <si>
     <t>False</t>
     <phoneticPr fontId="1"/>
@@ -208,10 +204,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Fuga</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>値</t>
     <rPh sb="0" eb="1">
       <t xml:space="preserve">アタイ </t>
@@ -313,64 +305,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Get( UUID )</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>顧客マスタ</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">コキャク </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>z_作成TS</t>
-  </si>
-  <si>
-    <t>z_作成者</t>
-  </si>
-  <si>
-    <t>z_修正TS</t>
-  </si>
-  <si>
-    <t>z_修正者</t>
-  </si>
-  <si>
-    <t>z_削除フラグ</t>
-  </si>
-  <si>
-    <t>z_01</t>
-  </si>
-  <si>
-    <t>__PK_ID</t>
-  </si>
-  <si>
-    <t>//----------</t>
-  </si>
-  <si>
-    <t>数字のみ</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>固定値</t>
-  </si>
-  <si>
-    <t>Always 1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0: False 1: True</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>日付のみ</t>
-  </si>
-  <si>
-    <t>OnWindowTransaction</t>
-  </si>
-  <si>
     <t>数字型</t>
     <rPh sb="0" eb="2">
       <t xml:space="preserve">スウジ </t>
@@ -439,37 +373,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作成TS</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">サクセイ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>修正TS</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">シュウセイ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>修正者</t>
-    <rPh sb="0" eb="3">
-      <t xml:space="preserve">シュウセイシャ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>値変更</t>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">アタイ </t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t xml:space="preserve">ヘンコウ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>フィールド名自動</t>
     <rPh sb="6" eb="8">
       <t xml:space="preserve">ジドウ </t>
@@ -490,24 +393,6 @@
   <si>
     <t>テーブル</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>SAMPLE</t>
@@ -653,17 +538,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1.Hoge</t>
-  </si>
-  <si>
-    <t>1.Hoge</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2.Fuga</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>S1</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -693,6 +567,48 @@
   </si>
   <si>
     <t>S8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値変更(True)</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">アタイ </t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">ヘンコウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hoge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fuga</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>c_hoge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.hoge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.fuga</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -700,7 +616,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -727,13 +643,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -884,7 +793,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -956,9 +865,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1280,7 +1186,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -1302,7 +1208,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="7" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="L1" s="22"/>
       <c r="M1" s="8"/>
@@ -1372,7 +1278,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="L2" s="23"/>
       <c r="M2" s="4"/>
@@ -1440,7 +1346,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="12" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="L3"/>
       <c r="M3" s="13"/>
@@ -1643,7 +1549,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
@@ -1718,17 +1624,17 @@
       <c r="I9" s="20"/>
       <c r="J9" s="19"/>
       <c r="K9" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="18" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
@@ -1763,17 +1669,17 @@
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
       <c r="AL9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="AP9" s="20"/>
-      <c r="AQ9" s="19"/>
+      <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="19"/>
@@ -1798,19 +1704,19 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="5"/>
       <c r="K10" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -1821,7 +1727,7 @@
       <c r="R10" s="4"/>
       <c r="S10" s="5"/>
       <c r="T10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="5"/>
@@ -1836,7 +1742,7 @@
       <c r="AA10" s="4"/>
       <c r="AB10" s="5"/>
       <c r="AC10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AD10" s="4"/>
       <c r="AE10" s="5"/>
@@ -1846,7 +1752,7 @@
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5"/>
@@ -1872,7 +1778,7 @@
       <c r="AY10" s="4"/>
       <c r="AZ10" s="5"/>
       <c r="BA10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BB10" s="4"/>
       <c r="BC10" s="4"/>
@@ -1888,19 +1794,19 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
       <c r="K11" s="4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1911,7 +1817,7 @@
       <c r="R11" s="4"/>
       <c r="S11" s="5"/>
       <c r="T11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="5"/>
@@ -1934,7 +1840,7 @@
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5"/>
@@ -1953,12 +1859,12 @@
       <c r="AV11" s="4"/>
       <c r="AW11" s="4"/>
       <c r="AX11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
@@ -1979,12 +1885,12 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="5"/>
       <c r="K12" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1995,7 +1901,7 @@
       <c r="R12" s="4"/>
       <c r="S12" s="5"/>
       <c r="T12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="5"/>
@@ -2018,7 +1924,7 @@
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
@@ -2052,21 +1958,23 @@
     </row>
     <row r="13" spans="1:60" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
       <c r="K13" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -2110,7 +2018,7 @@
       <c r="AY13" s="4"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
@@ -2122,21 +2030,23 @@
     </row>
     <row r="14" spans="1:60" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="5"/>
       <c r="K14" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -2190,21 +2100,23 @@
     </row>
     <row r="15" spans="1:60" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="5"/>
       <c r="K15" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -2258,21 +2170,23 @@
     </row>
     <row r="16" spans="1:60" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="5"/>
       <c r="K16" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2298,12 +2212,12 @@
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="3" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
       <c r="AL16" s="3" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
@@ -2320,7 +2234,7 @@
       <c r="AY16" s="4"/>
       <c r="AZ16" s="5"/>
       <c r="BA16" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB16" s="4"/>
       <c r="BC16" s="4"/>
@@ -2332,7 +2246,7 @@
     </row>
     <row r="17" spans="1:60" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
@@ -2341,12 +2255,12 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
       <c r="K17" s="4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2372,12 +2286,12 @@
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="3" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
       <c r="AL17" s="3" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
@@ -2394,7 +2308,7 @@
       <c r="AY17" s="4"/>
       <c r="AZ17" s="5"/>
       <c r="BA17" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
@@ -2406,7 +2320,7 @@
     </row>
     <row r="18" spans="1:60" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
@@ -2415,12 +2329,12 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="5"/>
       <c r="K18" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2464,7 +2378,7 @@
       <c r="AY18" s="4"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
@@ -2476,7 +2390,7 @@
     </row>
     <row r="19" spans="1:60" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -2485,12 +2399,12 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
       <c r="K19" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2534,7 +2448,7 @@
       <c r="AY19" s="4"/>
       <c r="AZ19" s="5"/>
       <c r="BA19" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB19" s="4"/>
       <c r="BC19" s="4"/>
@@ -2546,7 +2460,7 @@
     </row>
     <row r="20" spans="1:60" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -2555,12 +2469,12 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
       <c r="K20" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2604,7 +2518,7 @@
       <c r="AY20" s="4"/>
       <c r="AZ20" s="5"/>
       <c r="BA20" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
@@ -2616,7 +2530,7 @@
     </row>
     <row r="21" spans="1:60" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -2625,12 +2539,12 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="5"/>
       <c r="K21" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2674,7 +2588,7 @@
       <c r="AY21" s="4"/>
       <c r="AZ21" s="5"/>
       <c r="BA21" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
@@ -2686,23 +2600,23 @@
     </row>
     <row r="22" spans="1:60" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
       <c r="K22" s="4" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2710,7 +2624,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5"/>
@@ -2748,7 +2662,7 @@
       <c r="AY22" s="4"/>
       <c r="AZ22" s="5"/>
       <c r="BA22" s="4" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
@@ -2760,23 +2674,23 @@
     </row>
     <row r="23" spans="1:60" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="5"/>
       <c r="K23" s="4" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2784,7 +2698,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5"/>
@@ -2809,10 +2723,10 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
-      <c r="AO23" s="25"/>
+      <c r="AO23" s="24"/>
       <c r="AP23" s="21"/>
       <c r="AQ23" s="5"/>
-      <c r="AR23" s="25"/>
+      <c r="AR23" s="24"/>
       <c r="AS23" s="21"/>
       <c r="AT23" s="5"/>
       <c r="AU23" s="4"/>
@@ -2822,7 +2736,7 @@
       <c r="AY23" s="4"/>
       <c r="AZ23" s="5"/>
       <c r="BA23" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
@@ -2834,23 +2748,23 @@
     </row>
     <row r="24" spans="1:60" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="3" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="5"/>
       <c r="K24" s="4" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2858,7 +2772,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5"/>
@@ -2896,7 +2810,7 @@
       <c r="AY24" s="4"/>
       <c r="AZ24" s="5"/>
       <c r="BA24" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
@@ -2908,23 +2822,23 @@
     </row>
     <row r="25" spans="1:60" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="5"/>
       <c r="K25" s="4" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2932,7 +2846,7 @@
       <c r="O25" s="4"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5"/>
@@ -2970,7 +2884,7 @@
       <c r="AY25" s="4"/>
       <c r="AZ25" s="5"/>
       <c r="BA25" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
@@ -2982,23 +2896,23 @@
     </row>
     <row r="26" spans="1:60" ht="14" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="3" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="5"/>
       <c r="K26" s="4" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -3006,7 +2920,7 @@
       <c r="O26" s="4"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5"/>
@@ -3044,7 +2958,7 @@
       <c r="AY26" s="4"/>
       <c r="AZ26" s="5"/>
       <c r="BA26" s="4" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
@@ -3056,23 +2970,23 @@
     </row>
     <row r="27" spans="1:60" ht="14" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
       <c r="K27" s="4" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -3080,7 +2994,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5"/>
@@ -3105,10 +3019,10 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
-      <c r="AO27" s="25"/>
+      <c r="AO27" s="24"/>
       <c r="AP27" s="21"/>
       <c r="AQ27" s="5"/>
-      <c r="AR27" s="25"/>
+      <c r="AR27" s="24"/>
       <c r="AS27" s="21"/>
       <c r="AT27" s="5"/>
       <c r="AU27" s="4"/>
@@ -3118,7 +3032,7 @@
       <c r="AY27" s="4"/>
       <c r="AZ27" s="5"/>
       <c r="BA27" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
@@ -3130,23 +3044,23 @@
     </row>
     <row r="28" spans="1:60" ht="14" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="5"/>
       <c r="K28" s="4" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -3154,7 +3068,7 @@
       <c r="O28" s="4"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5"/>
@@ -3192,7 +3106,7 @@
       <c r="AY28" s="4"/>
       <c r="AZ28" s="5"/>
       <c r="BA28" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
@@ -3204,23 +3118,23 @@
     </row>
     <row r="29" spans="1:60" ht="14" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5"/>
       <c r="K29" s="4" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -3228,7 +3142,7 @@
       <c r="O29" s="4"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5"/>
@@ -3266,7 +3180,7 @@
       <c r="AY29" s="4"/>
       <c r="AZ29" s="5"/>
       <c r="BA29" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
@@ -3896,6 +3810,378 @@
       <c r="BG39" s="4"/>
       <c r="BH39" s="5"/>
     </row>
+    <row r="40" spans="1:60" ht="14" customHeight="1">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="5"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="4"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="5"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="5"/>
+      <c r="AR40" s="3"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="5"/>
+      <c r="AU40" s="4"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="3"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="4"/>
+      <c r="BB40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="5"/>
+    </row>
+    <row r="41" spans="1:60" ht="14" customHeight="1">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="5"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="5"/>
+      <c r="AL41" s="3"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="3"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="5"/>
+      <c r="AR41" s="3"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="5"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="3"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="5"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="5"/>
+    </row>
+    <row r="42" spans="1:60" ht="14" customHeight="1">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="5"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="3"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="5"/>
+      <c r="AL42" s="3"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="3"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="5"/>
+      <c r="AR42" s="3"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="5"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="3"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="5"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="5"/>
+    </row>
+    <row r="43" spans="1:60" ht="14" customHeight="1">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="5"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="3"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="5"/>
+      <c r="AL43" s="3"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="3"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="5"/>
+      <c r="AR43" s="3"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="5"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="3"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="5"/>
+    </row>
+    <row r="44" spans="1:60" ht="14" customHeight="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="5"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="5"/>
+      <c r="AL44" s="3"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="3"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="5"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="5"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="3"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="5"/>
+    </row>
+    <row r="45" spans="1:60" ht="14" customHeight="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="5"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="5"/>
+      <c r="AL45" s="3"/>
+      <c r="AM45" s="4"/>
+      <c r="AN45" s="4"/>
+      <c r="AO45" s="3"/>
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="5"/>
+      <c r="AR45" s="3"/>
+      <c r="AS45" s="4"/>
+      <c r="AT45" s="5"/>
+      <c r="AU45" s="4"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="3"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="4"/>
+      <c r="BB45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="4"/>
+      <c r="BE45" s="4"/>
+      <c r="BF45" s="4"/>
+      <c r="BG45" s="4"/>
+      <c r="BH45" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3913,7 +4199,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -3935,7 +4221,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="7" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="L1" s="22"/>
       <c r="M1" s="8"/>
@@ -4005,7 +4291,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="L2" s="23"/>
       <c r="M2" s="4"/>
@@ -4073,7 +4359,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="12" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="L3"/>
       <c r="M3" s="13"/>
@@ -4276,7 +4562,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
@@ -4351,17 +4637,17 @@
       <c r="I9" s="20"/>
       <c r="J9" s="19"/>
       <c r="K9" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="18" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
@@ -4396,17 +4682,17 @@
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
       <c r="AL9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="19"/>
@@ -4431,19 +4717,19 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="5"/>
       <c r="K10" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -4454,18 +4740,22 @@
       <c r="R10" s="4"/>
       <c r="S10" s="5"/>
       <c r="T10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="5"/>
-      <c r="W10" s="3"/>
+      <c r="W10" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="3"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="AA10" s="4"/>
       <c r="AB10" s="5"/>
       <c r="AC10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AD10" s="4"/>
       <c r="AE10" s="5"/>
@@ -4475,7 +4765,7 @@
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5"/>
@@ -4486,7 +4776,7 @@
       <c r="AN10" s="4"/>
       <c r="AO10" s="3"/>
       <c r="AP10" s="4"/>
-      <c r="AQ10" s="4"/>
+      <c r="AQ10" s="5"/>
       <c r="AR10" s="3"/>
       <c r="AS10" s="4"/>
       <c r="AT10" s="5"/>
@@ -4501,7 +4791,7 @@
       <c r="AY10" s="4"/>
       <c r="AZ10" s="5"/>
       <c r="BA10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BB10" s="4"/>
       <c r="BC10" s="4"/>
@@ -4517,19 +4807,19 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
       <c r="K11" s="4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -4544,10 +4834,14 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="5"/>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-      <c r="Z11" s="3"/>
+      <c r="Z11" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="AA11" s="4"/>
       <c r="AB11" s="5"/>
       <c r="AC11" s="3"/>
@@ -4559,7 +4853,7 @@
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5"/>
@@ -4568,7 +4862,7 @@
       <c r="AN11" s="4"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="4"/>
-      <c r="AQ11" s="4"/>
+      <c r="AQ11" s="5"/>
       <c r="AR11" s="3"/>
       <c r="AS11" s="4"/>
       <c r="AT11" s="5"/>
@@ -4578,12 +4872,12 @@
       <c r="AV11" s="4"/>
       <c r="AW11" s="4"/>
       <c r="AX11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="BB11" s="4"/>
       <c r="BC11" s="4"/>
@@ -4604,12 +4898,12 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="5"/>
       <c r="K12" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -4624,10 +4918,14 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="5"/>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="3"/>
+      <c r="Z12" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="AA12" s="4"/>
       <c r="AB12" s="5"/>
       <c r="AC12" s="3"/>
@@ -4639,7 +4937,7 @@
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
       <c r="AI12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
@@ -4648,16 +4946,18 @@
       <c r="AN12" s="4"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="4"/>
+      <c r="AQ12" s="5"/>
       <c r="AR12" s="3"/>
       <c r="AS12" s="4"/>
       <c r="AT12" s="5"/>
       <c r="AU12" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV12" s="4"/>
       <c r="AW12" s="4"/>
-      <c r="AX12" s="3"/>
+      <c r="AX12" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="AY12" s="4"/>
       <c r="AZ12" s="5"/>
       <c r="BA12" s="4"/>
@@ -4671,21 +4971,23 @@
     </row>
     <row r="13" spans="1:60" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
       <c r="K13" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -4695,9 +4997,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="4"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="T13" s="3"/>
       <c r="U13" s="4"/>
       <c r="V13" s="5"/>
       <c r="W13" s="4"/>
@@ -4720,7 +5020,7 @@
       <c r="AN13" s="4"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="4"/>
-      <c r="AQ13" s="4"/>
+      <c r="AQ13" s="5"/>
       <c r="AR13" s="3"/>
       <c r="AS13" s="4"/>
       <c r="AT13" s="5"/>
@@ -4731,7 +5031,7 @@
       <c r="AY13" s="4"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="BB13" s="4"/>
       <c r="BC13" s="4"/>
@@ -4743,21 +5043,23 @@
     </row>
     <row r="14" spans="1:60" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="5"/>
       <c r="K14" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -4790,7 +5092,7 @@
       <c r="AN14" s="4"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="4"/>
-      <c r="AQ14" s="4"/>
+      <c r="AQ14" s="5"/>
       <c r="AR14" s="3"/>
       <c r="AS14" s="4"/>
       <c r="AT14" s="5"/>
@@ -4811,21 +5113,23 @@
     </row>
     <row r="15" spans="1:60" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="5"/>
       <c r="K15" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -4858,7 +5162,7 @@
       <c r="AN15" s="4"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="4"/>
-      <c r="AQ15" s="4"/>
+      <c r="AQ15" s="5"/>
       <c r="AR15" s="3"/>
       <c r="AS15" s="4"/>
       <c r="AT15" s="5"/>
@@ -4879,30 +5183,30 @@
     </row>
     <row r="16" spans="1:60" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="5"/>
       <c r="K16" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="3"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="3" t="s">
-        <v>91</v>
-      </c>
+      <c r="Q16" s="3"/>
       <c r="R16" s="4"/>
       <c r="S16" s="5"/>
       <c r="T16" s="3"/>
@@ -4920,15 +5224,19 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
-      <c r="AI16" s="3"/>
+      <c r="AI16" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
-      <c r="AL16" s="3"/>
+      <c r="AL16" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="4"/>
-      <c r="AQ16" s="4"/>
+      <c r="AQ16" s="5"/>
       <c r="AR16" s="3"/>
       <c r="AS16" s="4"/>
       <c r="AT16" s="5"/>
@@ -4939,7 +5247,7 @@
       <c r="AY16" s="4"/>
       <c r="AZ16" s="5"/>
       <c r="BA16" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB16" s="4"/>
       <c r="BC16" s="4"/>
@@ -4951,7 +5259,7 @@
     </row>
     <row r="17" spans="1:60" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
@@ -4960,21 +5268,19 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
       <c r="K17" s="4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="3"/>
       <c r="O17" s="4"/>
       <c r="P17" s="5"/>
-      <c r="Q17" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="Q17" s="3"/>
       <c r="R17" s="4"/>
       <c r="S17" s="5"/>
       <c r="T17" s="3"/>
@@ -4992,15 +5298,19 @@
       <c r="AF17" s="3"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
-      <c r="AI17" s="3"/>
+      <c r="AI17" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
-      <c r="AL17" s="3"/>
+      <c r="AL17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="4"/>
-      <c r="AQ17" s="4"/>
+      <c r="AQ17" s="5"/>
       <c r="AR17" s="3"/>
       <c r="AS17" s="4"/>
       <c r="AT17" s="5"/>
@@ -5011,7 +5321,7 @@
       <c r="AY17" s="4"/>
       <c r="AZ17" s="5"/>
       <c r="BA17" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB17" s="4"/>
       <c r="BC17" s="4"/>
@@ -5023,7 +5333,7 @@
     </row>
     <row r="18" spans="1:60" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
@@ -5032,12 +5342,12 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="5"/>
       <c r="K18" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -5070,7 +5380,7 @@
       <c r="AN18" s="4"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="4"/>
-      <c r="AQ18" s="4"/>
+      <c r="AQ18" s="5"/>
       <c r="AR18" s="3"/>
       <c r="AS18" s="4"/>
       <c r="AT18" s="5"/>
@@ -5081,7 +5391,7 @@
       <c r="AY18" s="4"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB18" s="4"/>
       <c r="BC18" s="4"/>
@@ -5093,7 +5403,7 @@
     </row>
     <row r="19" spans="1:60" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -5102,12 +5412,12 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
       <c r="K19" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -5140,7 +5450,7 @@
       <c r="AN19" s="4"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="4"/>
-      <c r="AQ19" s="4"/>
+      <c r="AQ19" s="5"/>
       <c r="AR19" s="3"/>
       <c r="AS19" s="4"/>
       <c r="AT19" s="5"/>
@@ -5151,7 +5461,7 @@
       <c r="AY19" s="4"/>
       <c r="AZ19" s="5"/>
       <c r="BA19" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB19" s="4"/>
       <c r="BC19" s="4"/>
@@ -5163,7 +5473,7 @@
     </row>
     <row r="20" spans="1:60" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -5172,12 +5482,12 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
       <c r="K20" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -5210,7 +5520,7 @@
       <c r="AN20" s="4"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="4"/>
-      <c r="AQ20" s="4"/>
+      <c r="AQ20" s="5"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="4"/>
       <c r="AT20" s="5"/>
@@ -5221,7 +5531,7 @@
       <c r="AY20" s="4"/>
       <c r="AZ20" s="5"/>
       <c r="BA20" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB20" s="4"/>
       <c r="BC20" s="4"/>
@@ -5233,7 +5543,7 @@
     </row>
     <row r="21" spans="1:60" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -5242,12 +5552,12 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="5"/>
       <c r="K21" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -5280,7 +5590,7 @@
       <c r="AN21" s="4"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="4"/>
-      <c r="AQ21" s="4"/>
+      <c r="AQ21" s="5"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="4"/>
       <c r="AT21" s="5"/>
@@ -5291,7 +5601,7 @@
       <c r="AY21" s="4"/>
       <c r="AZ21" s="5"/>
       <c r="BA21" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="BB21" s="4"/>
       <c r="BC21" s="4"/>
@@ -5303,23 +5613,23 @@
     </row>
     <row r="22" spans="1:60" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="3" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
       <c r="K22" s="4" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -5327,7 +5637,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5"/>
@@ -5365,7 +5675,7 @@
       <c r="AY22" s="4"/>
       <c r="AZ22" s="5"/>
       <c r="BA22" s="4" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="BB22" s="4"/>
       <c r="BC22" s="4"/>
@@ -5377,23 +5687,23 @@
     </row>
     <row r="23" spans="1:60" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="3" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="5"/>
       <c r="K23" s="4" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -5401,7 +5711,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5"/>
@@ -5426,10 +5736,10 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
-      <c r="AO23" s="25"/>
+      <c r="AO23" s="24"/>
       <c r="AP23" s="21"/>
       <c r="AQ23" s="5"/>
-      <c r="AR23" s="25"/>
+      <c r="AR23" s="24"/>
       <c r="AS23" s="21"/>
       <c r="AT23" s="5"/>
       <c r="AU23" s="4"/>
@@ -5439,7 +5749,7 @@
       <c r="AY23" s="4"/>
       <c r="AZ23" s="5"/>
       <c r="BA23" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB23" s="4"/>
       <c r="BC23" s="4"/>
@@ -5451,23 +5761,23 @@
     </row>
     <row r="24" spans="1:60" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="3" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="5"/>
       <c r="K24" s="4" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -5475,7 +5785,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5"/>
@@ -5513,7 +5823,7 @@
       <c r="AY24" s="4"/>
       <c r="AZ24" s="5"/>
       <c r="BA24" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB24" s="4"/>
       <c r="BC24" s="4"/>
@@ -5525,23 +5835,23 @@
     </row>
     <row r="25" spans="1:60" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="5"/>
       <c r="K25" s="4" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -5549,7 +5859,7 @@
       <c r="O25" s="4"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5"/>
@@ -5587,7 +5897,7 @@
       <c r="AY25" s="4"/>
       <c r="AZ25" s="5"/>
       <c r="BA25" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB25" s="4"/>
       <c r="BC25" s="4"/>
@@ -5599,23 +5909,23 @@
     </row>
     <row r="26" spans="1:60" ht="14" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="3" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="5"/>
       <c r="K26" s="4" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -5623,7 +5933,7 @@
       <c r="O26" s="4"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5"/>
@@ -5661,7 +5971,7 @@
       <c r="AY26" s="4"/>
       <c r="AZ26" s="5"/>
       <c r="BA26" s="4" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="BB26" s="4"/>
       <c r="BC26" s="4"/>
@@ -5673,23 +5983,23 @@
     </row>
     <row r="27" spans="1:60" ht="14" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
       <c r="K27" s="4" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -5697,7 +6007,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5"/>
@@ -5722,10 +6032,10 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
-      <c r="AO27" s="25"/>
+      <c r="AO27" s="24"/>
       <c r="AP27" s="21"/>
       <c r="AQ27" s="5"/>
-      <c r="AR27" s="25"/>
+      <c r="AR27" s="24"/>
       <c r="AS27" s="21"/>
       <c r="AT27" s="5"/>
       <c r="AU27" s="4"/>
@@ -5735,7 +6045,7 @@
       <c r="AY27" s="4"/>
       <c r="AZ27" s="5"/>
       <c r="BA27" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB27" s="4"/>
       <c r="BC27" s="4"/>
@@ -5747,23 +6057,23 @@
     </row>
     <row r="28" spans="1:60" ht="14" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="5"/>
       <c r="K28" s="4" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -5771,7 +6081,7 @@
       <c r="O28" s="4"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5"/>
@@ -5809,7 +6119,7 @@
       <c r="AY28" s="4"/>
       <c r="AZ28" s="5"/>
       <c r="BA28" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB28" s="4"/>
       <c r="BC28" s="4"/>
@@ -5821,23 +6131,23 @@
     </row>
     <row r="29" spans="1:60" ht="14" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="5"/>
       <c r="K29" s="4" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -5845,7 +6155,7 @@
       <c r="O29" s="4"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5"/>
@@ -5883,7 +6193,7 @@
       <c r="AY29" s="4"/>
       <c r="AZ29" s="5"/>
       <c r="BA29" s="4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="BB29" s="4"/>
       <c r="BC29" s="4"/>
@@ -5936,7 +6246,7 @@
       <c r="AN30" s="4"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="4"/>
-      <c r="AQ30" s="4"/>
+      <c r="AQ30" s="5"/>
       <c r="AR30" s="3"/>
       <c r="AS30" s="4"/>
       <c r="AT30" s="5"/>
@@ -5998,7 +6308,7 @@
       <c r="AN31" s="4"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="4"/>
-      <c r="AQ31" s="4"/>
+      <c r="AQ31" s="5"/>
       <c r="AR31" s="3"/>
       <c r="AS31" s="4"/>
       <c r="AT31" s="5"/>
@@ -6060,7 +6370,7 @@
       <c r="AN32" s="4"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="4"/>
-      <c r="AQ32" s="4"/>
+      <c r="AQ32" s="5"/>
       <c r="AR32" s="3"/>
       <c r="AS32" s="4"/>
       <c r="AT32" s="5"/>
@@ -6122,7 +6432,7 @@
       <c r="AN33" s="4"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="4"/>
-      <c r="AQ33" s="4"/>
+      <c r="AQ33" s="5"/>
       <c r="AR33" s="3"/>
       <c r="AS33" s="4"/>
       <c r="AT33" s="5"/>
@@ -6184,7 +6494,7 @@
       <c r="AN34" s="4"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
+      <c r="AQ34" s="5"/>
       <c r="AR34" s="3"/>
       <c r="AS34" s="4"/>
       <c r="AT34" s="5"/>
@@ -6246,7 +6556,7 @@
       <c r="AN35" s="4"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="4"/>
-      <c r="AQ35" s="4"/>
+      <c r="AQ35" s="5"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="4"/>
       <c r="AT35" s="5"/>
@@ -6308,7 +6618,7 @@
       <c r="AN36" s="4"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="4"/>
-      <c r="AQ36" s="4"/>
+      <c r="AQ36" s="5"/>
       <c r="AR36" s="3"/>
       <c r="AS36" s="4"/>
       <c r="AT36" s="5"/>
@@ -6370,7 +6680,7 @@
       <c r="AN37" s="4"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="4"/>
-      <c r="AQ37" s="4"/>
+      <c r="AQ37" s="5"/>
       <c r="AR37" s="3"/>
       <c r="AS37" s="4"/>
       <c r="AT37" s="5"/>
@@ -6432,7 +6742,7 @@
       <c r="AN38" s="4"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="4"/>
-      <c r="AQ38" s="4"/>
+      <c r="AQ38" s="5"/>
       <c r="AR38" s="3"/>
       <c r="AS38" s="4"/>
       <c r="AT38" s="5"/>
@@ -6494,7 +6804,7 @@
       <c r="AN39" s="4"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="4"/>
-      <c r="AQ39" s="4"/>
+      <c r="AQ39" s="5"/>
       <c r="AR39" s="3"/>
       <c r="AS39" s="4"/>
       <c r="AT39" s="5"/>
@@ -6513,6 +6823,378 @@
       <c r="BG39" s="4"/>
       <c r="BH39" s="5"/>
     </row>
+    <row r="40" spans="1:60" ht="14" customHeight="1">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="5"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="4"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="5"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="5"/>
+      <c r="AR40" s="3"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="5"/>
+      <c r="AU40" s="4"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="3"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="4"/>
+      <c r="BB40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="5"/>
+    </row>
+    <row r="41" spans="1:60" ht="14" customHeight="1">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="5"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="5"/>
+      <c r="AL41" s="3"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="3"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="5"/>
+      <c r="AR41" s="3"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="5"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="3"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="5"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="5"/>
+    </row>
+    <row r="42" spans="1:60" ht="14" customHeight="1">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="5"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="3"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="5"/>
+      <c r="AL42" s="3"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="3"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="5"/>
+      <c r="AR42" s="3"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="5"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="3"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="5"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="5"/>
+    </row>
+    <row r="43" spans="1:60" ht="14" customHeight="1">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="5"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="3"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="5"/>
+      <c r="AL43" s="3"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="3"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="5"/>
+      <c r="AR43" s="3"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="5"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="3"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="5"/>
+    </row>
+    <row r="44" spans="1:60" ht="14" customHeight="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="5"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="5"/>
+      <c r="AL44" s="3"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="3"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="5"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="5"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="3"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="5"/>
+    </row>
+    <row r="45" spans="1:60" ht="14" customHeight="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="5"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="5"/>
+      <c r="AL45" s="3"/>
+      <c r="AM45" s="4"/>
+      <c r="AN45" s="4"/>
+      <c r="AO45" s="3"/>
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="5"/>
+      <c r="AR45" s="3"/>
+      <c r="AS45" s="4"/>
+      <c r="AT45" s="5"/>
+      <c r="AU45" s="4"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="3"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="4"/>
+      <c r="BB45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="4"/>
+      <c r="BE45" s="4"/>
+      <c r="BF45" s="4"/>
+      <c r="BG45" s="4"/>
+      <c r="BH45" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -6522,2584 +7204,23 @@
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6A4E85-5CCA-1545-8BE7-C47DE91C5205}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BH39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
-  <cols>
-    <col min="1" max="29" width="2.42578125" style="6"/>
-    <col min="30" max="33" width="2.42578125" style="6" customWidth="1"/>
-    <col min="34" max="16384" width="2.42578125" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:60" ht="14" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="22"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="5"/>
-    </row>
-    <row r="2" spans="1:60" ht="14" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="4"/>
-      <c r="AS2" s="4"/>
-      <c r="AT2" s="4"/>
-      <c r="AU2" s="4"/>
-      <c r="AV2" s="4"/>
-      <c r="AW2" s="4"/>
-      <c r="AX2" s="4"/>
-      <c r="AY2" s="4"/>
-      <c r="AZ2" s="4"/>
-      <c r="BA2" s="4"/>
-      <c r="BB2" s="4"/>
-      <c r="BC2" s="4"/>
-      <c r="BD2" s="4"/>
-      <c r="BE2" s="4"/>
-      <c r="BF2" s="4"/>
-      <c r="BG2" s="4"/>
-      <c r="BH2" s="5"/>
-    </row>
-    <row r="3" spans="1:60" ht="14" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
-      <c r="AV3" s="4"/>
-      <c r="AW3" s="4"/>
-      <c r="AX3" s="4"/>
-      <c r="AY3" s="4"/>
-      <c r="AZ3" s="4"/>
-      <c r="BA3" s="4"/>
-      <c r="BB3" s="4"/>
-      <c r="BC3" s="4"/>
-      <c r="BD3" s="4"/>
-      <c r="BE3" s="4"/>
-      <c r="BF3" s="4"/>
-      <c r="BG3" s="4"/>
-      <c r="BH3" s="5"/>
-    </row>
-    <row r="4" spans="1:60" ht="14" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="8"/>
-      <c r="AH4" s="8"/>
-      <c r="AI4" s="8"/>
-      <c r="AJ4" s="8"/>
-      <c r="AK4" s="8"/>
-      <c r="AL4" s="8"/>
-      <c r="AM4" s="8"/>
-      <c r="AN4" s="8"/>
-      <c r="AO4" s="8"/>
-      <c r="AP4" s="8"/>
-      <c r="AQ4" s="8"/>
-      <c r="AR4" s="8"/>
-      <c r="AS4" s="8"/>
-      <c r="AT4" s="8"/>
-      <c r="AU4" s="8"/>
-      <c r="AV4" s="8"/>
-      <c r="AW4" s="8"/>
-      <c r="AX4" s="8"/>
-      <c r="AY4" s="8"/>
-      <c r="AZ4" s="8"/>
-      <c r="BA4" s="8"/>
-      <c r="BB4" s="8"/>
-      <c r="BC4" s="8"/>
-      <c r="BD4" s="8"/>
-      <c r="BE4" s="8"/>
-      <c r="BF4" s="8"/>
-      <c r="BG4" s="8"/>
-      <c r="BH4" s="9"/>
-    </row>
-    <row r="5" spans="1:60" ht="14" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="BH5" s="11"/>
-    </row>
-    <row r="6" spans="1:60" ht="14" customHeight="1">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="13"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="14"/>
-    </row>
-    <row r="8" spans="1:60" ht="14" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ8" s="17"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="17"/>
-      <c r="AN8" s="17"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="17"/>
-      <c r="AR8" s="17"/>
-      <c r="AS8" s="17"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="17"/>
-      <c r="AX8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="16"/>
-      <c r="BA8" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="17"/>
-      <c r="BD8" s="17"/>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="17"/>
-      <c r="BH8" s="16"/>
-    </row>
-    <row r="9" spans="1:60" ht="14" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="20"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG9" s="20"/>
-      <c r="AH9" s="20"/>
-      <c r="AI9" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ9" s="20"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="AM9" s="20"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="AP9" s="20"/>
-      <c r="AQ9" s="20"/>
-      <c r="AR9" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS9" s="20"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="18"/>
-      <c r="AV9" s="20"/>
-      <c r="AW9" s="20"/>
-      <c r="AX9" s="18"/>
-      <c r="AY9" s="20"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="20"/>
-      <c r="BB9" s="20"/>
-      <c r="BC9" s="20"/>
-      <c r="BD9" s="20"/>
-      <c r="BE9" s="20"/>
-      <c r="BF9" s="20"/>
-      <c r="BG9" s="20"/>
-      <c r="BH9" s="19"/>
-    </row>
-    <row r="10" spans="1:60" ht="14" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="4"/>
-      <c r="AG10" s="4"/>
-      <c r="AH10" s="4"/>
-      <c r="AI10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="4"/>
-      <c r="AN10" s="4"/>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="4"/>
-      <c r="AQ10" s="4"/>
-      <c r="AR10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="4"/>
-      <c r="AT10" s="5"/>
-      <c r="AU10" s="4"/>
-      <c r="AV10" s="4"/>
-      <c r="AW10" s="4"/>
-      <c r="AX10" s="3"/>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="5"/>
-      <c r="BA10" s="4"/>
-      <c r="BB10" s="4"/>
-      <c r="BC10" s="4"/>
-      <c r="BD10" s="4"/>
-      <c r="BE10" s="4"/>
-      <c r="BF10" s="4"/>
-      <c r="BG10" s="4"/>
-      <c r="BH10" s="5"/>
-    </row>
-    <row r="11" spans="1:60" ht="14" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="4"/>
-      <c r="AH11" s="4"/>
-      <c r="AI11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ11" s="4"/>
-      <c r="AK11" s="5"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="4"/>
-      <c r="AN11" s="4"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="4"/>
-      <c r="AQ11" s="4"/>
-      <c r="AR11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="4"/>
-      <c r="AT11" s="5"/>
-      <c r="AU11" s="4"/>
-      <c r="AV11" s="4"/>
-      <c r="AW11" s="4"/>
-      <c r="AX11" s="3"/>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="5"/>
-      <c r="BA11" s="4"/>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="4"/>
-      <c r="BD11" s="4"/>
-      <c r="BE11" s="4"/>
-      <c r="BF11" s="4"/>
-      <c r="BG11" s="4"/>
-      <c r="BH11" s="5"/>
-    </row>
-    <row r="12" spans="1:60" ht="14" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="4"/>
-      <c r="AH12" s="4"/>
-      <c r="AI12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ12" s="4"/>
-      <c r="AK12" s="5"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="4"/>
-      <c r="AN12" s="4"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="4"/>
-      <c r="AQ12" s="4"/>
-      <c r="AR12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="4"/>
-      <c r="AT12" s="5"/>
-      <c r="AU12" s="4"/>
-      <c r="AV12" s="4"/>
-      <c r="AW12" s="4"/>
-      <c r="AX12" s="3"/>
-      <c r="AY12" s="4"/>
-      <c r="AZ12" s="5"/>
-      <c r="BA12" s="4"/>
-      <c r="BB12" s="4"/>
-      <c r="BC12" s="4"/>
-      <c r="BD12" s="4"/>
-      <c r="BE12" s="4"/>
-      <c r="BF12" s="4"/>
-      <c r="BG12" s="4"/>
-      <c r="BH12" s="5"/>
-    </row>
-    <row r="13" spans="1:60" ht="14" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="4"/>
-      <c r="AH13" s="4"/>
-      <c r="AI13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ13" s="4"/>
-      <c r="AK13" s="5"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="4"/>
-      <c r="AN13" s="4"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="4"/>
-      <c r="AQ13" s="4"/>
-      <c r="AR13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="4"/>
-      <c r="AT13" s="5"/>
-      <c r="AU13" s="4"/>
-      <c r="AV13" s="4"/>
-      <c r="AW13" s="4"/>
-      <c r="AX13" s="3"/>
-      <c r="AY13" s="4"/>
-      <c r="AZ13" s="5"/>
-      <c r="BA13" s="4"/>
-      <c r="BB13" s="4"/>
-      <c r="BC13" s="4"/>
-      <c r="BD13" s="4"/>
-      <c r="BE13" s="4"/>
-      <c r="BF13" s="4"/>
-      <c r="BG13" s="4"/>
-      <c r="BH13" s="5"/>
-    </row>
-    <row r="14" spans="1:60" ht="14" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U14" s="4"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="5"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="4"/>
-      <c r="AH14" s="4"/>
-      <c r="AI14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ14" s="4"/>
-      <c r="AK14" s="5"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="4"/>
-      <c r="AN14" s="4"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="4"/>
-      <c r="AQ14" s="4"/>
-      <c r="AR14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="4"/>
-      <c r="AT14" s="5"/>
-      <c r="AU14" s="4"/>
-      <c r="AV14" s="4"/>
-      <c r="AW14" s="4"/>
-      <c r="AX14" s="3"/>
-      <c r="AY14" s="4"/>
-      <c r="AZ14" s="5"/>
-      <c r="BA14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="BB14" s="4"/>
-      <c r="BC14" s="4"/>
-      <c r="BD14" s="4"/>
-      <c r="BE14" s="4"/>
-      <c r="BF14" s="4"/>
-      <c r="BG14" s="4"/>
-      <c r="BH14" s="5"/>
-    </row>
-    <row r="15" spans="1:60" ht="14" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U15" s="4"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="5"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="4"/>
-      <c r="AH15" s="4"/>
-      <c r="AI15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ15" s="4"/>
-      <c r="AK15" s="5"/>
-      <c r="AL15" s="3"/>
-      <c r="AM15" s="4"/>
-      <c r="AN15" s="4"/>
-      <c r="AO15" s="3"/>
-      <c r="AP15" s="4"/>
-      <c r="AQ15" s="4"/>
-      <c r="AR15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="4"/>
-      <c r="AT15" s="5"/>
-      <c r="AU15" s="4"/>
-      <c r="AV15" s="4"/>
-      <c r="AW15" s="4"/>
-      <c r="AX15" s="3"/>
-      <c r="AY15" s="4"/>
-      <c r="AZ15" s="5"/>
-      <c r="BA15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BB15" s="4"/>
-      <c r="BC15" s="4"/>
-      <c r="BD15" s="4"/>
-      <c r="BE15" s="4"/>
-      <c r="BF15" s="4"/>
-      <c r="BG15" s="4"/>
-      <c r="BH15" s="5"/>
-    </row>
-    <row r="16" spans="1:60" ht="14" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="5"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
-      <c r="AF16" s="3"/>
-      <c r="AG16" s="4"/>
-      <c r="AH16" s="4"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="4"/>
-      <c r="AK16" s="5"/>
-      <c r="AM16" s="4"/>
-      <c r="AN16" s="4"/>
-      <c r="AP16" s="4"/>
-      <c r="AQ16" s="4"/>
-      <c r="AR16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="4"/>
-      <c r="AT16" s="5"/>
-      <c r="AU16" s="4"/>
-      <c r="AV16" s="4"/>
-      <c r="AW16" s="4"/>
-      <c r="AX16" s="3"/>
-      <c r="AY16" s="4"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="4"/>
-      <c r="BB16" s="4"/>
-      <c r="BC16" s="4"/>
-      <c r="BD16" s="4"/>
-      <c r="BE16" s="4"/>
-      <c r="BF16" s="4"/>
-      <c r="BG16" s="4"/>
-      <c r="BH16" s="5"/>
-    </row>
-    <row r="17" spans="1:60" ht="14" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="5"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="4"/>
-      <c r="AH17" s="4"/>
-      <c r="AI17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ17" s="4"/>
-      <c r="AK17" s="5"/>
-      <c r="AL17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM17" s="4"/>
-      <c r="AN17" s="4"/>
-      <c r="AO17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP17" s="4"/>
-      <c r="AQ17" s="4"/>
-      <c r="AR17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="4"/>
-      <c r="AT17" s="5"/>
-      <c r="AU17" s="4"/>
-      <c r="AV17" s="4"/>
-      <c r="AW17" s="4"/>
-      <c r="AX17" s="3"/>
-      <c r="AY17" s="4"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="4"/>
-      <c r="BB17" s="4"/>
-      <c r="BC17" s="4"/>
-      <c r="BD17" s="4"/>
-      <c r="BE17" s="4"/>
-      <c r="BF17" s="4"/>
-      <c r="BG17" s="4"/>
-      <c r="BH17" s="5"/>
-    </row>
-    <row r="18" spans="1:60" ht="14" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="4"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="4"/>
-      <c r="AH18" s="4"/>
-      <c r="AI18" s="3"/>
-      <c r="AJ18" s="4"/>
-      <c r="AK18" s="5"/>
-      <c r="AL18" s="4"/>
-      <c r="AM18" s="4"/>
-      <c r="AN18" s="4"/>
-      <c r="AO18" s="3"/>
-      <c r="AP18" s="4"/>
-      <c r="AQ18" s="4"/>
-      <c r="AR18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS18" s="4"/>
-      <c r="AT18" s="5"/>
-      <c r="AU18" s="4"/>
-      <c r="AV18" s="4"/>
-      <c r="AW18" s="4"/>
-      <c r="AX18" s="3"/>
-      <c r="AY18" s="4"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="4"/>
-      <c r="BB18" s="4"/>
-      <c r="BC18" s="4"/>
-      <c r="BD18" s="4"/>
-      <c r="BE18" s="4"/>
-      <c r="BF18" s="4"/>
-      <c r="BG18" s="4"/>
-      <c r="BH18" s="5"/>
-    </row>
-    <row r="19" spans="1:60" ht="14" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="5"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="5"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="4"/>
-      <c r="AQ19" s="4"/>
-      <c r="AR19" s="3"/>
-      <c r="AS19" s="4"/>
-      <c r="AT19" s="5"/>
-      <c r="AU19" s="4"/>
-      <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-      <c r="AX19" s="3"/>
-      <c r="AY19" s="4"/>
-      <c r="AZ19" s="5"/>
-      <c r="BA19" s="4"/>
-      <c r="BB19" s="4"/>
-      <c r="BC19" s="4"/>
-      <c r="BD19" s="4"/>
-      <c r="BE19" s="4"/>
-      <c r="BF19" s="4"/>
-      <c r="BG19" s="4"/>
-      <c r="BH19" s="5"/>
-    </row>
-    <row r="20" spans="1:60" ht="14" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
-      <c r="AF20" s="3"/>
-      <c r="AG20" s="4"/>
-      <c r="AH20" s="4"/>
-      <c r="AI20" s="3"/>
-      <c r="AJ20" s="4"/>
-      <c r="AK20" s="5"/>
-      <c r="AL20" s="4"/>
-      <c r="AM20" s="4"/>
-      <c r="AN20" s="4"/>
-      <c r="AO20" s="3"/>
-      <c r="AP20" s="4"/>
-      <c r="AQ20" s="4"/>
-      <c r="AR20" s="3"/>
-      <c r="AS20" s="4"/>
-      <c r="AT20" s="5"/>
-      <c r="AU20" s="4"/>
-      <c r="AV20" s="4"/>
-      <c r="AW20" s="4"/>
-      <c r="AX20" s="3"/>
-      <c r="AY20" s="4"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="4"/>
-      <c r="BB20" s="4"/>
-      <c r="BC20" s="4"/>
-      <c r="BD20" s="4"/>
-      <c r="BE20" s="4"/>
-      <c r="BF20" s="4"/>
-      <c r="BG20" s="4"/>
-      <c r="BH20" s="5"/>
-    </row>
-    <row r="21" spans="1:60" ht="14" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="4"/>
-      <c r="AD21" s="4"/>
-      <c r="AE21" s="4"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="4"/>
-      <c r="AH21" s="4"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="4"/>
-      <c r="AK21" s="5"/>
-      <c r="AL21" s="4"/>
-      <c r="AM21" s="4"/>
-      <c r="AN21" s="4"/>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="4"/>
-      <c r="AQ21" s="4"/>
-      <c r="AR21" s="3"/>
-      <c r="AS21" s="4"/>
-      <c r="AT21" s="5"/>
-      <c r="AU21" s="4"/>
-      <c r="AV21" s="4"/>
-      <c r="AW21" s="4"/>
-      <c r="AX21" s="3"/>
-      <c r="AY21" s="4"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="4"/>
-      <c r="BB21" s="4"/>
-      <c r="BC21" s="4"/>
-      <c r="BD21" s="4"/>
-      <c r="BE21" s="4"/>
-      <c r="BF21" s="4"/>
-      <c r="BG21" s="4"/>
-      <c r="BH21" s="5"/>
-    </row>
-    <row r="22" spans="1:60" ht="14" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="4"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="4"/>
-      <c r="AD22" s="4"/>
-      <c r="AE22" s="4"/>
-      <c r="AF22" s="3"/>
-      <c r="AG22" s="4"/>
-      <c r="AH22" s="4"/>
-      <c r="AI22" s="3"/>
-      <c r="AJ22" s="4"/>
-      <c r="AK22" s="5"/>
-      <c r="AL22" s="4"/>
-      <c r="AM22" s="4"/>
-      <c r="AN22" s="4"/>
-      <c r="AO22" s="3"/>
-      <c r="AP22" s="4"/>
-      <c r="AQ22" s="4"/>
-      <c r="AR22" s="3"/>
-      <c r="AS22" s="4"/>
-      <c r="AT22" s="5"/>
-      <c r="AU22" s="4"/>
-      <c r="AV22" s="4"/>
-      <c r="AW22" s="4"/>
-      <c r="AX22" s="3"/>
-      <c r="AY22" s="4"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="4"/>
-      <c r="BB22" s="4"/>
-      <c r="BC22" s="4"/>
-      <c r="BD22" s="4"/>
-      <c r="BE22" s="4"/>
-      <c r="BF22" s="4"/>
-      <c r="BG22" s="4"/>
-      <c r="BH22" s="5"/>
-    </row>
-    <row r="23" spans="1:60" ht="14" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="4"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="4"/>
-      <c r="AD23" s="4"/>
-      <c r="AE23" s="4"/>
-      <c r="AF23" s="3"/>
-      <c r="AG23" s="4"/>
-      <c r="AH23" s="4"/>
-      <c r="AI23" s="3"/>
-      <c r="AJ23" s="4"/>
-      <c r="AK23" s="5"/>
-      <c r="AL23" s="4"/>
-      <c r="AM23" s="4"/>
-      <c r="AN23" s="4"/>
-      <c r="AO23" s="3"/>
-      <c r="AP23" s="21"/>
-      <c r="AQ23" s="21"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="21"/>
-      <c r="AT23" s="5"/>
-      <c r="AU23" s="4"/>
-      <c r="AV23" s="4"/>
-      <c r="AW23" s="4"/>
-      <c r="AX23" s="3"/>
-      <c r="AY23" s="4"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="4"/>
-      <c r="BB23" s="4"/>
-      <c r="BC23" s="4"/>
-      <c r="BD23" s="4"/>
-      <c r="BE23" s="4"/>
-      <c r="BF23" s="4"/>
-      <c r="BG23" s="4"/>
-      <c r="BH23" s="5"/>
-    </row>
-    <row r="24" spans="1:60" ht="14" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="4"/>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="4"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="4"/>
-      <c r="AD24" s="4"/>
-      <c r="AE24" s="4"/>
-      <c r="AF24" s="3"/>
-      <c r="AG24" s="4"/>
-      <c r="AH24" s="4"/>
-      <c r="AI24" s="3"/>
-      <c r="AJ24" s="4"/>
-      <c r="AK24" s="5"/>
-      <c r="AL24" s="4"/>
-      <c r="AM24" s="4"/>
-      <c r="AN24" s="4"/>
-      <c r="AO24" s="3"/>
-      <c r="AP24" s="4"/>
-      <c r="AQ24" s="4"/>
-      <c r="AR24" s="3"/>
-      <c r="AS24" s="4"/>
-      <c r="AT24" s="5"/>
-      <c r="AU24" s="4"/>
-      <c r="AV24" s="4"/>
-      <c r="AW24" s="4"/>
-      <c r="AX24" s="3"/>
-      <c r="AY24" s="4"/>
-      <c r="AZ24" s="5"/>
-      <c r="BA24" s="4"/>
-      <c r="BB24" s="4"/>
-      <c r="BC24" s="4"/>
-      <c r="BD24" s="4"/>
-      <c r="BE24" s="4"/>
-      <c r="BF24" s="4"/>
-      <c r="BG24" s="4"/>
-      <c r="BH24" s="5"/>
-    </row>
-    <row r="25" spans="1:60" ht="14" customHeight="1">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="4"/>
-      <c r="AB25" s="5"/>
-      <c r="AC25" s="4"/>
-      <c r="AD25" s="4"/>
-      <c r="AE25" s="4"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="4"/>
-      <c r="AH25" s="4"/>
-      <c r="AI25" s="3"/>
-      <c r="AJ25" s="4"/>
-      <c r="AK25" s="5"/>
-      <c r="AL25" s="4"/>
-      <c r="AM25" s="4"/>
-      <c r="AN25" s="4"/>
-      <c r="AO25" s="3"/>
-      <c r="AP25" s="4"/>
-      <c r="AQ25" s="4"/>
-      <c r="AR25" s="3"/>
-      <c r="AS25" s="4"/>
-      <c r="AT25" s="5"/>
-      <c r="AU25" s="4"/>
-      <c r="AV25" s="4"/>
-      <c r="AW25" s="4"/>
-      <c r="AX25" s="3"/>
-      <c r="AY25" s="4"/>
-      <c r="AZ25" s="5"/>
-      <c r="BA25" s="4"/>
-      <c r="BB25" s="4"/>
-      <c r="BC25" s="4"/>
-      <c r="BD25" s="4"/>
-      <c r="BE25" s="4"/>
-      <c r="BF25" s="4"/>
-      <c r="BG25" s="4"/>
-      <c r="BH25" s="5"/>
-    </row>
-    <row r="26" spans="1:60" ht="14" customHeight="1">
-      <c r="A26" s="3"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="4"/>
-      <c r="AB26" s="5"/>
-      <c r="AC26" s="4"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
-      <c r="AF26" s="3"/>
-      <c r="AG26" s="4"/>
-      <c r="AH26" s="4"/>
-      <c r="AI26" s="3"/>
-      <c r="AJ26" s="4"/>
-      <c r="AK26" s="5"/>
-      <c r="AL26" s="4"/>
-      <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="3"/>
-      <c r="AP26" s="4"/>
-      <c r="AQ26" s="4"/>
-      <c r="AR26" s="3"/>
-      <c r="AS26" s="4"/>
-      <c r="AT26" s="5"/>
-      <c r="AU26" s="4"/>
-      <c r="AV26" s="4"/>
-      <c r="AW26" s="4"/>
-      <c r="AX26" s="3"/>
-      <c r="AY26" s="4"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="4"/>
-      <c r="BB26" s="4"/>
-      <c r="BC26" s="4"/>
-      <c r="BD26" s="4"/>
-      <c r="BE26" s="4"/>
-      <c r="BF26" s="4"/>
-      <c r="BG26" s="4"/>
-      <c r="BH26" s="5"/>
-    </row>
-    <row r="27" spans="1:60" ht="14" customHeight="1">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="4"/>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="4"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="4"/>
-      <c r="AB27" s="5"/>
-      <c r="AC27" s="4"/>
-      <c r="AD27" s="4"/>
-      <c r="AE27" s="4"/>
-      <c r="AF27" s="3"/>
-      <c r="AG27" s="4"/>
-      <c r="AH27" s="4"/>
-      <c r="AI27" s="3"/>
-      <c r="AJ27" s="4"/>
-      <c r="AK27" s="5"/>
-      <c r="AL27" s="4"/>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="3"/>
-      <c r="AP27" s="4"/>
-      <c r="AQ27" s="4"/>
-      <c r="AR27" s="3"/>
-      <c r="AS27" s="4"/>
-      <c r="AT27" s="5"/>
-      <c r="AU27" s="4"/>
-      <c r="AV27" s="4"/>
-      <c r="AW27" s="4"/>
-      <c r="AX27" s="3"/>
-      <c r="AY27" s="4"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="4"/>
-      <c r="BB27" s="4"/>
-      <c r="BC27" s="4"/>
-      <c r="BD27" s="4"/>
-      <c r="BE27" s="4"/>
-      <c r="BF27" s="4"/>
-      <c r="BG27" s="4"/>
-      <c r="BH27" s="5"/>
-    </row>
-    <row r="28" spans="1:60" ht="14" customHeight="1">
-      <c r="A28" s="3"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
-      <c r="Z28" s="3"/>
-      <c r="AA28" s="4"/>
-      <c r="AB28" s="5"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-      <c r="AF28" s="3"/>
-      <c r="AG28" s="4"/>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="3"/>
-      <c r="AJ28" s="4"/>
-      <c r="AK28" s="5"/>
-      <c r="AL28" s="4"/>
-      <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="3"/>
-      <c r="AP28" s="4"/>
-      <c r="AQ28" s="4"/>
-      <c r="AR28" s="3"/>
-      <c r="AS28" s="4"/>
-      <c r="AT28" s="5"/>
-      <c r="AU28" s="4"/>
-      <c r="AV28" s="4"/>
-      <c r="AW28" s="4"/>
-      <c r="AX28" s="3"/>
-      <c r="AY28" s="4"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="4"/>
-      <c r="BB28" s="4"/>
-      <c r="BC28" s="4"/>
-      <c r="BD28" s="4"/>
-      <c r="BE28" s="4"/>
-      <c r="BF28" s="4"/>
-      <c r="BG28" s="4"/>
-      <c r="BH28" s="5"/>
-    </row>
-    <row r="29" spans="1:60" ht="14" customHeight="1">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="3"/>
-      <c r="AA29" s="4"/>
-      <c r="AB29" s="5"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="3"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="3"/>
-      <c r="AJ29" s="4"/>
-      <c r="AK29" s="5"/>
-      <c r="AL29" s="4"/>
-      <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="3"/>
-      <c r="AP29" s="4"/>
-      <c r="AQ29" s="4"/>
-      <c r="AR29" s="3"/>
-      <c r="AS29" s="4"/>
-      <c r="AT29" s="5"/>
-      <c r="AU29" s="4"/>
-      <c r="AV29" s="4"/>
-      <c r="AW29" s="4"/>
-      <c r="AX29" s="3"/>
-      <c r="AY29" s="4"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="4"/>
-      <c r="BB29" s="4"/>
-      <c r="BC29" s="4"/>
-      <c r="BD29" s="4"/>
-      <c r="BE29" s="4"/>
-      <c r="BF29" s="4"/>
-      <c r="BG29" s="4"/>
-      <c r="BH29" s="5"/>
-    </row>
-    <row r="30" spans="1:60" ht="14" customHeight="1">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="5"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="3"/>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="5"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-      <c r="AF30" s="3"/>
-      <c r="AG30" s="4"/>
-      <c r="AH30" s="4"/>
-      <c r="AI30" s="3"/>
-      <c r="AJ30" s="4"/>
-      <c r="AK30" s="5"/>
-      <c r="AL30" s="4"/>
-      <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="3"/>
-      <c r="AP30" s="4"/>
-      <c r="AQ30" s="4"/>
-      <c r="AR30" s="3"/>
-      <c r="AS30" s="4"/>
-      <c r="AT30" s="5"/>
-      <c r="AU30" s="4"/>
-      <c r="AV30" s="4"/>
-      <c r="AW30" s="4"/>
-      <c r="AX30" s="3"/>
-      <c r="AY30" s="4"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="4"/>
-      <c r="BB30" s="4"/>
-      <c r="BC30" s="4"/>
-      <c r="BD30" s="4"/>
-      <c r="BE30" s="4"/>
-      <c r="BF30" s="4"/>
-      <c r="BG30" s="4"/>
-      <c r="BH30" s="5"/>
-    </row>
-    <row r="31" spans="1:60" ht="14" customHeight="1">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="4"/>
-      <c r="AB31" s="5"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="4"/>
-      <c r="AE31" s="4"/>
-      <c r="AF31" s="3"/>
-      <c r="AG31" s="4"/>
-      <c r="AH31" s="4"/>
-      <c r="AI31" s="3"/>
-      <c r="AJ31" s="4"/>
-      <c r="AK31" s="5"/>
-      <c r="AL31" s="4"/>
-      <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="3"/>
-      <c r="AP31" s="4"/>
-      <c r="AQ31" s="4"/>
-      <c r="AR31" s="3"/>
-      <c r="AS31" s="4"/>
-      <c r="AT31" s="5"/>
-      <c r="AU31" s="4"/>
-      <c r="AV31" s="4"/>
-      <c r="AW31" s="4"/>
-      <c r="AX31" s="3"/>
-      <c r="AY31" s="4"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="4"/>
-      <c r="BB31" s="4"/>
-      <c r="BC31" s="4"/>
-      <c r="BD31" s="4"/>
-      <c r="BE31" s="4"/>
-      <c r="BF31" s="4"/>
-      <c r="BG31" s="4"/>
-      <c r="BH31" s="5"/>
-    </row>
-    <row r="32" spans="1:60" ht="14" customHeight="1">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="4"/>
-      <c r="AB32" s="5"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="4"/>
-      <c r="AE32" s="4"/>
-      <c r="AF32" s="3"/>
-      <c r="AG32" s="4"/>
-      <c r="AH32" s="4"/>
-      <c r="AI32" s="3"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="5"/>
-      <c r="AL32" s="4"/>
-      <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="3"/>
-      <c r="AP32" s="4"/>
-      <c r="AQ32" s="4"/>
-      <c r="AR32" s="3"/>
-      <c r="AS32" s="4"/>
-      <c r="AT32" s="5"/>
-      <c r="AU32" s="4"/>
-      <c r="AV32" s="4"/>
-      <c r="AW32" s="4"/>
-      <c r="AX32" s="3"/>
-      <c r="AY32" s="4"/>
-      <c r="AZ32" s="5"/>
-      <c r="BA32" s="4"/>
-      <c r="BB32" s="4"/>
-      <c r="BC32" s="4"/>
-      <c r="BD32" s="4"/>
-      <c r="BE32" s="4"/>
-      <c r="BF32" s="4"/>
-      <c r="BG32" s="4"/>
-      <c r="BH32" s="5"/>
-    </row>
-    <row r="33" spans="1:60" ht="14" customHeight="1">
-      <c r="A33" s="3"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="5"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="5"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
-      <c r="AF33" s="3"/>
-      <c r="AG33" s="4"/>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="3"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="5"/>
-      <c r="AL33" s="4"/>
-      <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="3"/>
-      <c r="AP33" s="4"/>
-      <c r="AQ33" s="4"/>
-      <c r="AR33" s="3"/>
-      <c r="AS33" s="4"/>
-      <c r="AT33" s="5"/>
-      <c r="AU33" s="4"/>
-      <c r="AV33" s="4"/>
-      <c r="AW33" s="4"/>
-      <c r="AX33" s="3"/>
-      <c r="AY33" s="4"/>
-      <c r="AZ33" s="5"/>
-      <c r="BA33" s="4"/>
-      <c r="BB33" s="4"/>
-      <c r="BC33" s="4"/>
-      <c r="BD33" s="4"/>
-      <c r="BE33" s="4"/>
-      <c r="BF33" s="4"/>
-      <c r="BG33" s="4"/>
-      <c r="BH33" s="5"/>
-    </row>
-    <row r="34" spans="1:60" ht="14" customHeight="1">
-      <c r="A34" s="3"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="5"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="5"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="3"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="3"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="5"/>
-      <c r="AL34" s="4"/>
-      <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="3"/>
-      <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
-      <c r="AR34" s="3"/>
-      <c r="AS34" s="4"/>
-      <c r="AT34" s="5"/>
-      <c r="AU34" s="4"/>
-      <c r="AV34" s="4"/>
-      <c r="AW34" s="4"/>
-      <c r="AX34" s="3"/>
-      <c r="AY34" s="4"/>
-      <c r="AZ34" s="5"/>
-      <c r="BA34" s="4"/>
-      <c r="BB34" s="4"/>
-      <c r="BC34" s="4"/>
-      <c r="BD34" s="4"/>
-      <c r="BE34" s="4"/>
-      <c r="BF34" s="4"/>
-      <c r="BG34" s="4"/>
-      <c r="BH34" s="5"/>
-    </row>
-    <row r="35" spans="1:60" ht="14" customHeight="1">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="5"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="5"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="3"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="3"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="5"/>
-      <c r="AL35" s="4"/>
-      <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="3"/>
-      <c r="AP35" s="4"/>
-      <c r="AQ35" s="4"/>
-      <c r="AR35" s="3"/>
-      <c r="AS35" s="4"/>
-      <c r="AT35" s="5"/>
-      <c r="AU35" s="4"/>
-      <c r="AV35" s="4"/>
-      <c r="AW35" s="4"/>
-      <c r="AX35" s="3"/>
-      <c r="AY35" s="4"/>
-      <c r="AZ35" s="5"/>
-      <c r="BA35" s="4"/>
-      <c r="BB35" s="4"/>
-      <c r="BC35" s="4"/>
-      <c r="BD35" s="4"/>
-      <c r="BE35" s="4"/>
-      <c r="BF35" s="4"/>
-      <c r="BG35" s="4"/>
-      <c r="BH35" s="5"/>
-    </row>
-    <row r="36" spans="1:60" ht="14" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="5"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="5"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="3"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="3"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="5"/>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="3"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="4"/>
-      <c r="AR36" s="3"/>
-      <c r="AS36" s="4"/>
-      <c r="AT36" s="5"/>
-      <c r="AU36" s="4"/>
-      <c r="AV36" s="4"/>
-      <c r="AW36" s="4"/>
-      <c r="AX36" s="3"/>
-      <c r="AY36" s="4"/>
-      <c r="AZ36" s="5"/>
-      <c r="BA36" s="4"/>
-      <c r="BB36" s="4"/>
-      <c r="BC36" s="4"/>
-      <c r="BD36" s="4"/>
-      <c r="BE36" s="4"/>
-      <c r="BF36" s="4"/>
-      <c r="BG36" s="4"/>
-      <c r="BH36" s="5"/>
-    </row>
-    <row r="37" spans="1:60" ht="14" customHeight="1">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="5"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="5"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
-      <c r="AF37" s="3"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
-      <c r="AI37" s="3"/>
-      <c r="AJ37" s="4"/>
-      <c r="AK37" s="5"/>
-      <c r="AL37" s="4"/>
-      <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="3"/>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="4"/>
-      <c r="AR37" s="3"/>
-      <c r="AS37" s="4"/>
-      <c r="AT37" s="5"/>
-      <c r="AU37" s="4"/>
-      <c r="AV37" s="4"/>
-      <c r="AW37" s="4"/>
-      <c r="AX37" s="3"/>
-      <c r="AY37" s="4"/>
-      <c r="AZ37" s="5"/>
-      <c r="BA37" s="4"/>
-      <c r="BB37" s="4"/>
-      <c r="BC37" s="4"/>
-      <c r="BD37" s="4"/>
-      <c r="BE37" s="4"/>
-      <c r="BF37" s="4"/>
-      <c r="BG37" s="4"/>
-      <c r="BH37" s="5"/>
-    </row>
-    <row r="38" spans="1:60" ht="14" customHeight="1">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="5"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="5"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="3"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="3"/>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="5"/>
-      <c r="AL38" s="4"/>
-      <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="3"/>
-      <c r="AP38" s="4"/>
-      <c r="AQ38" s="4"/>
-      <c r="AR38" s="3"/>
-      <c r="AS38" s="4"/>
-      <c r="AT38" s="5"/>
-      <c r="AU38" s="4"/>
-      <c r="AV38" s="4"/>
-      <c r="AW38" s="4"/>
-      <c r="AX38" s="3"/>
-      <c r="AY38" s="4"/>
-      <c r="AZ38" s="5"/>
-      <c r="BA38" s="4"/>
-      <c r="BB38" s="4"/>
-      <c r="BC38" s="4"/>
-      <c r="BD38" s="4"/>
-      <c r="BE38" s="4"/>
-      <c r="BF38" s="4"/>
-      <c r="BG38" s="4"/>
-      <c r="BH38" s="5"/>
-    </row>
-    <row r="39" spans="1:60" ht="14" customHeight="1">
-      <c r="A39" s="3"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="5"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="5"/>
-      <c r="AC39" s="4"/>
-      <c r="AD39" s="4"/>
-      <c r="AE39" s="4"/>
-      <c r="AF39" s="3"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="3"/>
-      <c r="AJ39" s="4"/>
-      <c r="AK39" s="5"/>
-      <c r="AL39" s="4"/>
-      <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="3"/>
-      <c r="AP39" s="4"/>
-      <c r="AQ39" s="4"/>
-      <c r="AR39" s="3"/>
-      <c r="AS39" s="4"/>
-      <c r="AT39" s="5"/>
-      <c r="AU39" s="4"/>
-      <c r="AV39" s="4"/>
-      <c r="AW39" s="4"/>
-      <c r="AX39" s="3"/>
-      <c r="AY39" s="4"/>
-      <c r="AZ39" s="5"/>
-      <c r="BA39" s="4"/>
-      <c r="BB39" s="4"/>
-      <c r="BC39" s="4"/>
-      <c r="BD39" s="4"/>
-      <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
-      <c r="BG39" s="4"/>
-      <c r="BH39" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
-    <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
-  </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D93C2F7-C0F6-924A-BBA6-30F6365A1D50}">
+          <x14:formula1>
+            <xm:f>'#SAMPLE'!$H$10:$H$45</xm:f>
+          </x14:formula1>
+          <xm:sqref>H10:H45</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EACF85C5-A8B1-FC41-8DC7-419D4BD600EC}">
+          <x14:formula1>
+            <xm:f>'#SAMPLE'!$K$10:$K$45</xm:f>
+          </x14:formula1>
+          <xm:sqref>K10:K45</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/build/Sample.xlsx
+++ b/build/Sample.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/Documents/Repos/golang/generateTables/build/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D9946F-E269-6F45-9043-1207EEA65EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EEF6B8-80F4-DC42-88D0-39A9607F4928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="600" windowWidth="27880" windowHeight="17400" activeTab="1" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
+    <workbookView xWindow="18180" yWindow="600" windowWidth="27880" windowHeight="17400" activeTab="1" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="#SAMPLE" sheetId="14" r:id="rId1"/>
-    <sheet name="SAMPLE" sheetId="12" r:id="rId2"/>
+    <sheet name="#SAMPLE" sheetId="16" r:id="rId1"/>
+    <sheet name="SAMPLE" sheetId="18" r:id="rId2"/>
+    <sheet name="@Sys" sheetId="17" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="144">
   <si>
     <t>False</t>
     <phoneticPr fontId="1"/>
@@ -611,12 +612,159 @@
     <t>2.fuga</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>@Sys</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>z_作成TS</t>
+  </si>
+  <si>
+    <t>通常タイプ</t>
+  </si>
+  <si>
+    <t>タイムスタンプ型</t>
+  </si>
+  <si>
+    <t>日付のみ</t>
+  </si>
+  <si>
+    <t>作成TS</t>
+  </si>
+  <si>
+    <t>z_作成者</t>
+  </si>
+  <si>
+    <t>テキスト型</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>z_修正TS</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>修正TS</t>
+  </si>
+  <si>
+    <t>z_修正者</t>
+  </si>
+  <si>
+    <t>修正者</t>
+  </si>
+  <si>
+    <t>z_削除フラグ</t>
+  </si>
+  <si>
+    <t>数字型</t>
+  </si>
+  <si>
+    <t>数字のみ</t>
+  </si>
+  <si>
+    <t>固定値</t>
+  </si>
+  <si>
+    <t>0: 未削除 1: 削除</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">サクジョ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>z_00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Always 0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>z_01</t>
+  </si>
+  <si>
+    <t>Always 1</t>
+  </si>
+  <si>
+    <t>OnWindowTransaction</t>
+  </si>
+  <si>
+    <t>__PK_ID</t>
+  </si>
+  <si>
+    <t>計算値</t>
+  </si>
+  <si>
+    <t>Get( UUID )</t>
+  </si>
+  <si>
+    <t>//----------</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>テキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>数字</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">スウジ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ヒヅケ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>時刻</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジコク </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>タイムスタンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -647,6 +795,13 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -662,7 +817,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -787,13 +942,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -867,6 +1035,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1182,11 +1377,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C938FA-784A-5E46-889A-2A02A5B7B050}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E23277E-66BF-4047-BD1E-7131CA4A8422}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH45"/>
+  <dimension ref="A1:BK45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -1194,7 +1389,7 @@
     <col min="31" max="16384" width="2.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="14" customHeight="1">
+    <row r="1" spans="1:63" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1241,12 +1436,12 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -1262,9 +1457,12 @@
       <c r="BE1" s="4"/>
       <c r="BF1" s="4"/>
       <c r="BG1" s="4"/>
-      <c r="BH1" s="5"/>
-    </row>
-    <row r="2" spans="1:60" ht="14" customHeight="1">
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="5"/>
+    </row>
+    <row r="2" spans="1:63" ht="14" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -1311,10 +1509,10 @@
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="4"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="3"/>
       <c r="AS2" s="4"/>
       <c r="AT2" s="4"/>
       <c r="AU2" s="4"/>
@@ -1330,9 +1528,12 @@
       <c r="BE2" s="4"/>
       <c r="BF2" s="4"/>
       <c r="BG2" s="4"/>
-      <c r="BH2" s="5"/>
-    </row>
-    <row r="3" spans="1:60" ht="14" customHeight="1">
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="4"/>
+      <c r="BJ2" s="4"/>
+      <c r="BK2" s="5"/>
+    </row>
+    <row r="3" spans="1:63" ht="14" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,10 +1580,10 @@
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="3"/>
       <c r="AS3" s="4"/>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
@@ -1398,9 +1599,12 @@
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
-      <c r="BH3" s="5"/>
-    </row>
-    <row r="4" spans="1:60" ht="14" customHeight="1">
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="5"/>
+    </row>
+    <row r="4" spans="1:63" ht="14" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -1462,13 +1666,16 @@
       <c r="BE4" s="8"/>
       <c r="BF4" s="8"/>
       <c r="BG4" s="8"/>
-      <c r="BH4" s="9"/>
-    </row>
-    <row r="5" spans="1:60" ht="14" customHeight="1">
+      <c r="BH4" s="8"/>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="8"/>
+      <c r="BK4" s="9"/>
+    </row>
+    <row r="5" spans="1:63" ht="14" customHeight="1">
       <c r="A5" s="10"/>
-      <c r="BH5" s="11"/>
-    </row>
-    <row r="6" spans="1:60" ht="14" customHeight="1">
+      <c r="BK5" s="11"/>
+    </row>
+    <row r="6" spans="1:63" ht="14" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1528,9 +1735,12 @@
       <c r="BE6" s="13"/>
       <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
-      <c r="BH6" s="14"/>
-    </row>
-    <row r="8" spans="1:60" ht="14" customHeight="1">
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="13"/>
+      <c r="BJ6" s="13"/>
+      <c r="BK6" s="14"/>
+    </row>
+    <row r="8" spans="1:63" ht="14" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
@@ -1586,29 +1796,32 @@
       <c r="AQ8" s="17"/>
       <c r="AR8" s="17"/>
       <c r="AS8" s="17"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="15" t="s">
+      <c r="AT8" s="17"/>
+      <c r="AU8" s="17"/>
+      <c r="AV8" s="17"/>
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="17"/>
-      <c r="AX8" s="15" t="s">
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="16"/>
-      <c r="BA8" s="17" t="s">
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="16"/>
+      <c r="BD8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="17"/>
-      <c r="BD8" s="17"/>
       <c r="BE8" s="17"/>
       <c r="BF8" s="17"/>
       <c r="BG8" s="17"/>
-      <c r="BH8" s="16"/>
-    </row>
-    <row r="9" spans="1:60" ht="14" customHeight="1">
+      <c r="BH8" s="17"/>
+      <c r="BI8" s="17"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="16"/>
+    </row>
+    <row r="9" spans="1:63" ht="14" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="20"/>
       <c r="C9" s="18" t="s">
@@ -1668,37 +1881,42 @@
       </c>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
-      <c r="AL9" s="18" t="s">
-        <v>27</v>
+      <c r="AL9" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="20"/>
+      <c r="AU9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AS9" s="20"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="18"/>
       <c r="AV9" s="20"/>
-      <c r="AW9" s="20"/>
+      <c r="AW9" s="19"/>
       <c r="AX9" s="18"/>
       <c r="AY9" s="20"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="20"/>
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="18"/>
       <c r="BB9" s="20"/>
-      <c r="BC9" s="20"/>
+      <c r="BC9" s="19"/>
       <c r="BD9" s="20"/>
       <c r="BE9" s="20"/>
       <c r="BF9" s="20"/>
       <c r="BG9" s="20"/>
-      <c r="BH9" s="19"/>
-    </row>
-    <row r="10" spans="1:60" ht="14" customHeight="1">
+      <c r="BH9" s="20"/>
+      <c r="BI9" s="20"/>
+      <c r="BJ9" s="20"/>
+      <c r="BK9" s="19"/>
+    </row>
+    <row r="10" spans="1:63" ht="14" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1756,39 +1974,42 @@
       </c>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5"/>
-      <c r="AL10" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
       <c r="AN10" s="4"/>
-      <c r="AO10" s="3"/>
+      <c r="AO10" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AP10" s="4"/>
-      <c r="AQ10" s="5"/>
+      <c r="AQ10" s="4"/>
       <c r="AR10" s="3"/>
       <c r="AS10" s="4"/>
       <c r="AT10" s="5"/>
-      <c r="AU10" s="4" t="s">
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="4"/>
+      <c r="AW10" s="5"/>
+      <c r="AX10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AV10" s="4"/>
-      <c r="AW10" s="4"/>
-      <c r="AX10" s="3" t="s">
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="5"/>
-      <c r="BA10" s="4" t="s">
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="5"/>
+      <c r="BD10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="BB10" s="4"/>
-      <c r="BC10" s="4"/>
-      <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
-      <c r="BH10" s="5"/>
-    </row>
-    <row r="11" spans="1:60" ht="14" customHeight="1">
+      <c r="BH10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="5"/>
+    </row>
+    <row r="11" spans="1:63" ht="14" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -1844,37 +2065,40 @@
       </c>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5"/>
-      <c r="AL11" s="3"/>
+      <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="4"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="4"/>
-      <c r="AQ11" s="5"/>
+      <c r="AQ11" s="4"/>
       <c r="AR11" s="3"/>
       <c r="AS11" s="4"/>
       <c r="AT11" s="5"/>
-      <c r="AU11" s="4" t="s">
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="4"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AV11" s="4"/>
-      <c r="AW11" s="4"/>
-      <c r="AX11" s="3" t="s">
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="5"/>
-      <c r="BA11" s="4" t="s">
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="5"/>
+      <c r="BD11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="4"/>
-      <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
-      <c r="BH11" s="5"/>
-    </row>
-    <row r="12" spans="1:60" ht="14" customHeight="1">
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="5"/>
+    </row>
+    <row r="12" spans="1:63" ht="14" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1928,35 +2152,38 @@
       </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="3"/>
+      <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="4"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="5"/>
+      <c r="AQ12" s="4"/>
       <c r="AR12" s="3"/>
       <c r="AS12" s="4"/>
       <c r="AT12" s="5"/>
-      <c r="AU12" s="4" t="s">
+      <c r="AU12" s="3"/>
+      <c r="AV12" s="4"/>
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AV12" s="4"/>
-      <c r="AW12" s="4"/>
-      <c r="AX12" s="3" t="s">
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AY12" s="4"/>
-      <c r="AZ12" s="5"/>
-      <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
-      <c r="BC12" s="4"/>
+      <c r="BC12" s="5"/>
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
-      <c r="BH12" s="5"/>
-    </row>
-    <row r="13" spans="1:60" ht="14" customHeight="1">
+      <c r="BH12" s="4"/>
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="5"/>
+    </row>
+    <row r="13" spans="1:63" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -2002,33 +2229,36 @@
       <c r="AI13" s="3"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5"/>
-      <c r="AL13" s="3"/>
+      <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="4"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="4"/>
-      <c r="AQ13" s="5"/>
+      <c r="AQ13" s="4"/>
       <c r="AR13" s="3"/>
       <c r="AS13" s="4"/>
       <c r="AT13" s="5"/>
-      <c r="AU13" s="4"/>
+      <c r="AU13" s="3"/>
       <c r="AV13" s="4"/>
-      <c r="AW13" s="4"/>
-      <c r="AX13" s="3"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="4"/>
       <c r="AY13" s="4"/>
-      <c r="AZ13" s="5"/>
-      <c r="BA13" s="4" t="s">
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="3"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="5"/>
+      <c r="BD13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BB13" s="4"/>
-      <c r="BC13" s="4"/>
-      <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
-      <c r="BH13" s="5"/>
-    </row>
-    <row r="14" spans="1:60" ht="14" customHeight="1">
+      <c r="BH13" s="4"/>
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="5"/>
+    </row>
+    <row r="14" spans="1:63" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -2074,31 +2304,34 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5"/>
-      <c r="AL14" s="3"/>
+      <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="4"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="4"/>
-      <c r="AQ14" s="5"/>
+      <c r="AQ14" s="4"/>
       <c r="AR14" s="3"/>
       <c r="AS14" s="4"/>
       <c r="AT14" s="5"/>
-      <c r="AU14" s="4"/>
+      <c r="AU14" s="3"/>
       <c r="AV14" s="4"/>
-      <c r="AW14" s="4"/>
-      <c r="AX14" s="3"/>
+      <c r="AW14" s="5"/>
+      <c r="AX14" s="4"/>
       <c r="AY14" s="4"/>
-      <c r="AZ14" s="5"/>
-      <c r="BA14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="3"/>
       <c r="BB14" s="4"/>
-      <c r="BC14" s="4"/>
+      <c r="BC14" s="5"/>
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
-      <c r="BH14" s="5"/>
-    </row>
-    <row r="15" spans="1:60" ht="14" customHeight="1">
+      <c r="BH14" s="4"/>
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="5"/>
+    </row>
+    <row r="15" spans="1:63" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -2144,31 +2377,34 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5"/>
-      <c r="AL15" s="3"/>
+      <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="4"/>
-      <c r="AQ15" s="5"/>
+      <c r="AQ15" s="4"/>
       <c r="AR15" s="3"/>
       <c r="AS15" s="4"/>
       <c r="AT15" s="5"/>
-      <c r="AU15" s="4"/>
+      <c r="AU15" s="3"/>
       <c r="AV15" s="4"/>
-      <c r="AW15" s="4"/>
-      <c r="AX15" s="3"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="4"/>
       <c r="AY15" s="4"/>
-      <c r="AZ15" s="5"/>
-      <c r="BA15" s="4"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="3"/>
       <c r="BB15" s="4"/>
-      <c r="BC15" s="4"/>
+      <c r="BC15" s="5"/>
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
-      <c r="BH15" s="5"/>
-    </row>
-    <row r="16" spans="1:60" ht="14" customHeight="1">
+      <c r="BH15" s="4"/>
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="4"/>
+      <c r="BK15" s="5"/>
+    </row>
+    <row r="16" spans="1:63" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -2216,35 +2452,38 @@
       </c>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
-      <c r="AL16" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
-      <c r="AO16" s="3"/>
+      <c r="AO16" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="AP16" s="4"/>
-      <c r="AQ16" s="5"/>
+      <c r="AQ16" s="4"/>
       <c r="AR16" s="3"/>
       <c r="AS16" s="4"/>
       <c r="AT16" s="5"/>
-      <c r="AU16" s="4"/>
+      <c r="AU16" s="3"/>
       <c r="AV16" s="4"/>
-      <c r="AW16" s="4"/>
-      <c r="AX16" s="3"/>
+      <c r="AW16" s="5"/>
+      <c r="AX16" s="4"/>
       <c r="AY16" s="4"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="4" t="s">
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="3"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="5"/>
+      <c r="BD16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB16" s="4"/>
-      <c r="BC16" s="4"/>
-      <c r="BD16" s="4"/>
       <c r="BE16" s="4"/>
       <c r="BF16" s="4"/>
       <c r="BG16" s="4"/>
-      <c r="BH16" s="5"/>
-    </row>
-    <row r="17" spans="1:60" ht="14" customHeight="1">
+      <c r="BH16" s="4"/>
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="4"/>
+      <c r="BK16" s="5"/>
+    </row>
+    <row r="17" spans="1:63" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -2290,35 +2529,38 @@
       </c>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
-      <c r="AL17" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
-      <c r="AO17" s="3"/>
+      <c r="AO17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="AP17" s="4"/>
-      <c r="AQ17" s="5"/>
+      <c r="AQ17" s="4"/>
       <c r="AR17" s="3"/>
       <c r="AS17" s="4"/>
       <c r="AT17" s="5"/>
-      <c r="AU17" s="4"/>
+      <c r="AU17" s="3"/>
       <c r="AV17" s="4"/>
-      <c r="AW17" s="4"/>
-      <c r="AX17" s="3"/>
+      <c r="AW17" s="5"/>
+      <c r="AX17" s="4"/>
       <c r="AY17" s="4"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="4" t="s">
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="3"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="5"/>
+      <c r="BD17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB17" s="4"/>
-      <c r="BC17" s="4"/>
-      <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
-      <c r="BH17" s="5"/>
-    </row>
-    <row r="18" spans="1:60" ht="14" customHeight="1">
+      <c r="BH17" s="4"/>
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="4"/>
+      <c r="BK17" s="5"/>
+    </row>
+    <row r="18" spans="1:63" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -2362,33 +2604,36 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5"/>
-      <c r="AL18" s="3"/>
+      <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="4"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="4"/>
-      <c r="AQ18" s="5"/>
+      <c r="AQ18" s="4"/>
       <c r="AR18" s="3"/>
       <c r="AS18" s="4"/>
       <c r="AT18" s="5"/>
-      <c r="AU18" s="4"/>
+      <c r="AU18" s="3"/>
       <c r="AV18" s="4"/>
-      <c r="AW18" s="4"/>
-      <c r="AX18" s="3"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="4"/>
       <c r="AY18" s="4"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="4" t="s">
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="3"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="5"/>
+      <c r="BD18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB18" s="4"/>
-      <c r="BC18" s="4"/>
-      <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
-      <c r="BH18" s="5"/>
-    </row>
-    <row r="19" spans="1:60" ht="14" customHeight="1">
+      <c r="BH18" s="4"/>
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="5"/>
+    </row>
+    <row r="19" spans="1:63" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -2432,33 +2677,36 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5"/>
-      <c r="AL19" s="3"/>
+      <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="4"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="4"/>
-      <c r="AQ19" s="5"/>
+      <c r="AQ19" s="4"/>
       <c r="AR19" s="3"/>
       <c r="AS19" s="4"/>
       <c r="AT19" s="5"/>
-      <c r="AU19" s="4"/>
+      <c r="AU19" s="3"/>
       <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-      <c r="AX19" s="3"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="4"/>
       <c r="AY19" s="4"/>
-      <c r="AZ19" s="5"/>
-      <c r="BA19" s="4" t="s">
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="5"/>
+      <c r="BD19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB19" s="4"/>
-      <c r="BC19" s="4"/>
-      <c r="BD19" s="4"/>
       <c r="BE19" s="4"/>
       <c r="BF19" s="4"/>
       <c r="BG19" s="4"/>
-      <c r="BH19" s="5"/>
-    </row>
-    <row r="20" spans="1:60" ht="14" customHeight="1">
+      <c r="BH19" s="4"/>
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="5"/>
+    </row>
+    <row r="20" spans="1:63" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -2502,33 +2750,36 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5"/>
-      <c r="AL20" s="3"/>
+      <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="4"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="4"/>
-      <c r="AQ20" s="5"/>
+      <c r="AQ20" s="4"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="4"/>
       <c r="AT20" s="5"/>
-      <c r="AU20" s="4"/>
+      <c r="AU20" s="3"/>
       <c r="AV20" s="4"/>
-      <c r="AW20" s="4"/>
-      <c r="AX20" s="3"/>
+      <c r="AW20" s="5"/>
+      <c r="AX20" s="4"/>
       <c r="AY20" s="4"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="4" t="s">
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="3"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="5"/>
+      <c r="BD20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB20" s="4"/>
-      <c r="BC20" s="4"/>
-      <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
-      <c r="BH20" s="5"/>
-    </row>
-    <row r="21" spans="1:60" ht="14" customHeight="1">
+      <c r="BH20" s="4"/>
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="5"/>
+    </row>
+    <row r="21" spans="1:63" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
@@ -2572,33 +2823,36 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5"/>
-      <c r="AL21" s="3"/>
+      <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="4"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="4"/>
-      <c r="AQ21" s="5"/>
+      <c r="AQ21" s="4"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="4"/>
       <c r="AT21" s="5"/>
-      <c r="AU21" s="4"/>
+      <c r="AU21" s="3"/>
       <c r="AV21" s="4"/>
-      <c r="AW21" s="4"/>
-      <c r="AX21" s="3"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="4"/>
       <c r="AY21" s="4"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="4" t="s">
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="3"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="5"/>
+      <c r="BD21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB21" s="4"/>
-      <c r="BC21" s="4"/>
-      <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
-      <c r="BH21" s="5"/>
-    </row>
-    <row r="22" spans="1:60" ht="14" customHeight="1">
+      <c r="BH21" s="4"/>
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="5"/>
+    </row>
+    <row r="22" spans="1:63" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -2646,33 +2900,36 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5"/>
-      <c r="AL22" s="3"/>
+      <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="4"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="4"/>
-      <c r="AQ22" s="5"/>
+      <c r="AQ22" s="4"/>
       <c r="AR22" s="3"/>
       <c r="AS22" s="4"/>
       <c r="AT22" s="5"/>
-      <c r="AU22" s="4"/>
+      <c r="AU22" s="3"/>
       <c r="AV22" s="4"/>
-      <c r="AW22" s="4"/>
-      <c r="AX22" s="3"/>
+      <c r="AW22" s="5"/>
+      <c r="AX22" s="4"/>
       <c r="AY22" s="4"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="4" t="s">
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="3"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="5"/>
+      <c r="BD22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BB22" s="4"/>
-      <c r="BC22" s="4"/>
-      <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
-      <c r="BH22" s="5"/>
-    </row>
-    <row r="23" spans="1:60" ht="14" customHeight="1">
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="5"/>
+    </row>
+    <row r="23" spans="1:63" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -2720,33 +2977,36 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5"/>
-      <c r="AL23" s="3"/>
+      <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
-      <c r="AO23" s="24"/>
-      <c r="AP23" s="21"/>
-      <c r="AQ23" s="5"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
       <c r="AR23" s="24"/>
       <c r="AS23" s="21"/>
       <c r="AT23" s="5"/>
-      <c r="AU23" s="4"/>
-      <c r="AV23" s="4"/>
-      <c r="AW23" s="4"/>
-      <c r="AX23" s="3"/>
+      <c r="AU23" s="24"/>
+      <c r="AV23" s="21"/>
+      <c r="AW23" s="5"/>
+      <c r="AX23" s="4"/>
       <c r="AY23" s="4"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="4" t="s">
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="3"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="5"/>
+      <c r="BD23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB23" s="4"/>
-      <c r="BC23" s="4"/>
-      <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
-      <c r="BH23" s="5"/>
-    </row>
-    <row r="24" spans="1:60" ht="14" customHeight="1">
+      <c r="BH23" s="4"/>
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="5"/>
+    </row>
+    <row r="24" spans="1:63" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -2794,33 +3054,36 @@
       <c r="AI24" s="3"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5"/>
-      <c r="AL24" s="3"/>
+      <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="4"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="4"/>
-      <c r="AQ24" s="5"/>
+      <c r="AQ24" s="4"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="4"/>
       <c r="AT24" s="5"/>
-      <c r="AU24" s="4"/>
+      <c r="AU24" s="3"/>
       <c r="AV24" s="4"/>
-      <c r="AW24" s="4"/>
-      <c r="AX24" s="3"/>
+      <c r="AW24" s="5"/>
+      <c r="AX24" s="4"/>
       <c r="AY24" s="4"/>
-      <c r="AZ24" s="5"/>
-      <c r="BA24" s="4" t="s">
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="3"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="5"/>
+      <c r="BD24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB24" s="4"/>
-      <c r="BC24" s="4"/>
-      <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
-      <c r="BH24" s="5"/>
-    </row>
-    <row r="25" spans="1:60" ht="14" customHeight="1">
+      <c r="BH24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="5"/>
+    </row>
+    <row r="25" spans="1:63" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -2868,33 +3131,36 @@
       <c r="AI25" s="3"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5"/>
-      <c r="AL25" s="3"/>
+      <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
       <c r="AN25" s="4"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="4"/>
-      <c r="AQ25" s="5"/>
+      <c r="AQ25" s="4"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="4"/>
       <c r="AT25" s="5"/>
-      <c r="AU25" s="4"/>
+      <c r="AU25" s="3"/>
       <c r="AV25" s="4"/>
-      <c r="AW25" s="4"/>
-      <c r="AX25" s="3"/>
+      <c r="AW25" s="5"/>
+      <c r="AX25" s="4"/>
       <c r="AY25" s="4"/>
-      <c r="AZ25" s="5"/>
-      <c r="BA25" s="4" t="s">
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="5"/>
+      <c r="BD25" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB25" s="4"/>
-      <c r="BC25" s="4"/>
-      <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
-      <c r="BH25" s="5"/>
-    </row>
-    <row r="26" spans="1:60" ht="14" customHeight="1">
+      <c r="BH25" s="4"/>
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="5"/>
+    </row>
+    <row r="26" spans="1:63" ht="14" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>78</v>
       </c>
@@ -2942,33 +3208,36 @@
       <c r="AI26" s="3"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5"/>
-      <c r="AL26" s="3"/>
+      <c r="AL26" s="4"/>
       <c r="AM26" s="4"/>
       <c r="AN26" s="4"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="4"/>
-      <c r="AQ26" s="5"/>
+      <c r="AQ26" s="4"/>
       <c r="AR26" s="3"/>
       <c r="AS26" s="4"/>
       <c r="AT26" s="5"/>
-      <c r="AU26" s="4"/>
+      <c r="AU26" s="3"/>
       <c r="AV26" s="4"/>
-      <c r="AW26" s="4"/>
-      <c r="AX26" s="3"/>
+      <c r="AW26" s="5"/>
+      <c r="AX26" s="4"/>
       <c r="AY26" s="4"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="4" t="s">
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="4"/>
+      <c r="BC26" s="5"/>
+      <c r="BD26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BB26" s="4"/>
-      <c r="BC26" s="4"/>
-      <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
-      <c r="BH26" s="5"/>
-    </row>
-    <row r="27" spans="1:60" ht="14" customHeight="1">
+      <c r="BH26" s="4"/>
+      <c r="BI26" s="4"/>
+      <c r="BJ26" s="4"/>
+      <c r="BK26" s="5"/>
+    </row>
+    <row r="27" spans="1:63" ht="14" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>79</v>
       </c>
@@ -3016,33 +3285,36 @@
       <c r="AI27" s="3"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5"/>
-      <c r="AL27" s="3"/>
+      <c r="AL27" s="4"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
-      <c r="AO27" s="24"/>
-      <c r="AP27" s="21"/>
-      <c r="AQ27" s="5"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="4"/>
+      <c r="AQ27" s="4"/>
       <c r="AR27" s="24"/>
       <c r="AS27" s="21"/>
       <c r="AT27" s="5"/>
-      <c r="AU27" s="4"/>
-      <c r="AV27" s="4"/>
-      <c r="AW27" s="4"/>
-      <c r="AX27" s="3"/>
+      <c r="AU27" s="24"/>
+      <c r="AV27" s="21"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="4"/>
       <c r="AY27" s="4"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="4" t="s">
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="4"/>
+      <c r="BC27" s="5"/>
+      <c r="BD27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB27" s="4"/>
-      <c r="BC27" s="4"/>
-      <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
-      <c r="BH27" s="5"/>
-    </row>
-    <row r="28" spans="1:60" ht="14" customHeight="1">
+      <c r="BH27" s="4"/>
+      <c r="BI27" s="4"/>
+      <c r="BJ27" s="4"/>
+      <c r="BK27" s="5"/>
+    </row>
+    <row r="28" spans="1:63" ht="14" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>80</v>
       </c>
@@ -3090,33 +3362,36 @@
       <c r="AI28" s="3"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5"/>
-      <c r="AL28" s="3"/>
+      <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
       <c r="AN28" s="4"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="4"/>
-      <c r="AQ28" s="5"/>
+      <c r="AQ28" s="4"/>
       <c r="AR28" s="3"/>
       <c r="AS28" s="4"/>
       <c r="AT28" s="5"/>
-      <c r="AU28" s="4"/>
+      <c r="AU28" s="3"/>
       <c r="AV28" s="4"/>
-      <c r="AW28" s="4"/>
-      <c r="AX28" s="3"/>
+      <c r="AW28" s="5"/>
+      <c r="AX28" s="4"/>
       <c r="AY28" s="4"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="4" t="s">
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="5"/>
+      <c r="BD28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB28" s="4"/>
-      <c r="BC28" s="4"/>
-      <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
-      <c r="BH28" s="5"/>
-    </row>
-    <row r="29" spans="1:60" ht="14" customHeight="1">
+      <c r="BH28" s="4"/>
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="5"/>
+    </row>
+    <row r="29" spans="1:63" ht="14" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>81</v>
       </c>
@@ -3164,33 +3439,36 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5"/>
-      <c r="AL29" s="3"/>
+      <c r="AL29" s="4"/>
       <c r="AM29" s="4"/>
       <c r="AN29" s="4"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="4"/>
-      <c r="AQ29" s="5"/>
+      <c r="AQ29" s="4"/>
       <c r="AR29" s="3"/>
       <c r="AS29" s="4"/>
       <c r="AT29" s="5"/>
-      <c r="AU29" s="4"/>
+      <c r="AU29" s="3"/>
       <c r="AV29" s="4"/>
-      <c r="AW29" s="4"/>
-      <c r="AX29" s="3"/>
+      <c r="AW29" s="5"/>
+      <c r="AX29" s="4"/>
       <c r="AY29" s="4"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="4" t="s">
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="5"/>
+      <c r="BD29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB29" s="4"/>
-      <c r="BC29" s="4"/>
-      <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
-      <c r="BH29" s="5"/>
-    </row>
-    <row r="30" spans="1:60" ht="14" customHeight="1">
+      <c r="BH29" s="4"/>
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="5"/>
+    </row>
+    <row r="30" spans="1:63" ht="14" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -3228,31 +3506,34 @@
       <c r="AI30" s="3"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5"/>
-      <c r="AL30" s="3"/>
+      <c r="AL30" s="4"/>
       <c r="AM30" s="4"/>
       <c r="AN30" s="4"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="4"/>
-      <c r="AQ30" s="5"/>
+      <c r="AQ30" s="4"/>
       <c r="AR30" s="3"/>
       <c r="AS30" s="4"/>
       <c r="AT30" s="5"/>
-      <c r="AU30" s="4"/>
+      <c r="AU30" s="3"/>
       <c r="AV30" s="4"/>
-      <c r="AW30" s="4"/>
-      <c r="AX30" s="3"/>
+      <c r="AW30" s="5"/>
+      <c r="AX30" s="4"/>
       <c r="AY30" s="4"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="3"/>
       <c r="BB30" s="4"/>
-      <c r="BC30" s="4"/>
+      <c r="BC30" s="5"/>
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
-      <c r="BH30" s="5"/>
-    </row>
-    <row r="31" spans="1:60" ht="14" customHeight="1">
+      <c r="BH30" s="4"/>
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="5"/>
+    </row>
+    <row r="31" spans="1:63" ht="14" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -3290,31 +3571,34 @@
       <c r="AI31" s="3"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5"/>
-      <c r="AL31" s="3"/>
+      <c r="AL31" s="4"/>
       <c r="AM31" s="4"/>
       <c r="AN31" s="4"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="4"/>
-      <c r="AQ31" s="5"/>
+      <c r="AQ31" s="4"/>
       <c r="AR31" s="3"/>
       <c r="AS31" s="4"/>
       <c r="AT31" s="5"/>
-      <c r="AU31" s="4"/>
+      <c r="AU31" s="3"/>
       <c r="AV31" s="4"/>
-      <c r="AW31" s="4"/>
-      <c r="AX31" s="3"/>
+      <c r="AW31" s="5"/>
+      <c r="AX31" s="4"/>
       <c r="AY31" s="4"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="3"/>
       <c r="BB31" s="4"/>
-      <c r="BC31" s="4"/>
+      <c r="BC31" s="5"/>
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
-      <c r="BH31" s="5"/>
-    </row>
-    <row r="32" spans="1:60" ht="14" customHeight="1">
+      <c r="BH31" s="4"/>
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="5"/>
+    </row>
+    <row r="32" spans="1:63" ht="14" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -3352,31 +3636,34 @@
       <c r="AI32" s="3"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="5"/>
-      <c r="AL32" s="3"/>
+      <c r="AL32" s="4"/>
       <c r="AM32" s="4"/>
       <c r="AN32" s="4"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="4"/>
-      <c r="AQ32" s="5"/>
+      <c r="AQ32" s="4"/>
       <c r="AR32" s="3"/>
       <c r="AS32" s="4"/>
       <c r="AT32" s="5"/>
-      <c r="AU32" s="4"/>
+      <c r="AU32" s="3"/>
       <c r="AV32" s="4"/>
-      <c r="AW32" s="4"/>
-      <c r="AX32" s="3"/>
+      <c r="AW32" s="5"/>
+      <c r="AX32" s="4"/>
       <c r="AY32" s="4"/>
-      <c r="AZ32" s="5"/>
-      <c r="BA32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="3"/>
       <c r="BB32" s="4"/>
-      <c r="BC32" s="4"/>
+      <c r="BC32" s="5"/>
       <c r="BD32" s="4"/>
       <c r="BE32" s="4"/>
       <c r="BF32" s="4"/>
       <c r="BG32" s="4"/>
-      <c r="BH32" s="5"/>
-    </row>
-    <row r="33" spans="1:60" ht="14" customHeight="1">
+      <c r="BH32" s="4"/>
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="5"/>
+    </row>
+    <row r="33" spans="1:63" ht="14" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -3414,31 +3701,34 @@
       <c r="AI33" s="3"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="5"/>
-      <c r="AL33" s="3"/>
+      <c r="AL33" s="4"/>
       <c r="AM33" s="4"/>
       <c r="AN33" s="4"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="4"/>
-      <c r="AQ33" s="5"/>
+      <c r="AQ33" s="4"/>
       <c r="AR33" s="3"/>
       <c r="AS33" s="4"/>
       <c r="AT33" s="5"/>
-      <c r="AU33" s="4"/>
+      <c r="AU33" s="3"/>
       <c r="AV33" s="4"/>
-      <c r="AW33" s="4"/>
-      <c r="AX33" s="3"/>
+      <c r="AW33" s="5"/>
+      <c r="AX33" s="4"/>
       <c r="AY33" s="4"/>
-      <c r="AZ33" s="5"/>
-      <c r="BA33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="3"/>
       <c r="BB33" s="4"/>
-      <c r="BC33" s="4"/>
+      <c r="BC33" s="5"/>
       <c r="BD33" s="4"/>
       <c r="BE33" s="4"/>
       <c r="BF33" s="4"/>
       <c r="BG33" s="4"/>
-      <c r="BH33" s="5"/>
-    </row>
-    <row r="34" spans="1:60" ht="14" customHeight="1">
+      <c r="BH33" s="4"/>
+      <c r="BI33" s="4"/>
+      <c r="BJ33" s="4"/>
+      <c r="BK33" s="5"/>
+    </row>
+    <row r="34" spans="1:63" ht="14" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -3476,31 +3766,34 @@
       <c r="AI34" s="3"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5"/>
-      <c r="AL34" s="3"/>
+      <c r="AL34" s="4"/>
       <c r="AM34" s="4"/>
       <c r="AN34" s="4"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="4"/>
-      <c r="AQ34" s="5"/>
+      <c r="AQ34" s="4"/>
       <c r="AR34" s="3"/>
       <c r="AS34" s="4"/>
       <c r="AT34" s="5"/>
-      <c r="AU34" s="4"/>
+      <c r="AU34" s="3"/>
       <c r="AV34" s="4"/>
-      <c r="AW34" s="4"/>
-      <c r="AX34" s="3"/>
+      <c r="AW34" s="5"/>
+      <c r="AX34" s="4"/>
       <c r="AY34" s="4"/>
-      <c r="AZ34" s="5"/>
-      <c r="BA34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="3"/>
       <c r="BB34" s="4"/>
-      <c r="BC34" s="4"/>
+      <c r="BC34" s="5"/>
       <c r="BD34" s="4"/>
       <c r="BE34" s="4"/>
       <c r="BF34" s="4"/>
       <c r="BG34" s="4"/>
-      <c r="BH34" s="5"/>
-    </row>
-    <row r="35" spans="1:60" ht="14" customHeight="1">
+      <c r="BH34" s="4"/>
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="5"/>
+    </row>
+    <row r="35" spans="1:63" ht="14" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -3538,31 +3831,34 @@
       <c r="AI35" s="3"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="5"/>
-      <c r="AL35" s="3"/>
+      <c r="AL35" s="4"/>
       <c r="AM35" s="4"/>
       <c r="AN35" s="4"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="4"/>
-      <c r="AQ35" s="5"/>
+      <c r="AQ35" s="4"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="4"/>
       <c r="AT35" s="5"/>
-      <c r="AU35" s="4"/>
+      <c r="AU35" s="3"/>
       <c r="AV35" s="4"/>
-      <c r="AW35" s="4"/>
-      <c r="AX35" s="3"/>
+      <c r="AW35" s="5"/>
+      <c r="AX35" s="4"/>
       <c r="AY35" s="4"/>
-      <c r="AZ35" s="5"/>
-      <c r="BA35" s="4"/>
+      <c r="AZ35" s="4"/>
+      <c r="BA35" s="3"/>
       <c r="BB35" s="4"/>
-      <c r="BC35" s="4"/>
+      <c r="BC35" s="5"/>
       <c r="BD35" s="4"/>
       <c r="BE35" s="4"/>
       <c r="BF35" s="4"/>
       <c r="BG35" s="4"/>
-      <c r="BH35" s="5"/>
-    </row>
-    <row r="36" spans="1:60" ht="14" customHeight="1">
+      <c r="BH35" s="4"/>
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="5"/>
+    </row>
+    <row r="36" spans="1:63" ht="14" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -3600,31 +3896,34 @@
       <c r="AI36" s="3"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="5"/>
-      <c r="AL36" s="3"/>
+      <c r="AL36" s="4"/>
       <c r="AM36" s="4"/>
       <c r="AN36" s="4"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="4"/>
-      <c r="AQ36" s="5"/>
+      <c r="AQ36" s="4"/>
       <c r="AR36" s="3"/>
       <c r="AS36" s="4"/>
       <c r="AT36" s="5"/>
-      <c r="AU36" s="4"/>
+      <c r="AU36" s="3"/>
       <c r="AV36" s="4"/>
-      <c r="AW36" s="4"/>
-      <c r="AX36" s="3"/>
+      <c r="AW36" s="5"/>
+      <c r="AX36" s="4"/>
       <c r="AY36" s="4"/>
-      <c r="AZ36" s="5"/>
-      <c r="BA36" s="4"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="3"/>
       <c r="BB36" s="4"/>
-      <c r="BC36" s="4"/>
+      <c r="BC36" s="5"/>
       <c r="BD36" s="4"/>
       <c r="BE36" s="4"/>
       <c r="BF36" s="4"/>
       <c r="BG36" s="4"/>
-      <c r="BH36" s="5"/>
-    </row>
-    <row r="37" spans="1:60" ht="14" customHeight="1">
+      <c r="BH36" s="4"/>
+      <c r="BI36" s="4"/>
+      <c r="BJ36" s="4"/>
+      <c r="BK36" s="5"/>
+    </row>
+    <row r="37" spans="1:63" ht="14" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -3662,31 +3961,34 @@
       <c r="AI37" s="3"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="5"/>
-      <c r="AL37" s="3"/>
+      <c r="AL37" s="4"/>
       <c r="AM37" s="4"/>
       <c r="AN37" s="4"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="4"/>
-      <c r="AQ37" s="5"/>
+      <c r="AQ37" s="4"/>
       <c r="AR37" s="3"/>
       <c r="AS37" s="4"/>
       <c r="AT37" s="5"/>
-      <c r="AU37" s="4"/>
+      <c r="AU37" s="3"/>
       <c r="AV37" s="4"/>
-      <c r="AW37" s="4"/>
-      <c r="AX37" s="3"/>
+      <c r="AW37" s="5"/>
+      <c r="AX37" s="4"/>
       <c r="AY37" s="4"/>
-      <c r="AZ37" s="5"/>
-      <c r="BA37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="3"/>
       <c r="BB37" s="4"/>
-      <c r="BC37" s="4"/>
+      <c r="BC37" s="5"/>
       <c r="BD37" s="4"/>
       <c r="BE37" s="4"/>
       <c r="BF37" s="4"/>
       <c r="BG37" s="4"/>
-      <c r="BH37" s="5"/>
-    </row>
-    <row r="38" spans="1:60" ht="14" customHeight="1">
+      <c r="BH37" s="4"/>
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="5"/>
+    </row>
+    <row r="38" spans="1:63" ht="14" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -3724,31 +4026,34 @@
       <c r="AI38" s="3"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="5"/>
-      <c r="AL38" s="3"/>
+      <c r="AL38" s="4"/>
       <c r="AM38" s="4"/>
       <c r="AN38" s="4"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="4"/>
-      <c r="AQ38" s="5"/>
+      <c r="AQ38" s="4"/>
       <c r="AR38" s="3"/>
       <c r="AS38" s="4"/>
       <c r="AT38" s="5"/>
-      <c r="AU38" s="4"/>
+      <c r="AU38" s="3"/>
       <c r="AV38" s="4"/>
-      <c r="AW38" s="4"/>
-      <c r="AX38" s="3"/>
+      <c r="AW38" s="5"/>
+      <c r="AX38" s="4"/>
       <c r="AY38" s="4"/>
-      <c r="AZ38" s="5"/>
-      <c r="BA38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="3"/>
       <c r="BB38" s="4"/>
-      <c r="BC38" s="4"/>
+      <c r="BC38" s="5"/>
       <c r="BD38" s="4"/>
       <c r="BE38" s="4"/>
       <c r="BF38" s="4"/>
       <c r="BG38" s="4"/>
-      <c r="BH38" s="5"/>
-    </row>
-    <row r="39" spans="1:60" ht="14" customHeight="1">
+      <c r="BH38" s="4"/>
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="5"/>
+    </row>
+    <row r="39" spans="1:63" ht="14" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -3786,31 +4091,34 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="5"/>
-      <c r="AL39" s="3"/>
+      <c r="AL39" s="4"/>
       <c r="AM39" s="4"/>
       <c r="AN39" s="4"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="4"/>
-      <c r="AQ39" s="5"/>
+      <c r="AQ39" s="4"/>
       <c r="AR39" s="3"/>
       <c r="AS39" s="4"/>
       <c r="AT39" s="5"/>
-      <c r="AU39" s="4"/>
+      <c r="AU39" s="3"/>
       <c r="AV39" s="4"/>
-      <c r="AW39" s="4"/>
-      <c r="AX39" s="3"/>
+      <c r="AW39" s="5"/>
+      <c r="AX39" s="4"/>
       <c r="AY39" s="4"/>
-      <c r="AZ39" s="5"/>
-      <c r="BA39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="3"/>
       <c r="BB39" s="4"/>
-      <c r="BC39" s="4"/>
+      <c r="BC39" s="5"/>
       <c r="BD39" s="4"/>
       <c r="BE39" s="4"/>
       <c r="BF39" s="4"/>
       <c r="BG39" s="4"/>
-      <c r="BH39" s="5"/>
-    </row>
-    <row r="40" spans="1:60" ht="14" customHeight="1">
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="5"/>
+    </row>
+    <row r="40" spans="1:63" ht="14" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -3848,31 +4156,34 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="5"/>
-      <c r="AL40" s="3"/>
+      <c r="AL40" s="4"/>
       <c r="AM40" s="4"/>
       <c r="AN40" s="4"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="4"/>
-      <c r="AQ40" s="5"/>
+      <c r="AQ40" s="4"/>
       <c r="AR40" s="3"/>
       <c r="AS40" s="4"/>
       <c r="AT40" s="5"/>
-      <c r="AU40" s="4"/>
+      <c r="AU40" s="3"/>
       <c r="AV40" s="4"/>
-      <c r="AW40" s="4"/>
-      <c r="AX40" s="3"/>
+      <c r="AW40" s="5"/>
+      <c r="AX40" s="4"/>
       <c r="AY40" s="4"/>
-      <c r="AZ40" s="5"/>
-      <c r="BA40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="3"/>
       <c r="BB40" s="4"/>
-      <c r="BC40" s="4"/>
+      <c r="BC40" s="5"/>
       <c r="BD40" s="4"/>
       <c r="BE40" s="4"/>
       <c r="BF40" s="4"/>
       <c r="BG40" s="4"/>
-      <c r="BH40" s="5"/>
-    </row>
-    <row r="41" spans="1:60" ht="14" customHeight="1">
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="5"/>
+    </row>
+    <row r="41" spans="1:63" ht="14" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
@@ -3910,31 +4221,34 @@
       <c r="AI41" s="3"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="5"/>
-      <c r="AL41" s="3"/>
+      <c r="AL41" s="4"/>
       <c r="AM41" s="4"/>
       <c r="AN41" s="4"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="4"/>
-      <c r="AQ41" s="5"/>
+      <c r="AQ41" s="4"/>
       <c r="AR41" s="3"/>
       <c r="AS41" s="4"/>
       <c r="AT41" s="5"/>
-      <c r="AU41" s="4"/>
+      <c r="AU41" s="3"/>
       <c r="AV41" s="4"/>
-      <c r="AW41" s="4"/>
-      <c r="AX41" s="3"/>
+      <c r="AW41" s="5"/>
+      <c r="AX41" s="4"/>
       <c r="AY41" s="4"/>
-      <c r="AZ41" s="5"/>
-      <c r="BA41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="3"/>
       <c r="BB41" s="4"/>
-      <c r="BC41" s="4"/>
+      <c r="BC41" s="5"/>
       <c r="BD41" s="4"/>
       <c r="BE41" s="4"/>
       <c r="BF41" s="4"/>
       <c r="BG41" s="4"/>
-      <c r="BH41" s="5"/>
-    </row>
-    <row r="42" spans="1:60" ht="14" customHeight="1">
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="5"/>
+    </row>
+    <row r="42" spans="1:63" ht="14" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
@@ -3972,31 +4286,34 @@
       <c r="AI42" s="3"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="5"/>
-      <c r="AL42" s="3"/>
+      <c r="AL42" s="4"/>
       <c r="AM42" s="4"/>
       <c r="AN42" s="4"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="4"/>
-      <c r="AQ42" s="5"/>
+      <c r="AQ42" s="4"/>
       <c r="AR42" s="3"/>
       <c r="AS42" s="4"/>
       <c r="AT42" s="5"/>
-      <c r="AU42" s="4"/>
+      <c r="AU42" s="3"/>
       <c r="AV42" s="4"/>
-      <c r="AW42" s="4"/>
-      <c r="AX42" s="3"/>
+      <c r="AW42" s="5"/>
+      <c r="AX42" s="4"/>
       <c r="AY42" s="4"/>
-      <c r="AZ42" s="5"/>
-      <c r="BA42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="3"/>
       <c r="BB42" s="4"/>
-      <c r="BC42" s="4"/>
+      <c r="BC42" s="5"/>
       <c r="BD42" s="4"/>
       <c r="BE42" s="4"/>
       <c r="BF42" s="4"/>
       <c r="BG42" s="4"/>
-      <c r="BH42" s="5"/>
-    </row>
-    <row r="43" spans="1:60" ht="14" customHeight="1">
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="5"/>
+    </row>
+    <row r="43" spans="1:63" ht="14" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
@@ -4034,31 +4351,34 @@
       <c r="AI43" s="3"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="5"/>
-      <c r="AL43" s="3"/>
+      <c r="AL43" s="4"/>
       <c r="AM43" s="4"/>
       <c r="AN43" s="4"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="4"/>
-      <c r="AQ43" s="5"/>
+      <c r="AQ43" s="4"/>
       <c r="AR43" s="3"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="5"/>
-      <c r="AU43" s="4"/>
+      <c r="AU43" s="3"/>
       <c r="AV43" s="4"/>
-      <c r="AW43" s="4"/>
-      <c r="AX43" s="3"/>
+      <c r="AW43" s="5"/>
+      <c r="AX43" s="4"/>
       <c r="AY43" s="4"/>
-      <c r="AZ43" s="5"/>
-      <c r="BA43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="3"/>
       <c r="BB43" s="4"/>
-      <c r="BC43" s="4"/>
+      <c r="BC43" s="5"/>
       <c r="BD43" s="4"/>
       <c r="BE43" s="4"/>
       <c r="BF43" s="4"/>
       <c r="BG43" s="4"/>
-      <c r="BH43" s="5"/>
-    </row>
-    <row r="44" spans="1:60" ht="14" customHeight="1">
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="5"/>
+    </row>
+    <row r="44" spans="1:63" ht="14" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
@@ -4096,31 +4416,34 @@
       <c r="AI44" s="3"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="5"/>
-      <c r="AL44" s="3"/>
+      <c r="AL44" s="4"/>
       <c r="AM44" s="4"/>
       <c r="AN44" s="4"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="4"/>
-      <c r="AQ44" s="5"/>
+      <c r="AQ44" s="4"/>
       <c r="AR44" s="3"/>
       <c r="AS44" s="4"/>
       <c r="AT44" s="5"/>
-      <c r="AU44" s="4"/>
+      <c r="AU44" s="3"/>
       <c r="AV44" s="4"/>
-      <c r="AW44" s="4"/>
-      <c r="AX44" s="3"/>
+      <c r="AW44" s="5"/>
+      <c r="AX44" s="4"/>
       <c r="AY44" s="4"/>
-      <c r="AZ44" s="5"/>
-      <c r="BA44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="3"/>
       <c r="BB44" s="4"/>
-      <c r="BC44" s="4"/>
+      <c r="BC44" s="5"/>
       <c r="BD44" s="4"/>
       <c r="BE44" s="4"/>
       <c r="BF44" s="4"/>
       <c r="BG44" s="4"/>
-      <c r="BH44" s="5"/>
-    </row>
-    <row r="45" spans="1:60" ht="14" customHeight="1">
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="5"/>
+    </row>
+    <row r="45" spans="1:63" ht="14" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="3"/>
@@ -4158,35 +4481,38 @@
       <c r="AI45" s="3"/>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="5"/>
-      <c r="AL45" s="3"/>
+      <c r="AL45" s="4"/>
       <c r="AM45" s="4"/>
       <c r="AN45" s="4"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="4"/>
-      <c r="AQ45" s="5"/>
+      <c r="AQ45" s="4"/>
       <c r="AR45" s="3"/>
       <c r="AS45" s="4"/>
       <c r="AT45" s="5"/>
-      <c r="AU45" s="4"/>
+      <c r="AU45" s="3"/>
       <c r="AV45" s="4"/>
-      <c r="AW45" s="4"/>
-      <c r="AX45" s="3"/>
+      <c r="AW45" s="5"/>
+      <c r="AX45" s="4"/>
       <c r="AY45" s="4"/>
-      <c r="AZ45" s="5"/>
-      <c r="BA45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="3"/>
       <c r="BB45" s="4"/>
-      <c r="BC45" s="4"/>
+      <c r="BC45" s="5"/>
       <c r="BD45" s="4"/>
       <c r="BE45" s="4"/>
       <c r="BF45" s="4"/>
       <c r="BG45" s="4"/>
-      <c r="BH45" s="5"/>
+      <c r="BH45" s="4"/>
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
@@ -4195,11 +4521,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC770E-B4AB-1E40-97A2-7B8C2F9085B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D788243-52D9-F642-B947-0B51E952DAC6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH45"/>
+  <dimension ref="A1:BK45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -4207,7 +4533,7 @@
     <col min="31" max="16384" width="2.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="14" customHeight="1">
+    <row r="1" spans="1:63" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -4254,12 +4580,12 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -4275,9 +4601,12 @@
       <c r="BE1" s="4"/>
       <c r="BF1" s="4"/>
       <c r="BG1" s="4"/>
-      <c r="BH1" s="5"/>
-    </row>
-    <row r="2" spans="1:60" ht="14" customHeight="1">
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="5"/>
+    </row>
+    <row r="2" spans="1:63" ht="14" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -4324,10 +4653,10 @@
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="4"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="3"/>
       <c r="AS2" s="4"/>
       <c r="AT2" s="4"/>
       <c r="AU2" s="4"/>
@@ -4343,9 +4672,12 @@
       <c r="BE2" s="4"/>
       <c r="BF2" s="4"/>
       <c r="BG2" s="4"/>
-      <c r="BH2" s="5"/>
-    </row>
-    <row r="3" spans="1:60" ht="14" customHeight="1">
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="4"/>
+      <c r="BJ2" s="4"/>
+      <c r="BK2" s="5"/>
+    </row>
+    <row r="3" spans="1:63" ht="14" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -4392,10 +4724,10 @@
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="3"/>
       <c r="AS3" s="4"/>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
@@ -4411,9 +4743,12 @@
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
       <c r="BG3" s="4"/>
-      <c r="BH3" s="5"/>
-    </row>
-    <row r="4" spans="1:60" ht="14" customHeight="1">
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="5"/>
+    </row>
+    <row r="4" spans="1:63" ht="14" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -4475,13 +4810,16 @@
       <c r="BE4" s="8"/>
       <c r="BF4" s="8"/>
       <c r="BG4" s="8"/>
-      <c r="BH4" s="9"/>
-    </row>
-    <row r="5" spans="1:60" ht="14" customHeight="1">
+      <c r="BH4" s="8"/>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="8"/>
+      <c r="BK4" s="9"/>
+    </row>
+    <row r="5" spans="1:63" ht="14" customHeight="1">
       <c r="A5" s="10"/>
-      <c r="BH5" s="11"/>
-    </row>
-    <row r="6" spans="1:60" ht="14" customHeight="1">
+      <c r="BK5" s="11"/>
+    </row>
+    <row r="6" spans="1:63" ht="14" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4541,9 +4879,12 @@
       <c r="BE6" s="13"/>
       <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
-      <c r="BH6" s="14"/>
-    </row>
-    <row r="8" spans="1:60" ht="14" customHeight="1">
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="13"/>
+      <c r="BJ6" s="13"/>
+      <c r="BK6" s="14"/>
+    </row>
+    <row r="8" spans="1:63" ht="14" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
@@ -4599,29 +4940,32 @@
       <c r="AQ8" s="17"/>
       <c r="AR8" s="17"/>
       <c r="AS8" s="17"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="15" t="s">
+      <c r="AT8" s="17"/>
+      <c r="AU8" s="17"/>
+      <c r="AV8" s="17"/>
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="17"/>
-      <c r="AX8" s="15" t="s">
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="16"/>
-      <c r="BA8" s="17" t="s">
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="16"/>
+      <c r="BD8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="17"/>
-      <c r="BD8" s="17"/>
       <c r="BE8" s="17"/>
       <c r="BF8" s="17"/>
       <c r="BG8" s="17"/>
-      <c r="BH8" s="16"/>
-    </row>
-    <row r="9" spans="1:60" ht="14" customHeight="1">
+      <c r="BH8" s="17"/>
+      <c r="BI8" s="17"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="16"/>
+    </row>
+    <row r="9" spans="1:63" ht="14" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="20"/>
       <c r="C9" s="18" t="s">
@@ -4681,37 +5025,42 @@
       </c>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
-      <c r="AL9" s="18" t="s">
-        <v>27</v>
+      <c r="AL9" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
       <c r="AO9" s="18" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="20"/>
+      <c r="AU9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AS9" s="20"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="18"/>
       <c r="AV9" s="20"/>
-      <c r="AW9" s="20"/>
+      <c r="AW9" s="19"/>
       <c r="AX9" s="18"/>
       <c r="AY9" s="20"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="20"/>
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="18"/>
       <c r="BB9" s="20"/>
-      <c r="BC9" s="20"/>
+      <c r="BC9" s="19"/>
       <c r="BD9" s="20"/>
       <c r="BE9" s="20"/>
       <c r="BF9" s="20"/>
       <c r="BG9" s="20"/>
-      <c r="BH9" s="19"/>
-    </row>
-    <row r="10" spans="1:60" ht="14" customHeight="1">
+      <c r="BH9" s="20"/>
+      <c r="BI9" s="20"/>
+      <c r="BJ9" s="20"/>
+      <c r="BK9" s="19"/>
+    </row>
+    <row r="10" spans="1:63" ht="14" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -4769,39 +5118,42 @@
       </c>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5"/>
-      <c r="AL10" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
       <c r="AN10" s="4"/>
-      <c r="AO10" s="3"/>
+      <c r="AO10" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="AP10" s="4"/>
-      <c r="AQ10" s="5"/>
+      <c r="AQ10" s="4"/>
       <c r="AR10" s="3"/>
       <c r="AS10" s="4"/>
       <c r="AT10" s="5"/>
-      <c r="AU10" s="4" t="s">
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="4"/>
+      <c r="AW10" s="5"/>
+      <c r="AX10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AV10" s="4"/>
-      <c r="AW10" s="4"/>
-      <c r="AX10" s="3" t="s">
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="5"/>
-      <c r="BA10" s="4" t="s">
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="5"/>
+      <c r="BD10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="BB10" s="4"/>
-      <c r="BC10" s="4"/>
-      <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
       <c r="BF10" s="4"/>
       <c r="BG10" s="4"/>
-      <c r="BH10" s="5"/>
-    </row>
-    <row r="11" spans="1:60" ht="14" customHeight="1">
+      <c r="BH10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="5"/>
+    </row>
+    <row r="11" spans="1:63" ht="14" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -4857,37 +5209,42 @@
       </c>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5"/>
-      <c r="AL11" s="3"/>
+      <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="4"/>
-      <c r="AO11" s="3"/>
+      <c r="AO11" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="AP11" s="4"/>
-      <c r="AQ11" s="5"/>
+      <c r="AQ11" s="4"/>
       <c r="AR11" s="3"/>
       <c r="AS11" s="4"/>
       <c r="AT11" s="5"/>
-      <c r="AU11" s="4" t="s">
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="4"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AV11" s="4"/>
-      <c r="AW11" s="4"/>
-      <c r="AX11" s="3" t="s">
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="5"/>
-      <c r="BA11" s="4" t="s">
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="5"/>
+      <c r="BD11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="4"/>
-      <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
       <c r="BF11" s="4"/>
       <c r="BG11" s="4"/>
-      <c r="BH11" s="5"/>
-    </row>
-    <row r="12" spans="1:60" ht="14" customHeight="1">
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="5"/>
+    </row>
+    <row r="12" spans="1:63" ht="14" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -4941,35 +5298,38 @@
       </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="3"/>
+      <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="4"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="4"/>
-      <c r="AQ12" s="5"/>
+      <c r="AQ12" s="4"/>
       <c r="AR12" s="3"/>
       <c r="AS12" s="4"/>
       <c r="AT12" s="5"/>
-      <c r="AU12" s="4" t="s">
+      <c r="AU12" s="3"/>
+      <c r="AV12" s="4"/>
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AV12" s="4"/>
-      <c r="AW12" s="4"/>
-      <c r="AX12" s="3" t="s">
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AY12" s="4"/>
-      <c r="AZ12" s="5"/>
-      <c r="BA12" s="4"/>
       <c r="BB12" s="4"/>
-      <c r="BC12" s="4"/>
+      <c r="BC12" s="5"/>
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
       <c r="BF12" s="4"/>
       <c r="BG12" s="4"/>
-      <c r="BH12" s="5"/>
-    </row>
-    <row r="13" spans="1:60" ht="14" customHeight="1">
+      <c r="BH12" s="4"/>
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="5"/>
+    </row>
+    <row r="13" spans="1:63" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -5012,36 +5372,45 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
-      <c r="AI13" s="3"/>
+      <c r="AI13" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5"/>
-      <c r="AL13" s="3"/>
+      <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="4"/>
-      <c r="AO13" s="3"/>
+      <c r="AO13" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="AP13" s="4"/>
-      <c r="AQ13" s="5"/>
-      <c r="AR13" s="3"/>
+      <c r="AQ13" s="4"/>
+      <c r="AR13" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="AS13" s="4"/>
       <c r="AT13" s="5"/>
-      <c r="AU13" s="4"/>
+      <c r="AU13" s="3"/>
       <c r="AV13" s="4"/>
-      <c r="AW13" s="4"/>
-      <c r="AX13" s="3"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="4"/>
       <c r="AY13" s="4"/>
-      <c r="AZ13" s="5"/>
-      <c r="BA13" s="4" t="s">
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="3"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="5"/>
+      <c r="BD13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BB13" s="4"/>
-      <c r="BC13" s="4"/>
-      <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
       <c r="BG13" s="4"/>
-      <c r="BH13" s="5"/>
-    </row>
-    <row r="14" spans="1:60" ht="14" customHeight="1">
+      <c r="BH13" s="4"/>
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="5"/>
+    </row>
+    <row r="14" spans="1:63" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -5087,31 +5456,34 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5"/>
-      <c r="AL14" s="3"/>
+      <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="4"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="4"/>
-      <c r="AQ14" s="5"/>
+      <c r="AQ14" s="4"/>
       <c r="AR14" s="3"/>
       <c r="AS14" s="4"/>
       <c r="AT14" s="5"/>
-      <c r="AU14" s="4"/>
+      <c r="AU14" s="3"/>
       <c r="AV14" s="4"/>
-      <c r="AW14" s="4"/>
-      <c r="AX14" s="3"/>
+      <c r="AW14" s="5"/>
+      <c r="AX14" s="4"/>
       <c r="AY14" s="4"/>
-      <c r="AZ14" s="5"/>
-      <c r="BA14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="3"/>
       <c r="BB14" s="4"/>
-      <c r="BC14" s="4"/>
+      <c r="BC14" s="5"/>
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
       <c r="BF14" s="4"/>
       <c r="BG14" s="4"/>
-      <c r="BH14" s="5"/>
-    </row>
-    <row r="15" spans="1:60" ht="14" customHeight="1">
+      <c r="BH14" s="4"/>
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="5"/>
+    </row>
+    <row r="15" spans="1:63" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -5157,31 +5529,34 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5"/>
-      <c r="AL15" s="3"/>
+      <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="4"/>
-      <c r="AQ15" s="5"/>
+      <c r="AQ15" s="4"/>
       <c r="AR15" s="3"/>
       <c r="AS15" s="4"/>
       <c r="AT15" s="5"/>
-      <c r="AU15" s="4"/>
+      <c r="AU15" s="3"/>
       <c r="AV15" s="4"/>
-      <c r="AW15" s="4"/>
-      <c r="AX15" s="3"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="4"/>
       <c r="AY15" s="4"/>
-      <c r="AZ15" s="5"/>
-      <c r="BA15" s="4"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="3"/>
       <c r="BB15" s="4"/>
-      <c r="BC15" s="4"/>
+      <c r="BC15" s="5"/>
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
       <c r="BF15" s="4"/>
       <c r="BG15" s="4"/>
-      <c r="BH15" s="5"/>
-    </row>
-    <row r="16" spans="1:60" ht="14" customHeight="1">
+      <c r="BH15" s="4"/>
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="4"/>
+      <c r="BK15" s="5"/>
+    </row>
+    <row r="16" spans="1:63" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -5206,7 +5581,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="5"/>
       <c r="T16" s="3"/>
@@ -5224,40 +5601,39 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
-      <c r="AI16" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="AI16" s="3"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
-      <c r="AL16" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="4"/>
-      <c r="AQ16" s="5"/>
+      <c r="AQ16" s="4"/>
       <c r="AR16" s="3"/>
       <c r="AS16" s="4"/>
       <c r="AT16" s="5"/>
-      <c r="AU16" s="4"/>
+      <c r="AU16" s="3"/>
       <c r="AV16" s="4"/>
-      <c r="AW16" s="4"/>
-      <c r="AX16" s="3"/>
+      <c r="AW16" s="5"/>
+      <c r="AX16" s="4"/>
       <c r="AY16" s="4"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="4" t="s">
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="3"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="5"/>
+      <c r="BD16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB16" s="4"/>
-      <c r="BC16" s="4"/>
-      <c r="BD16" s="4"/>
       <c r="BE16" s="4"/>
       <c r="BF16" s="4"/>
       <c r="BG16" s="4"/>
-      <c r="BH16" s="5"/>
-    </row>
-    <row r="17" spans="1:60" ht="14" customHeight="1">
+      <c r="BH16" s="4"/>
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="4"/>
+      <c r="BK16" s="5"/>
+    </row>
+    <row r="17" spans="1:63" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -5280,7 +5656,9 @@
       <c r="N17" s="3"/>
       <c r="O17" s="4"/>
       <c r="P17" s="5"/>
-      <c r="Q17" s="3"/>
+      <c r="Q17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="5"/>
       <c r="T17" s="3"/>
@@ -5298,40 +5676,39 @@
       <c r="AF17" s="3"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
-      <c r="AI17" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="AI17" s="3"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
-      <c r="AL17" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="4"/>
-      <c r="AQ17" s="5"/>
+      <c r="AQ17" s="4"/>
       <c r="AR17" s="3"/>
       <c r="AS17" s="4"/>
       <c r="AT17" s="5"/>
-      <c r="AU17" s="4"/>
+      <c r="AU17" s="3"/>
       <c r="AV17" s="4"/>
-      <c r="AW17" s="4"/>
-      <c r="AX17" s="3"/>
+      <c r="AW17" s="5"/>
+      <c r="AX17" s="4"/>
       <c r="AY17" s="4"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="4" t="s">
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="3"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="5"/>
+      <c r="BD17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB17" s="4"/>
-      <c r="BC17" s="4"/>
-      <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
       <c r="BF17" s="4"/>
       <c r="BG17" s="4"/>
-      <c r="BH17" s="5"/>
-    </row>
-    <row r="18" spans="1:60" ht="14" customHeight="1">
+      <c r="BH17" s="4"/>
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="4"/>
+      <c r="BK17" s="5"/>
+    </row>
+    <row r="18" spans="1:63" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -5375,33 +5752,36 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5"/>
-      <c r="AL18" s="3"/>
+      <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="4"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="4"/>
-      <c r="AQ18" s="5"/>
+      <c r="AQ18" s="4"/>
       <c r="AR18" s="3"/>
       <c r="AS18" s="4"/>
       <c r="AT18" s="5"/>
-      <c r="AU18" s="4"/>
+      <c r="AU18" s="3"/>
       <c r="AV18" s="4"/>
-      <c r="AW18" s="4"/>
-      <c r="AX18" s="3"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="4"/>
       <c r="AY18" s="4"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="4" t="s">
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="3"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="5"/>
+      <c r="BD18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB18" s="4"/>
-      <c r="BC18" s="4"/>
-      <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
       <c r="BF18" s="4"/>
       <c r="BG18" s="4"/>
-      <c r="BH18" s="5"/>
-    </row>
-    <row r="19" spans="1:60" ht="14" customHeight="1">
+      <c r="BH18" s="4"/>
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="5"/>
+    </row>
+    <row r="19" spans="1:63" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -5445,33 +5825,36 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5"/>
-      <c r="AL19" s="3"/>
+      <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="4"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="4"/>
-      <c r="AQ19" s="5"/>
+      <c r="AQ19" s="4"/>
       <c r="AR19" s="3"/>
       <c r="AS19" s="4"/>
       <c r="AT19" s="5"/>
-      <c r="AU19" s="4"/>
+      <c r="AU19" s="3"/>
       <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-      <c r="AX19" s="3"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="4"/>
       <c r="AY19" s="4"/>
-      <c r="AZ19" s="5"/>
-      <c r="BA19" s="4" t="s">
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="5"/>
+      <c r="BD19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB19" s="4"/>
-      <c r="BC19" s="4"/>
-      <c r="BD19" s="4"/>
       <c r="BE19" s="4"/>
       <c r="BF19" s="4"/>
       <c r="BG19" s="4"/>
-      <c r="BH19" s="5"/>
-    </row>
-    <row r="20" spans="1:60" ht="14" customHeight="1">
+      <c r="BH19" s="4"/>
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="5"/>
+    </row>
+    <row r="20" spans="1:63" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -5515,33 +5898,36 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5"/>
-      <c r="AL20" s="3"/>
+      <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="4"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="4"/>
-      <c r="AQ20" s="5"/>
+      <c r="AQ20" s="4"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="4"/>
       <c r="AT20" s="5"/>
-      <c r="AU20" s="4"/>
+      <c r="AU20" s="3"/>
       <c r="AV20" s="4"/>
-      <c r="AW20" s="4"/>
-      <c r="AX20" s="3"/>
+      <c r="AW20" s="5"/>
+      <c r="AX20" s="4"/>
       <c r="AY20" s="4"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="4" t="s">
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="3"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="5"/>
+      <c r="BD20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB20" s="4"/>
-      <c r="BC20" s="4"/>
-      <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
       <c r="BF20" s="4"/>
       <c r="BG20" s="4"/>
-      <c r="BH20" s="5"/>
-    </row>
-    <row r="21" spans="1:60" ht="14" customHeight="1">
+      <c r="BH20" s="4"/>
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="5"/>
+    </row>
+    <row r="21" spans="1:63" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
@@ -5585,33 +5971,36 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5"/>
-      <c r="AL21" s="3"/>
+      <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="4"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="4"/>
-      <c r="AQ21" s="5"/>
+      <c r="AQ21" s="4"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="4"/>
       <c r="AT21" s="5"/>
-      <c r="AU21" s="4"/>
+      <c r="AU21" s="3"/>
       <c r="AV21" s="4"/>
-      <c r="AW21" s="4"/>
-      <c r="AX21" s="3"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="4"/>
       <c r="AY21" s="4"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="4" t="s">
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="3"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="5"/>
+      <c r="BD21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BB21" s="4"/>
-      <c r="BC21" s="4"/>
-      <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
       <c r="BF21" s="4"/>
       <c r="BG21" s="4"/>
-      <c r="BH21" s="5"/>
-    </row>
-    <row r="22" spans="1:60" ht="14" customHeight="1">
+      <c r="BH21" s="4"/>
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="5"/>
+    </row>
+    <row r="22" spans="1:63" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -5659,33 +6048,36 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5"/>
-      <c r="AL22" s="3"/>
+      <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="4"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="4"/>
-      <c r="AQ22" s="5"/>
+      <c r="AQ22" s="4"/>
       <c r="AR22" s="3"/>
       <c r="AS22" s="4"/>
       <c r="AT22" s="5"/>
-      <c r="AU22" s="4"/>
+      <c r="AU22" s="3"/>
       <c r="AV22" s="4"/>
-      <c r="AW22" s="4"/>
-      <c r="AX22" s="3"/>
+      <c r="AW22" s="5"/>
+      <c r="AX22" s="4"/>
       <c r="AY22" s="4"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="4" t="s">
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="3"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="5"/>
+      <c r="BD22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BB22" s="4"/>
-      <c r="BC22" s="4"/>
-      <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
       <c r="BF22" s="4"/>
       <c r="BG22" s="4"/>
-      <c r="BH22" s="5"/>
-    </row>
-    <row r="23" spans="1:60" ht="14" customHeight="1">
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="5"/>
+    </row>
+    <row r="23" spans="1:63" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -5733,33 +6125,36 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5"/>
-      <c r="AL23" s="3"/>
+      <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
-      <c r="AO23" s="24"/>
-      <c r="AP23" s="21"/>
-      <c r="AQ23" s="5"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
       <c r="AR23" s="24"/>
       <c r="AS23" s="21"/>
       <c r="AT23" s="5"/>
-      <c r="AU23" s="4"/>
-      <c r="AV23" s="4"/>
-      <c r="AW23" s="4"/>
-      <c r="AX23" s="3"/>
+      <c r="AU23" s="24"/>
+      <c r="AV23" s="21"/>
+      <c r="AW23" s="5"/>
+      <c r="AX23" s="4"/>
       <c r="AY23" s="4"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="4" t="s">
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="3"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="5"/>
+      <c r="BD23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB23" s="4"/>
-      <c r="BC23" s="4"/>
-      <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
       <c r="BF23" s="4"/>
       <c r="BG23" s="4"/>
-      <c r="BH23" s="5"/>
-    </row>
-    <row r="24" spans="1:60" ht="14" customHeight="1">
+      <c r="BH23" s="4"/>
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="5"/>
+    </row>
+    <row r="24" spans="1:63" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -5807,33 +6202,36 @@
       <c r="AI24" s="3"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5"/>
-      <c r="AL24" s="3"/>
+      <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="4"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="4"/>
-      <c r="AQ24" s="5"/>
+      <c r="AQ24" s="4"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="4"/>
       <c r="AT24" s="5"/>
-      <c r="AU24" s="4"/>
+      <c r="AU24" s="3"/>
       <c r="AV24" s="4"/>
-      <c r="AW24" s="4"/>
-      <c r="AX24" s="3"/>
+      <c r="AW24" s="5"/>
+      <c r="AX24" s="4"/>
       <c r="AY24" s="4"/>
-      <c r="AZ24" s="5"/>
-      <c r="BA24" s="4" t="s">
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="3"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="5"/>
+      <c r="BD24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB24" s="4"/>
-      <c r="BC24" s="4"/>
-      <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
       <c r="BF24" s="4"/>
       <c r="BG24" s="4"/>
-      <c r="BH24" s="5"/>
-    </row>
-    <row r="25" spans="1:60" ht="14" customHeight="1">
+      <c r="BH24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="5"/>
+    </row>
+    <row r="25" spans="1:63" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -5881,33 +6279,36 @@
       <c r="AI25" s="3"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5"/>
-      <c r="AL25" s="3"/>
+      <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
       <c r="AN25" s="4"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="4"/>
-      <c r="AQ25" s="5"/>
+      <c r="AQ25" s="4"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="4"/>
       <c r="AT25" s="5"/>
-      <c r="AU25" s="4"/>
+      <c r="AU25" s="3"/>
       <c r="AV25" s="4"/>
-      <c r="AW25" s="4"/>
-      <c r="AX25" s="3"/>
+      <c r="AW25" s="5"/>
+      <c r="AX25" s="4"/>
       <c r="AY25" s="4"/>
-      <c r="AZ25" s="5"/>
-      <c r="BA25" s="4" t="s">
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="5"/>
+      <c r="BD25" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB25" s="4"/>
-      <c r="BC25" s="4"/>
-      <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
       <c r="BF25" s="4"/>
       <c r="BG25" s="4"/>
-      <c r="BH25" s="5"/>
-    </row>
-    <row r="26" spans="1:60" ht="14" customHeight="1">
+      <c r="BH25" s="4"/>
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="5"/>
+    </row>
+    <row r="26" spans="1:63" ht="14" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>78</v>
       </c>
@@ -5955,33 +6356,36 @@
       <c r="AI26" s="3"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5"/>
-      <c r="AL26" s="3"/>
+      <c r="AL26" s="4"/>
       <c r="AM26" s="4"/>
       <c r="AN26" s="4"/>
       <c r="AO26" s="3"/>
       <c r="AP26" s="4"/>
-      <c r="AQ26" s="5"/>
+      <c r="AQ26" s="4"/>
       <c r="AR26" s="3"/>
       <c r="AS26" s="4"/>
       <c r="AT26" s="5"/>
-      <c r="AU26" s="4"/>
+      <c r="AU26" s="3"/>
       <c r="AV26" s="4"/>
-      <c r="AW26" s="4"/>
-      <c r="AX26" s="3"/>
+      <c r="AW26" s="5"/>
+      <c r="AX26" s="4"/>
       <c r="AY26" s="4"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="4" t="s">
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="4"/>
+      <c r="BC26" s="5"/>
+      <c r="BD26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BB26" s="4"/>
-      <c r="BC26" s="4"/>
-      <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
       <c r="BF26" s="4"/>
       <c r="BG26" s="4"/>
-      <c r="BH26" s="5"/>
-    </row>
-    <row r="27" spans="1:60" ht="14" customHeight="1">
+      <c r="BH26" s="4"/>
+      <c r="BI26" s="4"/>
+      <c r="BJ26" s="4"/>
+      <c r="BK26" s="5"/>
+    </row>
+    <row r="27" spans="1:63" ht="14" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>79</v>
       </c>
@@ -6029,33 +6433,36 @@
       <c r="AI27" s="3"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5"/>
-      <c r="AL27" s="3"/>
+      <c r="AL27" s="4"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
-      <c r="AO27" s="24"/>
-      <c r="AP27" s="21"/>
-      <c r="AQ27" s="5"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="4"/>
+      <c r="AQ27" s="4"/>
       <c r="AR27" s="24"/>
       <c r="AS27" s="21"/>
       <c r="AT27" s="5"/>
-      <c r="AU27" s="4"/>
-      <c r="AV27" s="4"/>
-      <c r="AW27" s="4"/>
-      <c r="AX27" s="3"/>
+      <c r="AU27" s="24"/>
+      <c r="AV27" s="21"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="4"/>
       <c r="AY27" s="4"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="4" t="s">
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="4"/>
+      <c r="BC27" s="5"/>
+      <c r="BD27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB27" s="4"/>
-      <c r="BC27" s="4"/>
-      <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
       <c r="BF27" s="4"/>
       <c r="BG27" s="4"/>
-      <c r="BH27" s="5"/>
-    </row>
-    <row r="28" spans="1:60" ht="14" customHeight="1">
+      <c r="BH27" s="4"/>
+      <c r="BI27" s="4"/>
+      <c r="BJ27" s="4"/>
+      <c r="BK27" s="5"/>
+    </row>
+    <row r="28" spans="1:63" ht="14" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>80</v>
       </c>
@@ -6103,33 +6510,36 @@
       <c r="AI28" s="3"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5"/>
-      <c r="AL28" s="3"/>
+      <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
       <c r="AN28" s="4"/>
       <c r="AO28" s="3"/>
       <c r="AP28" s="4"/>
-      <c r="AQ28" s="5"/>
+      <c r="AQ28" s="4"/>
       <c r="AR28" s="3"/>
       <c r="AS28" s="4"/>
       <c r="AT28" s="5"/>
-      <c r="AU28" s="4"/>
+      <c r="AU28" s="3"/>
       <c r="AV28" s="4"/>
-      <c r="AW28" s="4"/>
-      <c r="AX28" s="3"/>
+      <c r="AW28" s="5"/>
+      <c r="AX28" s="4"/>
       <c r="AY28" s="4"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="4" t="s">
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="5"/>
+      <c r="BD28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB28" s="4"/>
-      <c r="BC28" s="4"/>
-      <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
       <c r="BF28" s="4"/>
       <c r="BG28" s="4"/>
-      <c r="BH28" s="5"/>
-    </row>
-    <row r="29" spans="1:60" ht="14" customHeight="1">
+      <c r="BH28" s="4"/>
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="5"/>
+    </row>
+    <row r="29" spans="1:63" ht="14" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>81</v>
       </c>
@@ -6177,33 +6587,36 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5"/>
-      <c r="AL29" s="3"/>
+      <c r="AL29" s="4"/>
       <c r="AM29" s="4"/>
       <c r="AN29" s="4"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="4"/>
-      <c r="AQ29" s="5"/>
+      <c r="AQ29" s="4"/>
       <c r="AR29" s="3"/>
       <c r="AS29" s="4"/>
       <c r="AT29" s="5"/>
-      <c r="AU29" s="4"/>
+      <c r="AU29" s="3"/>
       <c r="AV29" s="4"/>
-      <c r="AW29" s="4"/>
-      <c r="AX29" s="3"/>
+      <c r="AW29" s="5"/>
+      <c r="AX29" s="4"/>
       <c r="AY29" s="4"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="4" t="s">
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="5"/>
+      <c r="BD29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BB29" s="4"/>
-      <c r="BC29" s="4"/>
-      <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
       <c r="BF29" s="4"/>
       <c r="BG29" s="4"/>
-      <c r="BH29" s="5"/>
-    </row>
-    <row r="30" spans="1:60" ht="14" customHeight="1">
+      <c r="BH29" s="4"/>
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="5"/>
+    </row>
+    <row r="30" spans="1:63" ht="14" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -6241,31 +6654,34 @@
       <c r="AI30" s="3"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5"/>
-      <c r="AL30" s="3"/>
+      <c r="AL30" s="4"/>
       <c r="AM30" s="4"/>
       <c r="AN30" s="4"/>
       <c r="AO30" s="3"/>
       <c r="AP30" s="4"/>
-      <c r="AQ30" s="5"/>
+      <c r="AQ30" s="4"/>
       <c r="AR30" s="3"/>
       <c r="AS30" s="4"/>
       <c r="AT30" s="5"/>
-      <c r="AU30" s="4"/>
+      <c r="AU30" s="3"/>
       <c r="AV30" s="4"/>
-      <c r="AW30" s="4"/>
-      <c r="AX30" s="3"/>
+      <c r="AW30" s="5"/>
+      <c r="AX30" s="4"/>
       <c r="AY30" s="4"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="3"/>
       <c r="BB30" s="4"/>
-      <c r="BC30" s="4"/>
+      <c r="BC30" s="5"/>
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
       <c r="BF30" s="4"/>
       <c r="BG30" s="4"/>
-      <c r="BH30" s="5"/>
-    </row>
-    <row r="31" spans="1:60" ht="14" customHeight="1">
+      <c r="BH30" s="4"/>
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="5"/>
+    </row>
+    <row r="31" spans="1:63" ht="14" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -6303,31 +6719,34 @@
       <c r="AI31" s="3"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5"/>
-      <c r="AL31" s="3"/>
+      <c r="AL31" s="4"/>
       <c r="AM31" s="4"/>
       <c r="AN31" s="4"/>
       <c r="AO31" s="3"/>
       <c r="AP31" s="4"/>
-      <c r="AQ31" s="5"/>
+      <c r="AQ31" s="4"/>
       <c r="AR31" s="3"/>
       <c r="AS31" s="4"/>
       <c r="AT31" s="5"/>
-      <c r="AU31" s="4"/>
+      <c r="AU31" s="3"/>
       <c r="AV31" s="4"/>
-      <c r="AW31" s="4"/>
-      <c r="AX31" s="3"/>
+      <c r="AW31" s="5"/>
+      <c r="AX31" s="4"/>
       <c r="AY31" s="4"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="3"/>
       <c r="BB31" s="4"/>
-      <c r="BC31" s="4"/>
+      <c r="BC31" s="5"/>
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
       <c r="BF31" s="4"/>
       <c r="BG31" s="4"/>
-      <c r="BH31" s="5"/>
-    </row>
-    <row r="32" spans="1:60" ht="14" customHeight="1">
+      <c r="BH31" s="4"/>
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="5"/>
+    </row>
+    <row r="32" spans="1:63" ht="14" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -6365,31 +6784,34 @@
       <c r="AI32" s="3"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="5"/>
-      <c r="AL32" s="3"/>
+      <c r="AL32" s="4"/>
       <c r="AM32" s="4"/>
       <c r="AN32" s="4"/>
       <c r="AO32" s="3"/>
       <c r="AP32" s="4"/>
-      <c r="AQ32" s="5"/>
+      <c r="AQ32" s="4"/>
       <c r="AR32" s="3"/>
       <c r="AS32" s="4"/>
       <c r="AT32" s="5"/>
-      <c r="AU32" s="4"/>
+      <c r="AU32" s="3"/>
       <c r="AV32" s="4"/>
-      <c r="AW32" s="4"/>
-      <c r="AX32" s="3"/>
+      <c r="AW32" s="5"/>
+      <c r="AX32" s="4"/>
       <c r="AY32" s="4"/>
-      <c r="AZ32" s="5"/>
-      <c r="BA32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="3"/>
       <c r="BB32" s="4"/>
-      <c r="BC32" s="4"/>
+      <c r="BC32" s="5"/>
       <c r="BD32" s="4"/>
       <c r="BE32" s="4"/>
       <c r="BF32" s="4"/>
       <c r="BG32" s="4"/>
-      <c r="BH32" s="5"/>
-    </row>
-    <row r="33" spans="1:60" ht="14" customHeight="1">
+      <c r="BH32" s="4"/>
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="5"/>
+    </row>
+    <row r="33" spans="1:63" ht="14" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -6427,31 +6849,34 @@
       <c r="AI33" s="3"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="5"/>
-      <c r="AL33" s="3"/>
+      <c r="AL33" s="4"/>
       <c r="AM33" s="4"/>
       <c r="AN33" s="4"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="4"/>
-      <c r="AQ33" s="5"/>
+      <c r="AQ33" s="4"/>
       <c r="AR33" s="3"/>
       <c r="AS33" s="4"/>
       <c r="AT33" s="5"/>
-      <c r="AU33" s="4"/>
+      <c r="AU33" s="3"/>
       <c r="AV33" s="4"/>
-      <c r="AW33" s="4"/>
-      <c r="AX33" s="3"/>
+      <c r="AW33" s="5"/>
+      <c r="AX33" s="4"/>
       <c r="AY33" s="4"/>
-      <c r="AZ33" s="5"/>
-      <c r="BA33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="3"/>
       <c r="BB33" s="4"/>
-      <c r="BC33" s="4"/>
+      <c r="BC33" s="5"/>
       <c r="BD33" s="4"/>
       <c r="BE33" s="4"/>
       <c r="BF33" s="4"/>
       <c r="BG33" s="4"/>
-      <c r="BH33" s="5"/>
-    </row>
-    <row r="34" spans="1:60" ht="14" customHeight="1">
+      <c r="BH33" s="4"/>
+      <c r="BI33" s="4"/>
+      <c r="BJ33" s="4"/>
+      <c r="BK33" s="5"/>
+    </row>
+    <row r="34" spans="1:63" ht="14" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -6489,31 +6914,34 @@
       <c r="AI34" s="3"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5"/>
-      <c r="AL34" s="3"/>
+      <c r="AL34" s="4"/>
       <c r="AM34" s="4"/>
       <c r="AN34" s="4"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="4"/>
-      <c r="AQ34" s="5"/>
+      <c r="AQ34" s="4"/>
       <c r="AR34" s="3"/>
       <c r="AS34" s="4"/>
       <c r="AT34" s="5"/>
-      <c r="AU34" s="4"/>
+      <c r="AU34" s="3"/>
       <c r="AV34" s="4"/>
-      <c r="AW34" s="4"/>
-      <c r="AX34" s="3"/>
+      <c r="AW34" s="5"/>
+      <c r="AX34" s="4"/>
       <c r="AY34" s="4"/>
-      <c r="AZ34" s="5"/>
-      <c r="BA34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="3"/>
       <c r="BB34" s="4"/>
-      <c r="BC34" s="4"/>
+      <c r="BC34" s="5"/>
       <c r="BD34" s="4"/>
       <c r="BE34" s="4"/>
       <c r="BF34" s="4"/>
       <c r="BG34" s="4"/>
-      <c r="BH34" s="5"/>
-    </row>
-    <row r="35" spans="1:60" ht="14" customHeight="1">
+      <c r="BH34" s="4"/>
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="5"/>
+    </row>
+    <row r="35" spans="1:63" ht="14" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -6551,31 +6979,34 @@
       <c r="AI35" s="3"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="5"/>
-      <c r="AL35" s="3"/>
+      <c r="AL35" s="4"/>
       <c r="AM35" s="4"/>
       <c r="AN35" s="4"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="4"/>
-      <c r="AQ35" s="5"/>
+      <c r="AQ35" s="4"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="4"/>
       <c r="AT35" s="5"/>
-      <c r="AU35" s="4"/>
+      <c r="AU35" s="3"/>
       <c r="AV35" s="4"/>
-      <c r="AW35" s="4"/>
-      <c r="AX35" s="3"/>
+      <c r="AW35" s="5"/>
+      <c r="AX35" s="4"/>
       <c r="AY35" s="4"/>
-      <c r="AZ35" s="5"/>
-      <c r="BA35" s="4"/>
+      <c r="AZ35" s="4"/>
+      <c r="BA35" s="3"/>
       <c r="BB35" s="4"/>
-      <c r="BC35" s="4"/>
+      <c r="BC35" s="5"/>
       <c r="BD35" s="4"/>
       <c r="BE35" s="4"/>
       <c r="BF35" s="4"/>
       <c r="BG35" s="4"/>
-      <c r="BH35" s="5"/>
-    </row>
-    <row r="36" spans="1:60" ht="14" customHeight="1">
+      <c r="BH35" s="4"/>
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="5"/>
+    </row>
+    <row r="36" spans="1:63" ht="14" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -6613,31 +7044,34 @@
       <c r="AI36" s="3"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="5"/>
-      <c r="AL36" s="3"/>
+      <c r="AL36" s="4"/>
       <c r="AM36" s="4"/>
       <c r="AN36" s="4"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="4"/>
-      <c r="AQ36" s="5"/>
+      <c r="AQ36" s="4"/>
       <c r="AR36" s="3"/>
       <c r="AS36" s="4"/>
       <c r="AT36" s="5"/>
-      <c r="AU36" s="4"/>
+      <c r="AU36" s="3"/>
       <c r="AV36" s="4"/>
-      <c r="AW36" s="4"/>
-      <c r="AX36" s="3"/>
+      <c r="AW36" s="5"/>
+      <c r="AX36" s="4"/>
       <c r="AY36" s="4"/>
-      <c r="AZ36" s="5"/>
-      <c r="BA36" s="4"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="3"/>
       <c r="BB36" s="4"/>
-      <c r="BC36" s="4"/>
+      <c r="BC36" s="5"/>
       <c r="BD36" s="4"/>
       <c r="BE36" s="4"/>
       <c r="BF36" s="4"/>
       <c r="BG36" s="4"/>
-      <c r="BH36" s="5"/>
-    </row>
-    <row r="37" spans="1:60" ht="14" customHeight="1">
+      <c r="BH36" s="4"/>
+      <c r="BI36" s="4"/>
+      <c r="BJ36" s="4"/>
+      <c r="BK36" s="5"/>
+    </row>
+    <row r="37" spans="1:63" ht="14" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -6675,31 +7109,34 @@
       <c r="AI37" s="3"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="5"/>
-      <c r="AL37" s="3"/>
+      <c r="AL37" s="4"/>
       <c r="AM37" s="4"/>
       <c r="AN37" s="4"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="4"/>
-      <c r="AQ37" s="5"/>
+      <c r="AQ37" s="4"/>
       <c r="AR37" s="3"/>
       <c r="AS37" s="4"/>
       <c r="AT37" s="5"/>
-      <c r="AU37" s="4"/>
+      <c r="AU37" s="3"/>
       <c r="AV37" s="4"/>
-      <c r="AW37" s="4"/>
-      <c r="AX37" s="3"/>
+      <c r="AW37" s="5"/>
+      <c r="AX37" s="4"/>
       <c r="AY37" s="4"/>
-      <c r="AZ37" s="5"/>
-      <c r="BA37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="3"/>
       <c r="BB37" s="4"/>
-      <c r="BC37" s="4"/>
+      <c r="BC37" s="5"/>
       <c r="BD37" s="4"/>
       <c r="BE37" s="4"/>
       <c r="BF37" s="4"/>
       <c r="BG37" s="4"/>
-      <c r="BH37" s="5"/>
-    </row>
-    <row r="38" spans="1:60" ht="14" customHeight="1">
+      <c r="BH37" s="4"/>
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="5"/>
+    </row>
+    <row r="38" spans="1:63" ht="14" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -6737,31 +7174,34 @@
       <c r="AI38" s="3"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="5"/>
-      <c r="AL38" s="3"/>
+      <c r="AL38" s="4"/>
       <c r="AM38" s="4"/>
       <c r="AN38" s="4"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="4"/>
-      <c r="AQ38" s="5"/>
+      <c r="AQ38" s="4"/>
       <c r="AR38" s="3"/>
       <c r="AS38" s="4"/>
       <c r="AT38" s="5"/>
-      <c r="AU38" s="4"/>
+      <c r="AU38" s="3"/>
       <c r="AV38" s="4"/>
-      <c r="AW38" s="4"/>
-      <c r="AX38" s="3"/>
+      <c r="AW38" s="5"/>
+      <c r="AX38" s="4"/>
       <c r="AY38" s="4"/>
-      <c r="AZ38" s="5"/>
-      <c r="BA38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="3"/>
       <c r="BB38" s="4"/>
-      <c r="BC38" s="4"/>
+      <c r="BC38" s="5"/>
       <c r="BD38" s="4"/>
       <c r="BE38" s="4"/>
       <c r="BF38" s="4"/>
       <c r="BG38" s="4"/>
-      <c r="BH38" s="5"/>
-    </row>
-    <row r="39" spans="1:60" ht="14" customHeight="1">
+      <c r="BH38" s="4"/>
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="5"/>
+    </row>
+    <row r="39" spans="1:63" ht="14" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -6799,31 +7239,34 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="5"/>
-      <c r="AL39" s="3"/>
+      <c r="AL39" s="4"/>
       <c r="AM39" s="4"/>
       <c r="AN39" s="4"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="4"/>
-      <c r="AQ39" s="5"/>
+      <c r="AQ39" s="4"/>
       <c r="AR39" s="3"/>
       <c r="AS39" s="4"/>
       <c r="AT39" s="5"/>
-      <c r="AU39" s="4"/>
+      <c r="AU39" s="3"/>
       <c r="AV39" s="4"/>
-      <c r="AW39" s="4"/>
-      <c r="AX39" s="3"/>
+      <c r="AW39" s="5"/>
+      <c r="AX39" s="4"/>
       <c r="AY39" s="4"/>
-      <c r="AZ39" s="5"/>
-      <c r="BA39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="3"/>
       <c r="BB39" s="4"/>
-      <c r="BC39" s="4"/>
+      <c r="BC39" s="5"/>
       <c r="BD39" s="4"/>
       <c r="BE39" s="4"/>
       <c r="BF39" s="4"/>
       <c r="BG39" s="4"/>
-      <c r="BH39" s="5"/>
-    </row>
-    <row r="40" spans="1:60" ht="14" customHeight="1">
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="5"/>
+    </row>
+    <row r="40" spans="1:63" ht="14" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -6861,31 +7304,34 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="5"/>
-      <c r="AL40" s="3"/>
+      <c r="AL40" s="4"/>
       <c r="AM40" s="4"/>
       <c r="AN40" s="4"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="4"/>
-      <c r="AQ40" s="5"/>
+      <c r="AQ40" s="4"/>
       <c r="AR40" s="3"/>
       <c r="AS40" s="4"/>
       <c r="AT40" s="5"/>
-      <c r="AU40" s="4"/>
+      <c r="AU40" s="3"/>
       <c r="AV40" s="4"/>
-      <c r="AW40" s="4"/>
-      <c r="AX40" s="3"/>
+      <c r="AW40" s="5"/>
+      <c r="AX40" s="4"/>
       <c r="AY40" s="4"/>
-      <c r="AZ40" s="5"/>
-      <c r="BA40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="3"/>
       <c r="BB40" s="4"/>
-      <c r="BC40" s="4"/>
+      <c r="BC40" s="5"/>
       <c r="BD40" s="4"/>
       <c r="BE40" s="4"/>
       <c r="BF40" s="4"/>
       <c r="BG40" s="4"/>
-      <c r="BH40" s="5"/>
-    </row>
-    <row r="41" spans="1:60" ht="14" customHeight="1">
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="5"/>
+    </row>
+    <row r="41" spans="1:63" ht="14" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
@@ -6923,31 +7369,34 @@
       <c r="AI41" s="3"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="5"/>
-      <c r="AL41" s="3"/>
+      <c r="AL41" s="4"/>
       <c r="AM41" s="4"/>
       <c r="AN41" s="4"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="4"/>
-      <c r="AQ41" s="5"/>
+      <c r="AQ41" s="4"/>
       <c r="AR41" s="3"/>
       <c r="AS41" s="4"/>
       <c r="AT41" s="5"/>
-      <c r="AU41" s="4"/>
+      <c r="AU41" s="3"/>
       <c r="AV41" s="4"/>
-      <c r="AW41" s="4"/>
-      <c r="AX41" s="3"/>
+      <c r="AW41" s="5"/>
+      <c r="AX41" s="4"/>
       <c r="AY41" s="4"/>
-      <c r="AZ41" s="5"/>
-      <c r="BA41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="3"/>
       <c r="BB41" s="4"/>
-      <c r="BC41" s="4"/>
+      <c r="BC41" s="5"/>
       <c r="BD41" s="4"/>
       <c r="BE41" s="4"/>
       <c r="BF41" s="4"/>
       <c r="BG41" s="4"/>
-      <c r="BH41" s="5"/>
-    </row>
-    <row r="42" spans="1:60" ht="14" customHeight="1">
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="5"/>
+    </row>
+    <row r="42" spans="1:63" ht="14" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
@@ -6985,31 +7434,34 @@
       <c r="AI42" s="3"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="5"/>
-      <c r="AL42" s="3"/>
+      <c r="AL42" s="4"/>
       <c r="AM42" s="4"/>
       <c r="AN42" s="4"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="4"/>
-      <c r="AQ42" s="5"/>
+      <c r="AQ42" s="4"/>
       <c r="AR42" s="3"/>
       <c r="AS42" s="4"/>
       <c r="AT42" s="5"/>
-      <c r="AU42" s="4"/>
+      <c r="AU42" s="3"/>
       <c r="AV42" s="4"/>
-      <c r="AW42" s="4"/>
-      <c r="AX42" s="3"/>
+      <c r="AW42" s="5"/>
+      <c r="AX42" s="4"/>
       <c r="AY42" s="4"/>
-      <c r="AZ42" s="5"/>
-      <c r="BA42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="3"/>
       <c r="BB42" s="4"/>
-      <c r="BC42" s="4"/>
+      <c r="BC42" s="5"/>
       <c r="BD42" s="4"/>
       <c r="BE42" s="4"/>
       <c r="BF42" s="4"/>
       <c r="BG42" s="4"/>
-      <c r="BH42" s="5"/>
-    </row>
-    <row r="43" spans="1:60" ht="14" customHeight="1">
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="5"/>
+    </row>
+    <row r="43" spans="1:63" ht="14" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
@@ -7047,31 +7499,34 @@
       <c r="AI43" s="3"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="5"/>
-      <c r="AL43" s="3"/>
+      <c r="AL43" s="4"/>
       <c r="AM43" s="4"/>
       <c r="AN43" s="4"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="4"/>
-      <c r="AQ43" s="5"/>
+      <c r="AQ43" s="4"/>
       <c r="AR43" s="3"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="5"/>
-      <c r="AU43" s="4"/>
+      <c r="AU43" s="3"/>
       <c r="AV43" s="4"/>
-      <c r="AW43" s="4"/>
-      <c r="AX43" s="3"/>
+      <c r="AW43" s="5"/>
+      <c r="AX43" s="4"/>
       <c r="AY43" s="4"/>
-      <c r="AZ43" s="5"/>
-      <c r="BA43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="3"/>
       <c r="BB43" s="4"/>
-      <c r="BC43" s="4"/>
+      <c r="BC43" s="5"/>
       <c r="BD43" s="4"/>
       <c r="BE43" s="4"/>
       <c r="BF43" s="4"/>
       <c r="BG43" s="4"/>
-      <c r="BH43" s="5"/>
-    </row>
-    <row r="44" spans="1:60" ht="14" customHeight="1">
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="5"/>
+    </row>
+    <row r="44" spans="1:63" ht="14" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
@@ -7109,31 +7564,34 @@
       <c r="AI44" s="3"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="5"/>
-      <c r="AL44" s="3"/>
+      <c r="AL44" s="4"/>
       <c r="AM44" s="4"/>
       <c r="AN44" s="4"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="4"/>
-      <c r="AQ44" s="5"/>
+      <c r="AQ44" s="4"/>
       <c r="AR44" s="3"/>
       <c r="AS44" s="4"/>
       <c r="AT44" s="5"/>
-      <c r="AU44" s="4"/>
+      <c r="AU44" s="3"/>
       <c r="AV44" s="4"/>
-      <c r="AW44" s="4"/>
-      <c r="AX44" s="3"/>
+      <c r="AW44" s="5"/>
+      <c r="AX44" s="4"/>
       <c r="AY44" s="4"/>
-      <c r="AZ44" s="5"/>
-      <c r="BA44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="3"/>
       <c r="BB44" s="4"/>
-      <c r="BC44" s="4"/>
+      <c r="BC44" s="5"/>
       <c r="BD44" s="4"/>
       <c r="BE44" s="4"/>
       <c r="BF44" s="4"/>
       <c r="BG44" s="4"/>
-      <c r="BH44" s="5"/>
-    </row>
-    <row r="45" spans="1:60" ht="14" customHeight="1">
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="5"/>
+    </row>
+    <row r="45" spans="1:63" ht="14" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="3"/>
@@ -7171,56 +7629,3135 @@
       <c r="AI45" s="3"/>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="5"/>
-      <c r="AL45" s="3"/>
+      <c r="AL45" s="4"/>
       <c r="AM45" s="4"/>
       <c r="AN45" s="4"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="4"/>
-      <c r="AQ45" s="5"/>
+      <c r="AQ45" s="4"/>
       <c r="AR45" s="3"/>
       <c r="AS45" s="4"/>
       <c r="AT45" s="5"/>
-      <c r="AU45" s="4"/>
+      <c r="AU45" s="3"/>
       <c r="AV45" s="4"/>
-      <c r="AW45" s="4"/>
-      <c r="AX45" s="3"/>
+      <c r="AW45" s="5"/>
+      <c r="AX45" s="4"/>
       <c r="AY45" s="4"/>
-      <c r="AZ45" s="5"/>
-      <c r="BA45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="3"/>
       <c r="BB45" s="4"/>
-      <c r="BC45" s="4"/>
+      <c r="BC45" s="5"/>
       <c r="BD45" s="4"/>
       <c r="BE45" s="4"/>
       <c r="BF45" s="4"/>
       <c r="BG45" s="4"/>
-      <c r="BH45" s="5"/>
+      <c r="BH45" s="4"/>
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
   </headerFooter>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D93C2F7-C0F6-924A-BBA6-30F6365A1D50}">
-          <x14:formula1>
-            <xm:f>'#SAMPLE'!$H$10:$H$45</xm:f>
-          </x14:formula1>
-          <xm:sqref>H10:H45</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EACF85C5-A8B1-FC41-8DC7-419D4BD600EC}">
-          <x14:formula1>
-            <xm:f>'#SAMPLE'!$K$10:$K$45</xm:f>
-          </x14:formula1>
-          <xm:sqref>K10:K45</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA7DE17-74C0-0647-8E2B-58F9351B9DA4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BK45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
+  <cols>
+    <col min="1" max="26" width="2.42578125" style="6"/>
+    <col min="27" max="30" width="2.42578125" style="6" customWidth="1"/>
+    <col min="31" max="16384" width="2.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:63" ht="14" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+      <c r="BD1" s="4"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="5"/>
+    </row>
+    <row r="2" spans="1:63" ht="14" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="4"/>
+      <c r="AT2" s="4"/>
+      <c r="AU2" s="4"/>
+      <c r="AV2" s="4"/>
+      <c r="AW2" s="4"/>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="4"/>
+      <c r="AZ2" s="4"/>
+      <c r="BA2" s="4"/>
+      <c r="BB2" s="4"/>
+      <c r="BC2" s="4"/>
+      <c r="BD2" s="4"/>
+      <c r="BE2" s="4"/>
+      <c r="BF2" s="4"/>
+      <c r="BG2" s="4"/>
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="4"/>
+      <c r="BJ2" s="4"/>
+      <c r="BK2" s="5"/>
+    </row>
+    <row r="3" spans="1:63" ht="14" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L3"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
+      <c r="AL3" s="2"/>
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="4"/>
+      <c r="AT3" s="4"/>
+      <c r="AU3" s="4"/>
+      <c r="AV3" s="4"/>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
+      <c r="AY3" s="4"/>
+      <c r="AZ3" s="4"/>
+      <c r="BA3" s="4"/>
+      <c r="BB3" s="4"/>
+      <c r="BC3" s="4"/>
+      <c r="BD3" s="4"/>
+      <c r="BE3" s="4"/>
+      <c r="BF3" s="4"/>
+      <c r="BG3" s="4"/>
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="5"/>
+    </row>
+    <row r="4" spans="1:63" ht="14" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8"/>
+      <c r="AB4" s="8"/>
+      <c r="AC4" s="8"/>
+      <c r="AD4" s="8"/>
+      <c r="AE4" s="8"/>
+      <c r="AF4" s="8"/>
+      <c r="AG4" s="8"/>
+      <c r="AH4" s="8"/>
+      <c r="AI4" s="8"/>
+      <c r="AJ4" s="8"/>
+      <c r="AK4" s="8"/>
+      <c r="AL4" s="8"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="8"/>
+      <c r="AR4" s="8"/>
+      <c r="AS4" s="8"/>
+      <c r="AT4" s="8"/>
+      <c r="AU4" s="8"/>
+      <c r="AV4" s="8"/>
+      <c r="AW4" s="8"/>
+      <c r="AX4" s="8"/>
+      <c r="AY4" s="8"/>
+      <c r="AZ4" s="8"/>
+      <c r="BA4" s="8"/>
+      <c r="BB4" s="8"/>
+      <c r="BC4" s="8"/>
+      <c r="BD4" s="8"/>
+      <c r="BE4" s="8"/>
+      <c r="BF4" s="8"/>
+      <c r="BG4" s="8"/>
+      <c r="BH4" s="8"/>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="8"/>
+      <c r="BK4" s="9"/>
+    </row>
+    <row r="5" spans="1:63" ht="14" customHeight="1">
+      <c r="A5" s="10"/>
+      <c r="BK5" s="11"/>
+    </row>
+    <row r="6" spans="1:63" ht="14" customHeight="1">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="13"/>
+      <c r="AN6" s="13"/>
+      <c r="AO6" s="13"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="13"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="13"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="13"/>
+      <c r="BF6" s="13"/>
+      <c r="BG6" s="13"/>
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="13"/>
+      <c r="BJ6" s="13"/>
+      <c r="BK6" s="14"/>
+    </row>
+    <row r="8" spans="1:63" ht="14" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="17"/>
+      <c r="AO8" s="17"/>
+      <c r="AP8" s="17"/>
+      <c r="AQ8" s="17"/>
+      <c r="AR8" s="17"/>
+      <c r="AS8" s="17"/>
+      <c r="AT8" s="17"/>
+      <c r="AU8" s="17"/>
+      <c r="AV8" s="17"/>
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="16"/>
+      <c r="BD8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="17"/>
+      <c r="BG8" s="17"/>
+      <c r="BH8" s="17"/>
+      <c r="BI8" s="17"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="16"/>
+    </row>
+    <row r="9" spans="1:63" ht="14" customHeight="1">
+      <c r="A9" s="18"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="20"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="20"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="20"/>
+      <c r="AO9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP9" s="20"/>
+      <c r="AQ9" s="20"/>
+      <c r="AR9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="20"/>
+      <c r="AU9" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="19"/>
+      <c r="AX9" s="18"/>
+      <c r="AY9" s="20"/>
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="18"/>
+      <c r="BB9" s="20"/>
+      <c r="BC9" s="19"/>
+      <c r="BD9" s="20"/>
+      <c r="BE9" s="20"/>
+      <c r="BF9" s="20"/>
+      <c r="BG9" s="20"/>
+      <c r="BH9" s="20"/>
+      <c r="BI9" s="20"/>
+      <c r="BJ9" s="20"/>
+      <c r="BK9" s="19"/>
+    </row>
+    <row r="10" spans="1:63" ht="14" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="U10" s="26"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="26"/>
+      <c r="AD10" s="26"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ10" s="26"/>
+      <c r="AK10" s="27"/>
+      <c r="AL10" s="26"/>
+      <c r="AM10" s="26"/>
+      <c r="AN10" s="26"/>
+      <c r="AO10" s="25"/>
+      <c r="AP10" s="26"/>
+      <c r="AQ10" s="26"/>
+      <c r="AR10" s="25"/>
+      <c r="AS10" s="26"/>
+      <c r="AT10" s="26"/>
+      <c r="AU10" s="25"/>
+      <c r="AV10" s="26"/>
+      <c r="AW10" s="28"/>
+      <c r="AX10" s="26"/>
+      <c r="AY10" s="26"/>
+      <c r="AZ10" s="26"/>
+      <c r="BA10" s="25"/>
+      <c r="BB10" s="26"/>
+      <c r="BC10" s="28"/>
+      <c r="BD10" s="26"/>
+      <c r="BE10" s="26"/>
+      <c r="BF10" s="26"/>
+      <c r="BG10" s="26"/>
+      <c r="BH10" s="26"/>
+      <c r="BI10" s="26"/>
+      <c r="BJ10" s="26"/>
+      <c r="BK10" s="28"/>
+    </row>
+    <row r="11" spans="1:63" ht="14" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="26"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="26"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ11" s="26"/>
+      <c r="AK11" s="27"/>
+      <c r="AL11" s="29"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="30"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="30"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="25"/>
+      <c r="AV11" s="26"/>
+      <c r="AW11" s="31"/>
+      <c r="AX11" s="29"/>
+      <c r="AY11" s="29"/>
+      <c r="AZ11" s="29"/>
+      <c r="BA11" s="30"/>
+      <c r="BB11" s="29"/>
+      <c r="BC11" s="31"/>
+      <c r="BD11" s="29"/>
+      <c r="BE11" s="29"/>
+      <c r="BF11" s="29"/>
+      <c r="BG11" s="29"/>
+      <c r="BH11" s="29"/>
+      <c r="BI11" s="29"/>
+      <c r="BJ11" s="29"/>
+      <c r="BK11" s="31"/>
+    </row>
+    <row r="12" spans="1:63" ht="14" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="U12" s="26"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="29"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="29"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="29"/>
+      <c r="AI12" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ12" s="26"/>
+      <c r="AK12" s="27"/>
+      <c r="AL12" s="29"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="30"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="29"/>
+      <c r="AR12" s="30"/>
+      <c r="AS12" s="29"/>
+      <c r="AT12" s="29"/>
+      <c r="AU12" s="25"/>
+      <c r="AV12" s="26"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="29"/>
+      <c r="AY12" s="29"/>
+      <c r="AZ12" s="29"/>
+      <c r="BA12" s="30"/>
+      <c r="BB12" s="29"/>
+      <c r="BC12" s="31"/>
+      <c r="BD12" s="29"/>
+      <c r="BE12" s="29"/>
+      <c r="BF12" s="29"/>
+      <c r="BG12" s="29"/>
+      <c r="BH12" s="29"/>
+      <c r="BI12" s="29"/>
+      <c r="BJ12" s="29"/>
+      <c r="BK12" s="31"/>
+    </row>
+    <row r="13" spans="1:63" ht="14" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="AJ13" s="26"/>
+      <c r="AK13" s="27"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="30"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="30"/>
+      <c r="AS13" s="29"/>
+      <c r="AT13" s="29"/>
+      <c r="AU13" s="25"/>
+      <c r="AV13" s="26"/>
+      <c r="AW13" s="31"/>
+      <c r="AX13" s="29"/>
+      <c r="AY13" s="29"/>
+      <c r="AZ13" s="29"/>
+      <c r="BA13" s="30"/>
+      <c r="BB13" s="29"/>
+      <c r="BC13" s="31"/>
+      <c r="BD13" s="29"/>
+      <c r="BE13" s="29"/>
+      <c r="BF13" s="29"/>
+      <c r="BG13" s="29"/>
+      <c r="BH13" s="29"/>
+      <c r="BI13" s="29"/>
+      <c r="BJ13" s="29"/>
+      <c r="BK13" s="31"/>
+    </row>
+    <row r="14" spans="1:63" ht="14" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="U14" s="26"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="31"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ14" s="26"/>
+      <c r="AK14" s="27"/>
+      <c r="AL14" s="29"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="29"/>
+      <c r="AO14" s="30"/>
+      <c r="AP14" s="29"/>
+      <c r="AQ14" s="29"/>
+      <c r="AR14" s="30"/>
+      <c r="AS14" s="29"/>
+      <c r="AT14" s="29"/>
+      <c r="AU14" s="25"/>
+      <c r="AV14" s="26"/>
+      <c r="AW14" s="31"/>
+      <c r="AX14" s="29"/>
+      <c r="AY14" s="29"/>
+      <c r="AZ14" s="29"/>
+      <c r="BA14" s="30"/>
+      <c r="BB14" s="29"/>
+      <c r="BC14" s="31"/>
+      <c r="BD14" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE14" s="26"/>
+      <c r="BF14" s="26"/>
+      <c r="BG14" s="26"/>
+      <c r="BH14" s="26"/>
+      <c r="BI14" s="29"/>
+      <c r="BJ14" s="29"/>
+      <c r="BK14" s="31"/>
+    </row>
+    <row r="15" spans="1:63" ht="14" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="26"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="U15" s="26"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="31"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ15" s="26"/>
+      <c r="AK15" s="27"/>
+      <c r="AL15" s="29"/>
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="29"/>
+      <c r="AO15" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP15" s="29"/>
+      <c r="AQ15" s="29"/>
+      <c r="AR15" s="30"/>
+      <c r="AS15" s="29"/>
+      <c r="AT15" s="29"/>
+      <c r="AU15" s="25"/>
+      <c r="AV15" s="26"/>
+      <c r="AW15" s="31"/>
+      <c r="AX15" s="29"/>
+      <c r="AY15" s="29"/>
+      <c r="AZ15" s="29"/>
+      <c r="BA15" s="30"/>
+      <c r="BB15" s="29"/>
+      <c r="BC15" s="31"/>
+      <c r="BD15" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE15" s="26"/>
+      <c r="BF15" s="26"/>
+      <c r="BG15" s="26"/>
+      <c r="BH15" s="29"/>
+      <c r="BI15" s="29"/>
+      <c r="BJ15" s="29"/>
+      <c r="BK15" s="31"/>
+    </row>
+    <row r="16" spans="1:63" ht="14" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="U16" s="26"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="29"/>
+      <c r="AI16" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ16" s="26"/>
+      <c r="AK16" s="27"/>
+      <c r="AL16" s="29"/>
+      <c r="AM16" s="29"/>
+      <c r="AN16" s="29"/>
+      <c r="AO16" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP16" s="29"/>
+      <c r="AQ16" s="29"/>
+      <c r="AR16" s="30"/>
+      <c r="AS16" s="29"/>
+      <c r="AT16" s="29"/>
+      <c r="AU16" s="25"/>
+      <c r="AV16" s="26"/>
+      <c r="AW16" s="31"/>
+      <c r="AX16" s="29"/>
+      <c r="AY16" s="29"/>
+      <c r="AZ16" s="29"/>
+      <c r="BA16" s="30"/>
+      <c r="BB16" s="29"/>
+      <c r="BC16" s="31"/>
+      <c r="BD16" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="BE16" s="26"/>
+      <c r="BF16" s="26"/>
+      <c r="BG16" s="26"/>
+      <c r="BH16" s="29"/>
+      <c r="BI16" s="29"/>
+      <c r="BJ16" s="29"/>
+      <c r="BK16" s="31"/>
+    </row>
+    <row r="17" spans="1:63" ht="14" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="26"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="26"/>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="29"/>
+      <c r="AH17" s="29"/>
+      <c r="AI17" s="30"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="31"/>
+      <c r="AL17" s="32"/>
+      <c r="AM17" s="32"/>
+      <c r="AN17" s="32"/>
+      <c r="AO17" s="33"/>
+      <c r="AP17" s="29"/>
+      <c r="AQ17" s="29"/>
+      <c r="AR17" s="32"/>
+      <c r="AS17" s="29"/>
+      <c r="AT17" s="29"/>
+      <c r="AU17" s="25"/>
+      <c r="AV17" s="26"/>
+      <c r="AW17" s="31"/>
+      <c r="AX17" s="29"/>
+      <c r="AY17" s="29"/>
+      <c r="AZ17" s="29"/>
+      <c r="BA17" s="30"/>
+      <c r="BB17" s="29"/>
+      <c r="BC17" s="31"/>
+      <c r="BD17" s="29"/>
+      <c r="BE17" s="29"/>
+      <c r="BF17" s="29"/>
+      <c r="BG17" s="29"/>
+      <c r="BH17" s="29"/>
+      <c r="BI17" s="29"/>
+      <c r="BJ17" s="29"/>
+      <c r="BK17" s="31"/>
+    </row>
+    <row r="18" spans="1:63" ht="14" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="26"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="29"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="29"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="29"/>
+      <c r="AI18" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ18" s="26"/>
+      <c r="AK18" s="27"/>
+      <c r="AL18" s="26"/>
+      <c r="AM18" s="26"/>
+      <c r="AN18" s="26"/>
+      <c r="AO18" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP18" s="26"/>
+      <c r="AQ18" s="26"/>
+      <c r="AR18" s="25"/>
+      <c r="AS18" s="26"/>
+      <c r="AT18" s="26"/>
+      <c r="AU18" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="26"/>
+      <c r="AW18" s="31"/>
+      <c r="AX18" s="29"/>
+      <c r="AY18" s="29"/>
+      <c r="AZ18" s="29"/>
+      <c r="BA18" s="30"/>
+      <c r="BB18" s="29"/>
+      <c r="BC18" s="31"/>
+      <c r="BD18" s="29"/>
+      <c r="BE18" s="29"/>
+      <c r="BF18" s="29"/>
+      <c r="BG18" s="29"/>
+      <c r="BH18" s="29"/>
+      <c r="BI18" s="29"/>
+      <c r="BJ18" s="29"/>
+      <c r="BK18" s="31"/>
+    </row>
+    <row r="19" spans="1:63" ht="14" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="26"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="26"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="26"/>
+      <c r="AB19" s="31"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="29"/>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="29"/>
+      <c r="AK19" s="31"/>
+      <c r="AL19" s="29"/>
+      <c r="AM19" s="29"/>
+      <c r="AN19" s="29"/>
+      <c r="AO19" s="30"/>
+      <c r="AP19" s="29"/>
+      <c r="AQ19" s="29"/>
+      <c r="AR19" s="30"/>
+      <c r="AS19" s="29"/>
+      <c r="AT19" s="29"/>
+      <c r="AU19" s="25"/>
+      <c r="AV19" s="26"/>
+      <c r="AW19" s="31"/>
+      <c r="AX19" s="29"/>
+      <c r="AY19" s="29"/>
+      <c r="AZ19" s="29"/>
+      <c r="BA19" s="30"/>
+      <c r="BB19" s="29"/>
+      <c r="BC19" s="31"/>
+      <c r="BD19" s="29"/>
+      <c r="BE19" s="29"/>
+      <c r="BF19" s="29"/>
+      <c r="BG19" s="29"/>
+      <c r="BH19" s="29"/>
+      <c r="BI19" s="29"/>
+      <c r="BJ19" s="29"/>
+      <c r="BK19" s="31"/>
+    </row>
+    <row r="20" spans="1:63" ht="14" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="4"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="4"/>
+      <c r="AH20" s="4"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="4"/>
+      <c r="AK20" s="5"/>
+      <c r="AL20" s="4"/>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="4"/>
+      <c r="AQ20" s="4"/>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="4"/>
+      <c r="AT20" s="4"/>
+      <c r="AU20" s="3"/>
+      <c r="AV20" s="4"/>
+      <c r="AW20" s="5"/>
+      <c r="AX20" s="4"/>
+      <c r="AY20" s="4"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="3"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="5"/>
+      <c r="BD20" s="4"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="4"/>
+      <c r="BG20" s="4"/>
+      <c r="BH20" s="4"/>
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="5"/>
+    </row>
+    <row r="21" spans="1:63" ht="14" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="4"/>
+      <c r="AH21" s="4"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="4"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="4"/>
+      <c r="AM21" s="4"/>
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="4"/>
+      <c r="AR21" s="3"/>
+      <c r="AS21" s="4"/>
+      <c r="AT21" s="4"/>
+      <c r="AU21" s="3"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="5"/>
+      <c r="BD21" s="4"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="4"/>
+      <c r="BG21" s="4"/>
+      <c r="BH21" s="4"/>
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="5"/>
+    </row>
+    <row r="22" spans="1:63" ht="14" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="4"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="4"/>
+      <c r="AK22" s="5"/>
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="4"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="4"/>
+      <c r="AU22" s="3"/>
+      <c r="AV22" s="4"/>
+      <c r="AW22" s="5"/>
+      <c r="AX22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="5"/>
+      <c r="BD22" s="4"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="5"/>
+    </row>
+    <row r="23" spans="1:63" ht="14" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="5"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="3"/>
+      <c r="AV23" s="4"/>
+      <c r="AW23" s="5"/>
+      <c r="AX23" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="5"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
+      <c r="BH23" s="4"/>
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="5"/>
+    </row>
+    <row r="24" spans="1:63" ht="14" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="5"/>
+      <c r="AL24" s="4"/>
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="3"/>
+      <c r="AP24" s="4"/>
+      <c r="AQ24" s="4"/>
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="4"/>
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="24"/>
+      <c r="AV24" s="21"/>
+      <c r="AW24" s="5"/>
+      <c r="AX24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="4"/>
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="5"/>
+      <c r="BD24" s="4"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="4"/>
+      <c r="BG24" s="4"/>
+      <c r="BH24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="5"/>
+    </row>
+    <row r="25" spans="1:63" ht="14" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="5"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="5"/>
+      <c r="AL25" s="4"/>
+      <c r="AM25" s="4"/>
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="4"/>
+      <c r="AQ25" s="4"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="4"/>
+      <c r="AT25" s="4"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="4"/>
+      <c r="AW25" s="5"/>
+      <c r="AX25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="5"/>
+      <c r="BD25" s="4"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="4"/>
+      <c r="BG25" s="4"/>
+      <c r="BH25" s="4"/>
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="5"/>
+    </row>
+    <row r="26" spans="1:63" ht="14" customHeight="1">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="4"/>
+      <c r="AK26" s="5"/>
+      <c r="AL26" s="4"/>
+      <c r="AM26" s="4"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="3"/>
+      <c r="AP26" s="4"/>
+      <c r="AQ26" s="4"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="4"/>
+      <c r="AT26" s="4"/>
+      <c r="AU26" s="3"/>
+      <c r="AV26" s="4"/>
+      <c r="AW26" s="5"/>
+      <c r="AX26" s="4"/>
+      <c r="AY26" s="4"/>
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="4"/>
+      <c r="BC26" s="5"/>
+      <c r="BD26" s="4"/>
+      <c r="BE26" s="4"/>
+      <c r="BF26" s="4"/>
+      <c r="BG26" s="4"/>
+      <c r="BH26" s="4"/>
+      <c r="BI26" s="4"/>
+      <c r="BJ26" s="4"/>
+      <c r="BK26" s="5"/>
+    </row>
+    <row r="27" spans="1:63" ht="14" customHeight="1">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="4"/>
+      <c r="AD27" s="4"/>
+      <c r="AE27" s="4"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="4"/>
+      <c r="AH27" s="4"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="5"/>
+      <c r="AL27" s="4"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="4"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="4"/>
+      <c r="AQ27" s="4"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="4"/>
+      <c r="AT27" s="4"/>
+      <c r="AU27" s="3"/>
+      <c r="AV27" s="4"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="4"/>
+      <c r="AY27" s="4"/>
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="4"/>
+      <c r="BC27" s="5"/>
+      <c r="BD27" s="4"/>
+      <c r="BE27" s="4"/>
+      <c r="BF27" s="4"/>
+      <c r="BG27" s="4"/>
+      <c r="BH27" s="4"/>
+      <c r="BI27" s="4"/>
+      <c r="BJ27" s="4"/>
+      <c r="BK27" s="5"/>
+    </row>
+    <row r="28" spans="1:63" ht="14" customHeight="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="5"/>
+      <c r="AL28" s="4"/>
+      <c r="AM28" s="4"/>
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="4"/>
+      <c r="AQ28" s="4"/>
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="4"/>
+      <c r="AT28" s="4"/>
+      <c r="AU28" s="3"/>
+      <c r="AV28" s="4"/>
+      <c r="AW28" s="5"/>
+      <c r="AX28" s="4"/>
+      <c r="AY28" s="4"/>
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="5"/>
+      <c r="BD28" s="4"/>
+      <c r="BE28" s="4"/>
+      <c r="BF28" s="4"/>
+      <c r="BG28" s="4"/>
+      <c r="BH28" s="4"/>
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="5"/>
+    </row>
+    <row r="29" spans="1:63" ht="14" customHeight="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="5"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
+      <c r="AN29" s="4"/>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="4"/>
+      <c r="AQ29" s="4"/>
+      <c r="AR29" s="3"/>
+      <c r="AS29" s="4"/>
+      <c r="AT29" s="4"/>
+      <c r="AU29" s="3"/>
+      <c r="AV29" s="4"/>
+      <c r="AW29" s="5"/>
+      <c r="AX29" s="4"/>
+      <c r="AY29" s="4"/>
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="5"/>
+      <c r="BD29" s="4"/>
+      <c r="BE29" s="4"/>
+      <c r="BF29" s="4"/>
+      <c r="BG29" s="4"/>
+      <c r="BH29" s="4"/>
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="5"/>
+    </row>
+    <row r="30" spans="1:63" ht="14" customHeight="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="3"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="5"/>
+      <c r="AL30" s="4"/>
+      <c r="AM30" s="4"/>
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="3"/>
+      <c r="AP30" s="4"/>
+      <c r="AQ30" s="4"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="4"/>
+      <c r="AT30" s="4"/>
+      <c r="AU30" s="3"/>
+      <c r="AV30" s="4"/>
+      <c r="AW30" s="5"/>
+      <c r="AX30" s="4"/>
+      <c r="AY30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="4"/>
+      <c r="BC30" s="5"/>
+      <c r="BD30" s="4"/>
+      <c r="BE30" s="4"/>
+      <c r="BF30" s="4"/>
+      <c r="BG30" s="4"/>
+      <c r="BH30" s="4"/>
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="5"/>
+    </row>
+    <row r="31" spans="1:63" ht="14" customHeight="1">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="5"/>
+      <c r="AC31" s="4"/>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="3"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="5"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="3"/>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="4"/>
+      <c r="AR31" s="3"/>
+      <c r="AS31" s="4"/>
+      <c r="AT31" s="4"/>
+      <c r="AU31" s="3"/>
+      <c r="AV31" s="4"/>
+      <c r="AW31" s="5"/>
+      <c r="AX31" s="4"/>
+      <c r="AY31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="3"/>
+      <c r="BB31" s="4"/>
+      <c r="BC31" s="5"/>
+      <c r="BD31" s="4"/>
+      <c r="BE31" s="4"/>
+      <c r="BF31" s="4"/>
+      <c r="BG31" s="4"/>
+      <c r="BH31" s="4"/>
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="5"/>
+    </row>
+    <row r="32" spans="1:63" ht="14" customHeight="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="5"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="4"/>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="5"/>
+      <c r="AL32" s="4"/>
+      <c r="AM32" s="4"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="3"/>
+      <c r="AP32" s="4"/>
+      <c r="AQ32" s="4"/>
+      <c r="AR32" s="3"/>
+      <c r="AS32" s="4"/>
+      <c r="AT32" s="4"/>
+      <c r="AU32" s="3"/>
+      <c r="AV32" s="4"/>
+      <c r="AW32" s="5"/>
+      <c r="AX32" s="4"/>
+      <c r="AY32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="3"/>
+      <c r="BB32" s="4"/>
+      <c r="BC32" s="5"/>
+      <c r="BD32" s="4"/>
+      <c r="BE32" s="4"/>
+      <c r="BF32" s="4"/>
+      <c r="BG32" s="4"/>
+      <c r="BH32" s="4"/>
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="5"/>
+    </row>
+    <row r="33" spans="1:63" ht="14" customHeight="1">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="5"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="3"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="5"/>
+      <c r="AL33" s="4"/>
+      <c r="AM33" s="4"/>
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="3"/>
+      <c r="AP33" s="4"/>
+      <c r="AQ33" s="4"/>
+      <c r="AR33" s="3"/>
+      <c r="AS33" s="4"/>
+      <c r="AT33" s="4"/>
+      <c r="AU33" s="3"/>
+      <c r="AV33" s="4"/>
+      <c r="AW33" s="5"/>
+      <c r="AX33" s="4"/>
+      <c r="AY33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="3"/>
+      <c r="BB33" s="4"/>
+      <c r="BC33" s="5"/>
+      <c r="BD33" s="4"/>
+      <c r="BE33" s="4"/>
+      <c r="BF33" s="4"/>
+      <c r="BG33" s="4"/>
+      <c r="BH33" s="4"/>
+      <c r="BI33" s="4"/>
+      <c r="BJ33" s="4"/>
+      <c r="BK33" s="5"/>
+    </row>
+    <row r="34" spans="1:63" ht="14" customHeight="1">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="5"/>
+      <c r="AC34" s="4"/>
+      <c r="AD34" s="4"/>
+      <c r="AE34" s="4"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="3"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="5"/>
+      <c r="AL34" s="4"/>
+      <c r="AM34" s="4"/>
+      <c r="AN34" s="4"/>
+      <c r="AO34" s="3"/>
+      <c r="AP34" s="4"/>
+      <c r="AQ34" s="4"/>
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="4"/>
+      <c r="AT34" s="4"/>
+      <c r="AU34" s="3"/>
+      <c r="AV34" s="4"/>
+      <c r="AW34" s="5"/>
+      <c r="AX34" s="4"/>
+      <c r="AY34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="3"/>
+      <c r="BB34" s="4"/>
+      <c r="BC34" s="5"/>
+      <c r="BD34" s="4"/>
+      <c r="BE34" s="4"/>
+      <c r="BF34" s="4"/>
+      <c r="BG34" s="4"/>
+      <c r="BH34" s="4"/>
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="5"/>
+    </row>
+    <row r="35" spans="1:63" ht="14" customHeight="1">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="5"/>
+      <c r="AC35" s="4"/>
+      <c r="AD35" s="4"/>
+      <c r="AE35" s="4"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="4"/>
+      <c r="AH35" s="4"/>
+      <c r="AI35" s="3"/>
+      <c r="AJ35" s="4"/>
+      <c r="AK35" s="5"/>
+      <c r="AL35" s="4"/>
+      <c r="AM35" s="4"/>
+      <c r="AN35" s="4"/>
+      <c r="AO35" s="3"/>
+      <c r="AP35" s="4"/>
+      <c r="AQ35" s="4"/>
+      <c r="AR35" s="3"/>
+      <c r="AS35" s="4"/>
+      <c r="AT35" s="4"/>
+      <c r="AU35" s="3"/>
+      <c r="AV35" s="4"/>
+      <c r="AW35" s="5"/>
+      <c r="AX35" s="4"/>
+      <c r="AY35" s="4"/>
+      <c r="AZ35" s="4"/>
+      <c r="BA35" s="3"/>
+      <c r="BB35" s="4"/>
+      <c r="BC35" s="5"/>
+      <c r="BD35" s="4"/>
+      <c r="BE35" s="4"/>
+      <c r="BF35" s="4"/>
+      <c r="BG35" s="4"/>
+      <c r="BH35" s="4"/>
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="5"/>
+    </row>
+    <row r="36" spans="1:63" ht="14" customHeight="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="5"/>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="4"/>
+      <c r="AE36" s="4"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="4"/>
+      <c r="AH36" s="4"/>
+      <c r="AI36" s="3"/>
+      <c r="AJ36" s="4"/>
+      <c r="AK36" s="5"/>
+      <c r="AL36" s="4"/>
+      <c r="AM36" s="4"/>
+      <c r="AN36" s="4"/>
+      <c r="AO36" s="3"/>
+      <c r="AP36" s="4"/>
+      <c r="AQ36" s="4"/>
+      <c r="AR36" s="3"/>
+      <c r="AS36" s="4"/>
+      <c r="AT36" s="4"/>
+      <c r="AU36" s="3"/>
+      <c r="AV36" s="4"/>
+      <c r="AW36" s="5"/>
+      <c r="AX36" s="4"/>
+      <c r="AY36" s="4"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="3"/>
+      <c r="BB36" s="4"/>
+      <c r="BC36" s="5"/>
+      <c r="BD36" s="4"/>
+      <c r="BE36" s="4"/>
+      <c r="BF36" s="4"/>
+      <c r="BG36" s="4"/>
+      <c r="BH36" s="4"/>
+      <c r="BI36" s="4"/>
+      <c r="BJ36" s="4"/>
+      <c r="BK36" s="5"/>
+    </row>
+    <row r="37" spans="1:63" ht="14" customHeight="1">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="4"/>
+      <c r="AB37" s="5"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+      <c r="AE37" s="4"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="4"/>
+      <c r="AH37" s="4"/>
+      <c r="AI37" s="3"/>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="5"/>
+      <c r="AL37" s="4"/>
+      <c r="AM37" s="4"/>
+      <c r="AN37" s="4"/>
+      <c r="AO37" s="3"/>
+      <c r="AP37" s="4"/>
+      <c r="AQ37" s="4"/>
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="4"/>
+      <c r="AT37" s="4"/>
+      <c r="AU37" s="3"/>
+      <c r="AV37" s="4"/>
+      <c r="AW37" s="5"/>
+      <c r="AX37" s="4"/>
+      <c r="AY37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="3"/>
+      <c r="BB37" s="4"/>
+      <c r="BC37" s="5"/>
+      <c r="BD37" s="4"/>
+      <c r="BE37" s="4"/>
+      <c r="BF37" s="4"/>
+      <c r="BG37" s="4"/>
+      <c r="BH37" s="4"/>
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="5"/>
+    </row>
+    <row r="38" spans="1:63" ht="14" customHeight="1">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="5"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="3"/>
+      <c r="AJ38" s="4"/>
+      <c r="AK38" s="5"/>
+      <c r="AL38" s="4"/>
+      <c r="AM38" s="4"/>
+      <c r="AN38" s="4"/>
+      <c r="AO38" s="3"/>
+      <c r="AP38" s="4"/>
+      <c r="AQ38" s="4"/>
+      <c r="AR38" s="3"/>
+      <c r="AS38" s="4"/>
+      <c r="AT38" s="4"/>
+      <c r="AU38" s="3"/>
+      <c r="AV38" s="4"/>
+      <c r="AW38" s="5"/>
+      <c r="AX38" s="4"/>
+      <c r="AY38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="3"/>
+      <c r="BB38" s="4"/>
+      <c r="BC38" s="5"/>
+      <c r="BD38" s="4"/>
+      <c r="BE38" s="4"/>
+      <c r="BF38" s="4"/>
+      <c r="BG38" s="4"/>
+      <c r="BH38" s="4"/>
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="5"/>
+    </row>
+    <row r="39" spans="1:63" ht="14" customHeight="1">
+      <c r="A39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="5"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="4"/>
+      <c r="AH39" s="4"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="4"/>
+      <c r="AK39" s="5"/>
+      <c r="AL39" s="4"/>
+      <c r="AM39" s="4"/>
+      <c r="AN39" s="4"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="4"/>
+      <c r="AQ39" s="4"/>
+      <c r="AR39" s="3"/>
+      <c r="AS39" s="4"/>
+      <c r="AT39" s="4"/>
+      <c r="AU39" s="3"/>
+      <c r="AV39" s="4"/>
+      <c r="AW39" s="5"/>
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="3"/>
+      <c r="BB39" s="4"/>
+      <c r="BC39" s="5"/>
+      <c r="BD39" s="4"/>
+      <c r="BE39" s="4"/>
+      <c r="BF39" s="4"/>
+      <c r="BG39" s="4"/>
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="5"/>
+    </row>
+    <row r="40" spans="1:63" ht="14" customHeight="1">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="5"/>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="4"/>
+      <c r="AH40" s="4"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="4"/>
+      <c r="AK40" s="5"/>
+      <c r="AL40" s="4"/>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="4"/>
+      <c r="AR40" s="3"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="4"/>
+      <c r="AU40" s="3"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="5"/>
+      <c r="AX40" s="4"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="3"/>
+      <c r="BB40" s="4"/>
+      <c r="BC40" s="5"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="5"/>
+    </row>
+    <row r="41" spans="1:63" ht="14" customHeight="1">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="5"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="3"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="5"/>
+      <c r="AL41" s="4"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="3"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="4"/>
+      <c r="AR41" s="3"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="4"/>
+      <c r="AU41" s="3"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="5"/>
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="3"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="5"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="5"/>
+    </row>
+    <row r="42" spans="1:63" ht="14" customHeight="1">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="5"/>
+      <c r="AC42" s="4"/>
+      <c r="AD42" s="4"/>
+      <c r="AE42" s="4"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="4"/>
+      <c r="AH42" s="4"/>
+      <c r="AI42" s="3"/>
+      <c r="AJ42" s="4"/>
+      <c r="AK42" s="5"/>
+      <c r="AL42" s="4"/>
+      <c r="AM42" s="4"/>
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="3"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="3"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="3"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="5"/>
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="3"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="5"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="5"/>
+    </row>
+    <row r="43" spans="1:63" ht="14" customHeight="1">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="5"/>
+      <c r="AC43" s="4"/>
+      <c r="AD43" s="4"/>
+      <c r="AE43" s="4"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="4"/>
+      <c r="AH43" s="4"/>
+      <c r="AI43" s="3"/>
+      <c r="AJ43" s="4"/>
+      <c r="AK43" s="5"/>
+      <c r="AL43" s="4"/>
+      <c r="AM43" s="4"/>
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="3"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="3"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="3"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="5"/>
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="3"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="5"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="5"/>
+    </row>
+    <row r="44" spans="1:63" ht="14" customHeight="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="5"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="4"/>
+      <c r="AH44" s="4"/>
+      <c r="AI44" s="3"/>
+      <c r="AJ44" s="4"/>
+      <c r="AK44" s="5"/>
+      <c r="AL44" s="4"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="3"/>
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="4"/>
+      <c r="AU44" s="3"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="5"/>
+      <c r="AX44" s="4"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="3"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="5"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="5"/>
+    </row>
+    <row r="45" spans="1:63" ht="14" customHeight="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="5"/>
+      <c r="AC45" s="4"/>
+      <c r="AD45" s="4"/>
+      <c r="AE45" s="4"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="4"/>
+      <c r="AH45" s="4"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="4"/>
+      <c r="AK45" s="5"/>
+      <c r="AL45" s="4"/>
+      <c r="AM45" s="4"/>
+      <c r="AN45" s="4"/>
+      <c r="AO45" s="3"/>
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="4"/>
+      <c r="AR45" s="3"/>
+      <c r="AS45" s="4"/>
+      <c r="AT45" s="4"/>
+      <c r="AU45" s="3"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="5"/>
+      <c r="AX45" s="4"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="3"/>
+      <c r="BB45" s="4"/>
+      <c r="BC45" s="5"/>
+      <c r="BD45" s="4"/>
+      <c r="BE45" s="4"/>
+      <c r="BF45" s="4"/>
+      <c r="BG45" s="4"/>
+      <c r="BH45" s="4"/>
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
+  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
+    <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/build/Sample.xlsx
+++ b/build/Sample.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/Documents/Repos/golang/generateTables/build/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EEF6B8-80F4-DC42-88D0-39A9607F4928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8797DC-EDDC-DC45-BB60-0013B5012075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18180" yWindow="600" windowWidth="27880" windowHeight="17400" activeTab="1" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
+    <workbookView xWindow="1460" yWindow="600" windowWidth="27600" windowHeight="22820" activeTab="2" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="#SAMPLE" sheetId="16" r:id="rId1"/>
-    <sheet name="SAMPLE" sheetId="18" r:id="rId2"/>
-    <sheet name="@Sys" sheetId="17" r:id="rId3"/>
+    <sheet name="#SAMPLE" sheetId="19" r:id="rId1"/>
+    <sheet name="SAMPLE" sheetId="20" r:id="rId2"/>
+    <sheet name="@Sys" sheetId="21" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1377,11 +1377,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E23277E-66BF-4047-BD1E-7131CA4A8422}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC957C65-2EBD-8946-9E33-2CD07F8CE2F8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BK45"/>
+  <dimension ref="A1:BM45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -1389,10 +1389,8 @@
     <col min="31" max="16384" width="2.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="14" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="1" spans="1:65" ht="14" customHeight="1">
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1439,12 +1437,12 @@
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
       <c r="AW1" s="4"/>
       <c r="AX1" s="4"/>
@@ -1460,9 +1458,11 @@
       <c r="BH1" s="4"/>
       <c r="BI1" s="4"/>
       <c r="BJ1" s="4"/>
-      <c r="BK1" s="5"/>
-    </row>
-    <row r="2" spans="1:63" ht="14" customHeight="1">
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="5"/>
+    </row>
+    <row r="2" spans="1:65" ht="14" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -1512,10 +1512,10 @@
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="4"/>
-      <c r="AT2" s="4"/>
-      <c r="AU2" s="4"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="3"/>
       <c r="AV2" s="4"/>
       <c r="AW2" s="4"/>
       <c r="AX2" s="4"/>
@@ -1531,9 +1531,11 @@
       <c r="BH2" s="4"/>
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
-      <c r="BK2" s="5"/>
-    </row>
-    <row r="3" spans="1:63" ht="14" customHeight="1">
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="4"/>
+      <c r="BM2" s="5"/>
+    </row>
+    <row r="3" spans="1:65" ht="14" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1583,10 +1585,10 @@
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2"/>
+      <c r="AU3" s="3"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="4"/>
       <c r="AX3" s="4"/>
@@ -1602,9 +1604,11 @@
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
-      <c r="BK3" s="5"/>
-    </row>
-    <row r="4" spans="1:63" ht="14" customHeight="1">
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="5"/>
+    </row>
+    <row r="4" spans="1:65" ht="14" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -1669,13 +1673,15 @@
       <c r="BH4" s="8"/>
       <c r="BI4" s="8"/>
       <c r="BJ4" s="8"/>
-      <c r="BK4" s="9"/>
-    </row>
-    <row r="5" spans="1:63" ht="14" customHeight="1">
+      <c r="BK4" s="8"/>
+      <c r="BL4" s="8"/>
+      <c r="BM4" s="9"/>
+    </row>
+    <row r="5" spans="1:65" ht="14" customHeight="1">
       <c r="A5" s="10"/>
-      <c r="BK5" s="11"/>
-    </row>
-    <row r="6" spans="1:63" ht="14" customHeight="1">
+      <c r="BM5" s="11"/>
+    </row>
+    <row r="6" spans="1:65" ht="14" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1738,9 +1744,11 @@
       <c r="BH6" s="13"/>
       <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="14"/>
-    </row>
-    <row r="8" spans="1:63" ht="14" customHeight="1">
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="14"/>
+    </row>
+    <row r="8" spans="1:65" ht="14" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
@@ -1783,12 +1791,12 @@
       <c r="AF8" s="17"/>
       <c r="AG8" s="17"/>
       <c r="AH8" s="17"/>
-      <c r="AI8" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
+      <c r="AL8" s="15" t="s">
+        <v>8</v>
+      </c>
       <c r="AM8" s="17"/>
       <c r="AN8" s="17"/>
       <c r="AO8" s="17"/>
@@ -1799,29 +1807,31 @@
       <c r="AT8" s="17"/>
       <c r="AU8" s="17"/>
       <c r="AV8" s="17"/>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="15" t="s">
+      <c r="AW8" s="17"/>
+      <c r="AX8" s="17"/>
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="15" t="s">
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="17"/>
+      <c r="BD8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="16"/>
-      <c r="BD8" s="17" t="s">
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="16"/>
+      <c r="BG8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="17"/>
       <c r="BH8" s="17"/>
       <c r="BI8" s="17"/>
       <c r="BJ8" s="17"/>
-      <c r="BK8" s="16"/>
-    </row>
-    <row r="9" spans="1:63" ht="14" customHeight="1">
+      <c r="BK8" s="17"/>
+      <c r="BL8" s="17"/>
+      <c r="BM8" s="16"/>
+    </row>
+    <row r="9" spans="1:65" ht="14" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="20"/>
       <c r="C9" s="18" t="s">
@@ -1877,46 +1887,50 @@
       <c r="AG9" s="20"/>
       <c r="AH9" s="20"/>
       <c r="AI9" s="18" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
-      <c r="AL9" s="20" t="s">
+      <c r="AL9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="AM9" s="20"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="18" t="s">
-        <v>27</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="20"/>
       <c r="AU9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AV9" s="20"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="18"/>
       <c r="AY9" s="20"/>
-      <c r="AZ9" s="20"/>
+      <c r="AZ9" s="19"/>
       <c r="BA9" s="18"/>
       <c r="BB9" s="20"/>
-      <c r="BC9" s="19"/>
-      <c r="BD9" s="20"/>
+      <c r="BC9" s="20"/>
+      <c r="BD9" s="18"/>
       <c r="BE9" s="20"/>
-      <c r="BF9" s="20"/>
+      <c r="BF9" s="19"/>
       <c r="BG9" s="20"/>
       <c r="BH9" s="20"/>
       <c r="BI9" s="20"/>
       <c r="BJ9" s="20"/>
-      <c r="BK9" s="19"/>
-    </row>
-    <row r="10" spans="1:63" ht="14" customHeight="1">
+      <c r="BK9" s="20"/>
+      <c r="BL9" s="20"/>
+      <c r="BM9" s="19"/>
+    </row>
+    <row r="10" spans="1:65" ht="14" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1969,47 +1983,49 @@
       </c>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
-      <c r="AI10" s="18" t="s">
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="13"/>
+      <c r="AK10" s="14"/>
+      <c r="AL10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
-      <c r="AN10" s="4"/>
-      <c r="AO10" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="4"/>
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
-      <c r="AR10" s="3"/>
+      <c r="AR10" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AS10" s="4"/>
-      <c r="AT10" s="5"/>
+      <c r="AT10" s="4"/>
       <c r="AU10" s="3"/>
       <c r="AV10" s="4"/>
       <c r="AW10" s="5"/>
-      <c r="AX10" s="4" t="s">
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="5"/>
+      <c r="BA10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="4"/>
-      <c r="BA10" s="3" t="s">
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="BB10" s="4"/>
-      <c r="BC10" s="5"/>
-      <c r="BD10" s="4" t="s">
+      <c r="BE10" s="4"/>
+      <c r="BF10" s="5"/>
+      <c r="BG10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="BE10" s="4"/>
-      <c r="BF10" s="4"/>
-      <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
       <c r="BI10" s="4"/>
       <c r="BJ10" s="4"/>
-      <c r="BK10" s="5"/>
-    </row>
-    <row r="11" spans="1:63" ht="14" customHeight="1">
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+      <c r="BM10" s="5"/>
+    </row>
+    <row r="11" spans="1:65" ht="14" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -2060,45 +2076,47 @@
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
-      <c r="AI11" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="AI11" s="3"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5"/>
-      <c r="AL11" s="4"/>
+      <c r="AL11" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="AM11" s="4"/>
-      <c r="AN11" s="4"/>
-      <c r="AO11" s="3"/>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="4"/>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="3"/>
       <c r="AS11" s="4"/>
-      <c r="AT11" s="5"/>
+      <c r="AT11" s="4"/>
       <c r="AU11" s="3"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
-      <c r="AX11" s="4" t="s">
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="5"/>
+      <c r="BA11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="4"/>
-      <c r="BA11" s="3" t="s">
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="5"/>
-      <c r="BD11" s="4" t="s">
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="5"/>
+      <c r="BG11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="BE11" s="4"/>
-      <c r="BF11" s="4"/>
-      <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
       <c r="BI11" s="4"/>
       <c r="BJ11" s="4"/>
-      <c r="BK11" s="5"/>
-    </row>
-    <row r="12" spans="1:63" ht="14" customHeight="1">
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+      <c r="BM11" s="5"/>
+    </row>
+    <row r="12" spans="1:65" ht="14" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -2147,43 +2165,45 @@
       </c>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
-      <c r="AI12" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="AI12" s="3"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="4"/>
+      <c r="AL12" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="AM12" s="4"/>
-      <c r="AN12" s="4"/>
-      <c r="AO12" s="3"/>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="4"/>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="3"/>
       <c r="AS12" s="4"/>
-      <c r="AT12" s="5"/>
+      <c r="AT12" s="4"/>
       <c r="AU12" s="3"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="4" t="s">
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="5"/>
+      <c r="BA12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AY12" s="4"/>
-      <c r="AZ12" s="4"/>
-      <c r="BA12" s="3" t="s">
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+      <c r="BD12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="BB12" s="4"/>
-      <c r="BC12" s="5"/>
-      <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
-      <c r="BF12" s="4"/>
+      <c r="BF12" s="5"/>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
       <c r="BI12" s="4"/>
       <c r="BJ12" s="4"/>
-      <c r="BK12" s="5"/>
-    </row>
-    <row r="13" spans="1:63" ht="14" customHeight="1">
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+      <c r="BM12" s="5"/>
+    </row>
+    <row r="13" spans="1:65" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -2229,36 +2249,38 @@
       <c r="AI13" s="3"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5"/>
-      <c r="AL13" s="4"/>
+      <c r="AL13" s="3"/>
       <c r="AM13" s="4"/>
-      <c r="AN13" s="4"/>
-      <c r="AO13" s="3"/>
+      <c r="AN13" s="5"/>
+      <c r="AO13" s="4"/>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="3"/>
       <c r="AS13" s="4"/>
-      <c r="AT13" s="5"/>
+      <c r="AT13" s="4"/>
       <c r="AU13" s="3"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-      <c r="AX13" s="4"/>
+      <c r="AX13" s="3"/>
       <c r="AY13" s="4"/>
-      <c r="AZ13" s="4"/>
-      <c r="BA13" s="3"/>
+      <c r="AZ13" s="5"/>
+      <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
-      <c r="BC13" s="5"/>
-      <c r="BD13" s="4" t="s">
+      <c r="BC13" s="4"/>
+      <c r="BD13" s="3"/>
+      <c r="BE13" s="4"/>
+      <c r="BF13" s="5"/>
+      <c r="BG13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BE13" s="4"/>
-      <c r="BF13" s="4"/>
-      <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
       <c r="BI13" s="4"/>
       <c r="BJ13" s="4"/>
-      <c r="BK13" s="5"/>
-    </row>
-    <row r="14" spans="1:63" ht="14" customHeight="1">
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+      <c r="BM13" s="5"/>
+    </row>
+    <row r="14" spans="1:65" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -2304,34 +2326,36 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5"/>
-      <c r="AL14" s="4"/>
+      <c r="AL14" s="3"/>
       <c r="AM14" s="4"/>
-      <c r="AN14" s="4"/>
-      <c r="AO14" s="3"/>
+      <c r="AN14" s="5"/>
+      <c r="AO14" s="4"/>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="3"/>
       <c r="AS14" s="4"/>
-      <c r="AT14" s="5"/>
+      <c r="AT14" s="4"/>
       <c r="AU14" s="3"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-      <c r="AX14" s="4"/>
+      <c r="AX14" s="3"/>
       <c r="AY14" s="4"/>
-      <c r="AZ14" s="4"/>
-      <c r="BA14" s="3"/>
+      <c r="AZ14" s="5"/>
+      <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
-      <c r="BC14" s="5"/>
-      <c r="BD14" s="4"/>
+      <c r="BC14" s="4"/>
+      <c r="BD14" s="3"/>
       <c r="BE14" s="4"/>
-      <c r="BF14" s="4"/>
+      <c r="BF14" s="5"/>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
       <c r="BI14" s="4"/>
       <c r="BJ14" s="4"/>
-      <c r="BK14" s="5"/>
-    </row>
-    <row r="15" spans="1:63" ht="14" customHeight="1">
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+      <c r="BM14" s="5"/>
+    </row>
+    <row r="15" spans="1:65" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -2377,34 +2401,36 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5"/>
-      <c r="AL15" s="4"/>
+      <c r="AL15" s="3"/>
       <c r="AM15" s="4"/>
-      <c r="AN15" s="4"/>
-      <c r="AO15" s="3"/>
+      <c r="AN15" s="5"/>
+      <c r="AO15" s="4"/>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="3"/>
       <c r="AS15" s="4"/>
-      <c r="AT15" s="5"/>
+      <c r="AT15" s="4"/>
       <c r="AU15" s="3"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-      <c r="AX15" s="4"/>
+      <c r="AX15" s="3"/>
       <c r="AY15" s="4"/>
-      <c r="AZ15" s="4"/>
-      <c r="BA15" s="3"/>
+      <c r="AZ15" s="5"/>
+      <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
-      <c r="BC15" s="5"/>
-      <c r="BD15" s="4"/>
+      <c r="BC15" s="4"/>
+      <c r="BD15" s="3"/>
       <c r="BE15" s="4"/>
-      <c r="BF15" s="4"/>
+      <c r="BF15" s="5"/>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
       <c r="BI15" s="4"/>
       <c r="BJ15" s="4"/>
-      <c r="BK15" s="5"/>
-    </row>
-    <row r="16" spans="1:63" ht="14" customHeight="1">
+      <c r="BK15" s="4"/>
+      <c r="BL15" s="4"/>
+      <c r="BM15" s="5"/>
+    </row>
+    <row r="16" spans="1:65" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -2447,43 +2473,45 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
-      <c r="AI16" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="AI16" s="3"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
-      <c r="AL16" s="4"/>
+      <c r="AL16" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="AM16" s="4"/>
-      <c r="AN16" s="4"/>
-      <c r="AO16" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="AN16" s="5"/>
+      <c r="AO16" s="4"/>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
-      <c r="AR16" s="3"/>
+      <c r="AR16" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="AS16" s="4"/>
-      <c r="AT16" s="5"/>
+      <c r="AT16" s="4"/>
       <c r="AU16" s="3"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
-      <c r="AX16" s="4"/>
+      <c r="AX16" s="3"/>
       <c r="AY16" s="4"/>
-      <c r="AZ16" s="4"/>
-      <c r="BA16" s="3"/>
+      <c r="AZ16" s="5"/>
+      <c r="BA16" s="4"/>
       <c r="BB16" s="4"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="4" t="s">
+      <c r="BC16" s="4"/>
+      <c r="BD16" s="3"/>
+      <c r="BE16" s="4"/>
+      <c r="BF16" s="5"/>
+      <c r="BG16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE16" s="4"/>
-      <c r="BF16" s="4"/>
-      <c r="BG16" s="4"/>
       <c r="BH16" s="4"/>
       <c r="BI16" s="4"/>
       <c r="BJ16" s="4"/>
-      <c r="BK16" s="5"/>
-    </row>
-    <row r="17" spans="1:63" ht="14" customHeight="1">
+      <c r="BK16" s="4"/>
+      <c r="BL16" s="4"/>
+      <c r="BM16" s="5"/>
+    </row>
+    <row r="17" spans="1:65" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -2524,43 +2552,45 @@
       <c r="AF17" s="3"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
-      <c r="AI17" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="AI17" s="3"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
-      <c r="AL17" s="4"/>
+      <c r="AL17" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="AM17" s="4"/>
-      <c r="AN17" s="4"/>
-      <c r="AO17" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="AN17" s="5"/>
+      <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
-      <c r="AR17" s="3"/>
+      <c r="AR17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="AS17" s="4"/>
-      <c r="AT17" s="5"/>
+      <c r="AT17" s="4"/>
       <c r="AU17" s="3"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="5"/>
-      <c r="AX17" s="4"/>
+      <c r="AX17" s="3"/>
       <c r="AY17" s="4"/>
-      <c r="AZ17" s="4"/>
-      <c r="BA17" s="3"/>
+      <c r="AZ17" s="5"/>
+      <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="4" t="s">
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="3"/>
+      <c r="BE17" s="4"/>
+      <c r="BF17" s="5"/>
+      <c r="BG17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE17" s="4"/>
-      <c r="BF17" s="4"/>
-      <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
       <c r="BI17" s="4"/>
       <c r="BJ17" s="4"/>
-      <c r="BK17" s="5"/>
-    </row>
-    <row r="18" spans="1:63" ht="14" customHeight="1">
+      <c r="BK17" s="4"/>
+      <c r="BL17" s="4"/>
+      <c r="BM17" s="5"/>
+    </row>
+    <row r="18" spans="1:65" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -2604,36 +2634,38 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5"/>
-      <c r="AL18" s="4"/>
+      <c r="AL18" s="3"/>
       <c r="AM18" s="4"/>
-      <c r="AN18" s="4"/>
-      <c r="AO18" s="3"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="4"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="3"/>
       <c r="AS18" s="4"/>
-      <c r="AT18" s="5"/>
+      <c r="AT18" s="4"/>
       <c r="AU18" s="3"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="4"/>
+      <c r="AX18" s="3"/>
       <c r="AY18" s="4"/>
-      <c r="AZ18" s="4"/>
-      <c r="BA18" s="3"/>
+      <c r="AZ18" s="5"/>
+      <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="4" t="s">
+      <c r="BC18" s="4"/>
+      <c r="BD18" s="3"/>
+      <c r="BE18" s="4"/>
+      <c r="BF18" s="5"/>
+      <c r="BG18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE18" s="4"/>
-      <c r="BF18" s="4"/>
-      <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>
       <c r="BJ18" s="4"/>
-      <c r="BK18" s="5"/>
-    </row>
-    <row r="19" spans="1:63" ht="14" customHeight="1">
+      <c r="BK18" s="4"/>
+      <c r="BL18" s="4"/>
+      <c r="BM18" s="5"/>
+    </row>
+    <row r="19" spans="1:65" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -2677,36 +2709,38 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5"/>
-      <c r="AL19" s="4"/>
+      <c r="AL19" s="3"/>
       <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="3"/>
+      <c r="AN19" s="5"/>
+      <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="3"/>
       <c r="AS19" s="4"/>
-      <c r="AT19" s="5"/>
+      <c r="AT19" s="4"/>
       <c r="AU19" s="3"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
-      <c r="AX19" s="4"/>
+      <c r="AX19" s="3"/>
       <c r="AY19" s="4"/>
-      <c r="AZ19" s="4"/>
-      <c r="BA19" s="3"/>
+      <c r="AZ19" s="5"/>
+      <c r="BA19" s="4"/>
       <c r="BB19" s="4"/>
-      <c r="BC19" s="5"/>
-      <c r="BD19" s="4" t="s">
+      <c r="BC19" s="4"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="4"/>
+      <c r="BF19" s="5"/>
+      <c r="BG19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE19" s="4"/>
-      <c r="BF19" s="4"/>
-      <c r="BG19" s="4"/>
       <c r="BH19" s="4"/>
       <c r="BI19" s="4"/>
       <c r="BJ19" s="4"/>
-      <c r="BK19" s="5"/>
-    </row>
-    <row r="20" spans="1:63" ht="14" customHeight="1">
+      <c r="BK19" s="4"/>
+      <c r="BL19" s="4"/>
+      <c r="BM19" s="5"/>
+    </row>
+    <row r="20" spans="1:65" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -2750,36 +2784,38 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5"/>
-      <c r="AL20" s="4"/>
+      <c r="AL20" s="3"/>
       <c r="AM20" s="4"/>
-      <c r="AN20" s="4"/>
-      <c r="AO20" s="3"/>
+      <c r="AN20" s="5"/>
+      <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="4"/>
-      <c r="AT20" s="5"/>
+      <c r="AT20" s="4"/>
       <c r="AU20" s="3"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
-      <c r="AX20" s="4"/>
+      <c r="AX20" s="3"/>
       <c r="AY20" s="4"/>
-      <c r="AZ20" s="4"/>
-      <c r="BA20" s="3"/>
+      <c r="AZ20" s="5"/>
+      <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="4" t="s">
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="3"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="5"/>
+      <c r="BG20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE20" s="4"/>
-      <c r="BF20" s="4"/>
-      <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
       <c r="BJ20" s="4"/>
-      <c r="BK20" s="5"/>
-    </row>
-    <row r="21" spans="1:63" ht="14" customHeight="1">
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+      <c r="BM20" s="5"/>
+    </row>
+    <row r="21" spans="1:65" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
@@ -2823,36 +2859,38 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5"/>
-      <c r="AL21" s="4"/>
+      <c r="AL21" s="3"/>
       <c r="AM21" s="4"/>
-      <c r="AN21" s="4"/>
-      <c r="AO21" s="3"/>
+      <c r="AN21" s="5"/>
+      <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="4"/>
-      <c r="AT21" s="5"/>
+      <c r="AT21" s="4"/>
       <c r="AU21" s="3"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="4"/>
+      <c r="AX21" s="3"/>
       <c r="AY21" s="4"/>
-      <c r="AZ21" s="4"/>
-      <c r="BA21" s="3"/>
+      <c r="AZ21" s="5"/>
+      <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="4" t="s">
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="3"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="5"/>
+      <c r="BG21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE21" s="4"/>
-      <c r="BF21" s="4"/>
-      <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
       <c r="BJ21" s="4"/>
-      <c r="BK21" s="5"/>
-    </row>
-    <row r="22" spans="1:63" ht="14" customHeight="1">
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+      <c r="BM21" s="5"/>
+    </row>
+    <row r="22" spans="1:65" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -2900,36 +2938,38 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5"/>
-      <c r="AL22" s="4"/>
+      <c r="AL22" s="3"/>
       <c r="AM22" s="4"/>
-      <c r="AN22" s="4"/>
-      <c r="AO22" s="3"/>
+      <c r="AN22" s="5"/>
+      <c r="AO22" s="4"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="3"/>
       <c r="AS22" s="4"/>
-      <c r="AT22" s="5"/>
+      <c r="AT22" s="4"/>
       <c r="AU22" s="3"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
-      <c r="AX22" s="4"/>
+      <c r="AX22" s="3"/>
       <c r="AY22" s="4"/>
-      <c r="AZ22" s="4"/>
-      <c r="BA22" s="3"/>
+      <c r="AZ22" s="5"/>
+      <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="4" t="s">
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="3"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="5"/>
+      <c r="BG22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BE22" s="4"/>
-      <c r="BF22" s="4"/>
-      <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
       <c r="BJ22" s="4"/>
-      <c r="BK22" s="5"/>
-    </row>
-    <row r="23" spans="1:63" ht="14" customHeight="1">
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="5"/>
+    </row>
+    <row r="23" spans="1:65" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -2977,36 +3017,38 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5"/>
-      <c r="AL23" s="4"/>
+      <c r="AL23" s="3"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="4"/>
-      <c r="AO23" s="3"/>
+      <c r="AN23" s="5"/>
+      <c r="AO23" s="4"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
-      <c r="AR23" s="24"/>
-      <c r="AS23" s="21"/>
-      <c r="AT23" s="5"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4"/>
       <c r="AU23" s="24"/>
       <c r="AV23" s="21"/>
       <c r="AW23" s="5"/>
-      <c r="AX23" s="4"/>
-      <c r="AY23" s="4"/>
-      <c r="AZ23" s="4"/>
-      <c r="BA23" s="3"/>
+      <c r="AX23" s="24"/>
+      <c r="AY23" s="21"/>
+      <c r="AZ23" s="5"/>
+      <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="4" t="s">
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="3"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="5"/>
+      <c r="BG23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE23" s="4"/>
-      <c r="BF23" s="4"/>
-      <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
       <c r="BJ23" s="4"/>
-      <c r="BK23" s="5"/>
-    </row>
-    <row r="24" spans="1:63" ht="14" customHeight="1">
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+      <c r="BM23" s="5"/>
+    </row>
+    <row r="24" spans="1:65" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -3054,36 +3096,38 @@
       <c r="AI24" s="3"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5"/>
-      <c r="AL24" s="4"/>
+      <c r="AL24" s="3"/>
       <c r="AM24" s="4"/>
-      <c r="AN24" s="4"/>
-      <c r="AO24" s="3"/>
+      <c r="AN24" s="5"/>
+      <c r="AO24" s="4"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="4"/>
-      <c r="AT24" s="5"/>
+      <c r="AT24" s="4"/>
       <c r="AU24" s="3"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
-      <c r="AX24" s="4"/>
+      <c r="AX24" s="3"/>
       <c r="AY24" s="4"/>
-      <c r="AZ24" s="4"/>
-      <c r="BA24" s="3"/>
+      <c r="AZ24" s="5"/>
+      <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="4" t="s">
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="3"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="5"/>
+      <c r="BG24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE24" s="4"/>
-      <c r="BF24" s="4"/>
-      <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
-      <c r="BK24" s="5"/>
-    </row>
-    <row r="25" spans="1:63" ht="14" customHeight="1">
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+      <c r="BM24" s="5"/>
+    </row>
+    <row r="25" spans="1:65" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -3131,36 +3175,38 @@
       <c r="AI25" s="3"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5"/>
-      <c r="AL25" s="4"/>
+      <c r="AL25" s="3"/>
       <c r="AM25" s="4"/>
-      <c r="AN25" s="4"/>
-      <c r="AO25" s="3"/>
+      <c r="AN25" s="5"/>
+      <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="4"/>
-      <c r="AT25" s="5"/>
+      <c r="AT25" s="4"/>
       <c r="AU25" s="3"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="5"/>
-      <c r="AX25" s="4"/>
+      <c r="AX25" s="3"/>
       <c r="AY25" s="4"/>
-      <c r="AZ25" s="4"/>
-      <c r="BA25" s="3"/>
+      <c r="AZ25" s="5"/>
+      <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="4" t="s">
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="5"/>
+      <c r="BG25" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE25" s="4"/>
-      <c r="BF25" s="4"/>
-      <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
-      <c r="BK25" s="5"/>
-    </row>
-    <row r="26" spans="1:63" ht="14" customHeight="1">
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+      <c r="BM25" s="5"/>
+    </row>
+    <row r="26" spans="1:65" ht="14" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>78</v>
       </c>
@@ -3208,36 +3254,38 @@
       <c r="AI26" s="3"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5"/>
-      <c r="AL26" s="4"/>
+      <c r="AL26" s="3"/>
       <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="3"/>
+      <c r="AN26" s="5"/>
+      <c r="AO26" s="4"/>
       <c r="AP26" s="4"/>
       <c r="AQ26" s="4"/>
       <c r="AR26" s="3"/>
       <c r="AS26" s="4"/>
-      <c r="AT26" s="5"/>
+      <c r="AT26" s="4"/>
       <c r="AU26" s="3"/>
       <c r="AV26" s="4"/>
       <c r="AW26" s="5"/>
-      <c r="AX26" s="4"/>
+      <c r="AX26" s="3"/>
       <c r="AY26" s="4"/>
-      <c r="AZ26" s="4"/>
-      <c r="BA26" s="3"/>
+      <c r="AZ26" s="5"/>
+      <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="4" t="s">
+      <c r="BC26" s="4"/>
+      <c r="BD26" s="3"/>
+      <c r="BE26" s="4"/>
+      <c r="BF26" s="5"/>
+      <c r="BG26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BE26" s="4"/>
-      <c r="BF26" s="4"/>
-      <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
       <c r="BJ26" s="4"/>
-      <c r="BK26" s="5"/>
-    </row>
-    <row r="27" spans="1:63" ht="14" customHeight="1">
+      <c r="BK26" s="4"/>
+      <c r="BL26" s="4"/>
+      <c r="BM26" s="5"/>
+    </row>
+    <row r="27" spans="1:65" ht="14" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>79</v>
       </c>
@@ -3285,36 +3333,38 @@
       <c r="AI27" s="3"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5"/>
-      <c r="AL27" s="4"/>
+      <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="3"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="4"/>
       <c r="AP27" s="4"/>
       <c r="AQ27" s="4"/>
-      <c r="AR27" s="24"/>
-      <c r="AS27" s="21"/>
-      <c r="AT27" s="5"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="4"/>
+      <c r="AT27" s="4"/>
       <c r="AU27" s="24"/>
       <c r="AV27" s="21"/>
       <c r="AW27" s="5"/>
-      <c r="AX27" s="4"/>
-      <c r="AY27" s="4"/>
-      <c r="AZ27" s="4"/>
-      <c r="BA27" s="3"/>
+      <c r="AX27" s="24"/>
+      <c r="AY27" s="21"/>
+      <c r="AZ27" s="5"/>
+      <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="4" t="s">
+      <c r="BC27" s="4"/>
+      <c r="BD27" s="3"/>
+      <c r="BE27" s="4"/>
+      <c r="BF27" s="5"/>
+      <c r="BG27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE27" s="4"/>
-      <c r="BF27" s="4"/>
-      <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
       <c r="BJ27" s="4"/>
-      <c r="BK27" s="5"/>
-    </row>
-    <row r="28" spans="1:63" ht="14" customHeight="1">
+      <c r="BK27" s="4"/>
+      <c r="BL27" s="4"/>
+      <c r="BM27" s="5"/>
+    </row>
+    <row r="28" spans="1:65" ht="14" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>80</v>
       </c>
@@ -3362,36 +3412,38 @@
       <c r="AI28" s="3"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5"/>
-      <c r="AL28" s="4"/>
+      <c r="AL28" s="3"/>
       <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="3"/>
+      <c r="AN28" s="5"/>
+      <c r="AO28" s="4"/>
       <c r="AP28" s="4"/>
       <c r="AQ28" s="4"/>
       <c r="AR28" s="3"/>
       <c r="AS28" s="4"/>
-      <c r="AT28" s="5"/>
+      <c r="AT28" s="4"/>
       <c r="AU28" s="3"/>
       <c r="AV28" s="4"/>
       <c r="AW28" s="5"/>
-      <c r="AX28" s="4"/>
+      <c r="AX28" s="3"/>
       <c r="AY28" s="4"/>
-      <c r="AZ28" s="4"/>
-      <c r="BA28" s="3"/>
+      <c r="AZ28" s="5"/>
+      <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="4" t="s">
+      <c r="BC28" s="4"/>
+      <c r="BD28" s="3"/>
+      <c r="BE28" s="4"/>
+      <c r="BF28" s="5"/>
+      <c r="BG28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE28" s="4"/>
-      <c r="BF28" s="4"/>
-      <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
       <c r="BJ28" s="4"/>
-      <c r="BK28" s="5"/>
-    </row>
-    <row r="29" spans="1:63" ht="14" customHeight="1">
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+      <c r="BM28" s="5"/>
+    </row>
+    <row r="29" spans="1:65" ht="14" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>81</v>
       </c>
@@ -3439,36 +3491,38 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5"/>
-      <c r="AL29" s="4"/>
+      <c r="AL29" s="3"/>
       <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="3"/>
+      <c r="AN29" s="5"/>
+      <c r="AO29" s="4"/>
       <c r="AP29" s="4"/>
       <c r="AQ29" s="4"/>
       <c r="AR29" s="3"/>
       <c r="AS29" s="4"/>
-      <c r="AT29" s="5"/>
+      <c r="AT29" s="4"/>
       <c r="AU29" s="3"/>
       <c r="AV29" s="4"/>
       <c r="AW29" s="5"/>
-      <c r="AX29" s="4"/>
+      <c r="AX29" s="3"/>
       <c r="AY29" s="4"/>
-      <c r="AZ29" s="4"/>
-      <c r="BA29" s="3"/>
+      <c r="AZ29" s="5"/>
+      <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="4" t="s">
+      <c r="BC29" s="4"/>
+      <c r="BD29" s="3"/>
+      <c r="BE29" s="4"/>
+      <c r="BF29" s="5"/>
+      <c r="BG29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE29" s="4"/>
-      <c r="BF29" s="4"/>
-      <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="4"/>
-      <c r="BK29" s="5"/>
-    </row>
-    <row r="30" spans="1:63" ht="14" customHeight="1">
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+      <c r="BM29" s="5"/>
+    </row>
+    <row r="30" spans="1:65" ht="14" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -3506,34 +3560,36 @@
       <c r="AI30" s="3"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5"/>
-      <c r="AL30" s="4"/>
+      <c r="AL30" s="3"/>
       <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="3"/>
+      <c r="AN30" s="5"/>
+      <c r="AO30" s="4"/>
       <c r="AP30" s="4"/>
       <c r="AQ30" s="4"/>
       <c r="AR30" s="3"/>
       <c r="AS30" s="4"/>
-      <c r="AT30" s="5"/>
+      <c r="AT30" s="4"/>
       <c r="AU30" s="3"/>
       <c r="AV30" s="4"/>
       <c r="AW30" s="5"/>
-      <c r="AX30" s="4"/>
+      <c r="AX30" s="3"/>
       <c r="AY30" s="4"/>
-      <c r="AZ30" s="4"/>
-      <c r="BA30" s="3"/>
+      <c r="AZ30" s="5"/>
+      <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="4"/>
+      <c r="BC30" s="4"/>
+      <c r="BD30" s="3"/>
       <c r="BE30" s="4"/>
-      <c r="BF30" s="4"/>
+      <c r="BF30" s="5"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="4"/>
-      <c r="BK30" s="5"/>
-    </row>
-    <row r="31" spans="1:63" ht="14" customHeight="1">
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+      <c r="BM30" s="5"/>
+    </row>
+    <row r="31" spans="1:65" ht="14" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -3571,34 +3627,36 @@
       <c r="AI31" s="3"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5"/>
-      <c r="AL31" s="4"/>
+      <c r="AL31" s="3"/>
       <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="3"/>
+      <c r="AN31" s="5"/>
+      <c r="AO31" s="4"/>
       <c r="AP31" s="4"/>
       <c r="AQ31" s="4"/>
       <c r="AR31" s="3"/>
       <c r="AS31" s="4"/>
-      <c r="AT31" s="5"/>
+      <c r="AT31" s="4"/>
       <c r="AU31" s="3"/>
       <c r="AV31" s="4"/>
       <c r="AW31" s="5"/>
-      <c r="AX31" s="4"/>
+      <c r="AX31" s="3"/>
       <c r="AY31" s="4"/>
-      <c r="AZ31" s="4"/>
-      <c r="BA31" s="3"/>
+      <c r="AZ31" s="5"/>
+      <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="4"/>
+      <c r="BC31" s="4"/>
+      <c r="BD31" s="3"/>
       <c r="BE31" s="4"/>
-      <c r="BF31" s="4"/>
+      <c r="BF31" s="5"/>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="4"/>
-      <c r="BK31" s="5"/>
-    </row>
-    <row r="32" spans="1:63" ht="14" customHeight="1">
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+      <c r="BM31" s="5"/>
+    </row>
+    <row r="32" spans="1:65" ht="14" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -3636,34 +3694,36 @@
       <c r="AI32" s="3"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="5"/>
-      <c r="AL32" s="4"/>
+      <c r="AL32" s="3"/>
       <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="3"/>
+      <c r="AN32" s="5"/>
+      <c r="AO32" s="4"/>
       <c r="AP32" s="4"/>
       <c r="AQ32" s="4"/>
       <c r="AR32" s="3"/>
       <c r="AS32" s="4"/>
-      <c r="AT32" s="5"/>
+      <c r="AT32" s="4"/>
       <c r="AU32" s="3"/>
       <c r="AV32" s="4"/>
       <c r="AW32" s="5"/>
-      <c r="AX32" s="4"/>
+      <c r="AX32" s="3"/>
       <c r="AY32" s="4"/>
-      <c r="AZ32" s="4"/>
-      <c r="BA32" s="3"/>
+      <c r="AZ32" s="5"/>
+      <c r="BA32" s="4"/>
       <c r="BB32" s="4"/>
-      <c r="BC32" s="5"/>
-      <c r="BD32" s="4"/>
+      <c r="BC32" s="4"/>
+      <c r="BD32" s="3"/>
       <c r="BE32" s="4"/>
-      <c r="BF32" s="4"/>
+      <c r="BF32" s="5"/>
       <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
       <c r="BJ32" s="4"/>
-      <c r="BK32" s="5"/>
-    </row>
-    <row r="33" spans="1:63" ht="14" customHeight="1">
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+      <c r="BM32" s="5"/>
+    </row>
+    <row r="33" spans="1:65" ht="14" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -3701,34 +3761,36 @@
       <c r="AI33" s="3"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="5"/>
-      <c r="AL33" s="4"/>
+      <c r="AL33" s="3"/>
       <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="3"/>
+      <c r="AN33" s="5"/>
+      <c r="AO33" s="4"/>
       <c r="AP33" s="4"/>
       <c r="AQ33" s="4"/>
       <c r="AR33" s="3"/>
       <c r="AS33" s="4"/>
-      <c r="AT33" s="5"/>
+      <c r="AT33" s="4"/>
       <c r="AU33" s="3"/>
       <c r="AV33" s="4"/>
       <c r="AW33" s="5"/>
-      <c r="AX33" s="4"/>
+      <c r="AX33" s="3"/>
       <c r="AY33" s="4"/>
-      <c r="AZ33" s="4"/>
-      <c r="BA33" s="3"/>
+      <c r="AZ33" s="5"/>
+      <c r="BA33" s="4"/>
       <c r="BB33" s="4"/>
-      <c r="BC33" s="5"/>
-      <c r="BD33" s="4"/>
+      <c r="BC33" s="4"/>
+      <c r="BD33" s="3"/>
       <c r="BE33" s="4"/>
-      <c r="BF33" s="4"/>
+      <c r="BF33" s="5"/>
       <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
       <c r="BJ33" s="4"/>
-      <c r="BK33" s="5"/>
-    </row>
-    <row r="34" spans="1:63" ht="14" customHeight="1">
+      <c r="BK33" s="4"/>
+      <c r="BL33" s="4"/>
+      <c r="BM33" s="5"/>
+    </row>
+    <row r="34" spans="1:65" ht="14" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -3766,34 +3828,36 @@
       <c r="AI34" s="3"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5"/>
-      <c r="AL34" s="4"/>
+      <c r="AL34" s="3"/>
       <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="3"/>
+      <c r="AN34" s="5"/>
+      <c r="AO34" s="4"/>
       <c r="AP34" s="4"/>
       <c r="AQ34" s="4"/>
       <c r="AR34" s="3"/>
       <c r="AS34" s="4"/>
-      <c r="AT34" s="5"/>
+      <c r="AT34" s="4"/>
       <c r="AU34" s="3"/>
       <c r="AV34" s="4"/>
       <c r="AW34" s="5"/>
-      <c r="AX34" s="4"/>
+      <c r="AX34" s="3"/>
       <c r="AY34" s="4"/>
-      <c r="AZ34" s="4"/>
-      <c r="BA34" s="3"/>
+      <c r="AZ34" s="5"/>
+      <c r="BA34" s="4"/>
       <c r="BB34" s="4"/>
-      <c r="BC34" s="5"/>
-      <c r="BD34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="3"/>
       <c r="BE34" s="4"/>
-      <c r="BF34" s="4"/>
+      <c r="BF34" s="5"/>
       <c r="BG34" s="4"/>
       <c r="BH34" s="4"/>
       <c r="BI34" s="4"/>
       <c r="BJ34" s="4"/>
-      <c r="BK34" s="5"/>
-    </row>
-    <row r="35" spans="1:63" ht="14" customHeight="1">
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+      <c r="BM34" s="5"/>
+    </row>
+    <row r="35" spans="1:65" ht="14" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -3831,34 +3895,36 @@
       <c r="AI35" s="3"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="5"/>
-      <c r="AL35" s="4"/>
+      <c r="AL35" s="3"/>
       <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="3"/>
+      <c r="AN35" s="5"/>
+      <c r="AO35" s="4"/>
       <c r="AP35" s="4"/>
       <c r="AQ35" s="4"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="4"/>
-      <c r="AT35" s="5"/>
+      <c r="AT35" s="4"/>
       <c r="AU35" s="3"/>
       <c r="AV35" s="4"/>
       <c r="AW35" s="5"/>
-      <c r="AX35" s="4"/>
+      <c r="AX35" s="3"/>
       <c r="AY35" s="4"/>
-      <c r="AZ35" s="4"/>
-      <c r="BA35" s="3"/>
+      <c r="AZ35" s="5"/>
+      <c r="BA35" s="4"/>
       <c r="BB35" s="4"/>
-      <c r="BC35" s="5"/>
-      <c r="BD35" s="4"/>
+      <c r="BC35" s="4"/>
+      <c r="BD35" s="3"/>
       <c r="BE35" s="4"/>
-      <c r="BF35" s="4"/>
+      <c r="BF35" s="5"/>
       <c r="BG35" s="4"/>
       <c r="BH35" s="4"/>
       <c r="BI35" s="4"/>
       <c r="BJ35" s="4"/>
-      <c r="BK35" s="5"/>
-    </row>
-    <row r="36" spans="1:63" ht="14" customHeight="1">
+      <c r="BK35" s="4"/>
+      <c r="BL35" s="4"/>
+      <c r="BM35" s="5"/>
+    </row>
+    <row r="36" spans="1:65" ht="14" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -3896,34 +3962,36 @@
       <c r="AI36" s="3"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="5"/>
-      <c r="AL36" s="4"/>
+      <c r="AL36" s="3"/>
       <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="3"/>
+      <c r="AN36" s="5"/>
+      <c r="AO36" s="4"/>
       <c r="AP36" s="4"/>
       <c r="AQ36" s="4"/>
       <c r="AR36" s="3"/>
       <c r="AS36" s="4"/>
-      <c r="AT36" s="5"/>
+      <c r="AT36" s="4"/>
       <c r="AU36" s="3"/>
       <c r="AV36" s="4"/>
       <c r="AW36" s="5"/>
-      <c r="AX36" s="4"/>
+      <c r="AX36" s="3"/>
       <c r="AY36" s="4"/>
-      <c r="AZ36" s="4"/>
-      <c r="BA36" s="3"/>
+      <c r="AZ36" s="5"/>
+      <c r="BA36" s="4"/>
       <c r="BB36" s="4"/>
-      <c r="BC36" s="5"/>
-      <c r="BD36" s="4"/>
+      <c r="BC36" s="4"/>
+      <c r="BD36" s="3"/>
       <c r="BE36" s="4"/>
-      <c r="BF36" s="4"/>
+      <c r="BF36" s="5"/>
       <c r="BG36" s="4"/>
       <c r="BH36" s="4"/>
       <c r="BI36" s="4"/>
       <c r="BJ36" s="4"/>
-      <c r="BK36" s="5"/>
-    </row>
-    <row r="37" spans="1:63" ht="14" customHeight="1">
+      <c r="BK36" s="4"/>
+      <c r="BL36" s="4"/>
+      <c r="BM36" s="5"/>
+    </row>
+    <row r="37" spans="1:65" ht="14" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -3961,34 +4029,36 @@
       <c r="AI37" s="3"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="5"/>
-      <c r="AL37" s="4"/>
+      <c r="AL37" s="3"/>
       <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="3"/>
+      <c r="AN37" s="5"/>
+      <c r="AO37" s="4"/>
       <c r="AP37" s="4"/>
       <c r="AQ37" s="4"/>
       <c r="AR37" s="3"/>
       <c r="AS37" s="4"/>
-      <c r="AT37" s="5"/>
+      <c r="AT37" s="4"/>
       <c r="AU37" s="3"/>
       <c r="AV37" s="4"/>
       <c r="AW37" s="5"/>
-      <c r="AX37" s="4"/>
+      <c r="AX37" s="3"/>
       <c r="AY37" s="4"/>
-      <c r="AZ37" s="4"/>
-      <c r="BA37" s="3"/>
+      <c r="AZ37" s="5"/>
+      <c r="BA37" s="4"/>
       <c r="BB37" s="4"/>
-      <c r="BC37" s="5"/>
-      <c r="BD37" s="4"/>
+      <c r="BC37" s="4"/>
+      <c r="BD37" s="3"/>
       <c r="BE37" s="4"/>
-      <c r="BF37" s="4"/>
+      <c r="BF37" s="5"/>
       <c r="BG37" s="4"/>
       <c r="BH37" s="4"/>
       <c r="BI37" s="4"/>
       <c r="BJ37" s="4"/>
-      <c r="BK37" s="5"/>
-    </row>
-    <row r="38" spans="1:63" ht="14" customHeight="1">
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+      <c r="BM37" s="5"/>
+    </row>
+    <row r="38" spans="1:65" ht="14" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -4026,34 +4096,36 @@
       <c r="AI38" s="3"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="5"/>
-      <c r="AL38" s="4"/>
+      <c r="AL38" s="3"/>
       <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="3"/>
+      <c r="AN38" s="5"/>
+      <c r="AO38" s="4"/>
       <c r="AP38" s="4"/>
       <c r="AQ38" s="4"/>
       <c r="AR38" s="3"/>
       <c r="AS38" s="4"/>
-      <c r="AT38" s="5"/>
+      <c r="AT38" s="4"/>
       <c r="AU38" s="3"/>
       <c r="AV38" s="4"/>
       <c r="AW38" s="5"/>
-      <c r="AX38" s="4"/>
+      <c r="AX38" s="3"/>
       <c r="AY38" s="4"/>
-      <c r="AZ38" s="4"/>
-      <c r="BA38" s="3"/>
+      <c r="AZ38" s="5"/>
+      <c r="BA38" s="4"/>
       <c r="BB38" s="4"/>
-      <c r="BC38" s="5"/>
-      <c r="BD38" s="4"/>
+      <c r="BC38" s="4"/>
+      <c r="BD38" s="3"/>
       <c r="BE38" s="4"/>
-      <c r="BF38" s="4"/>
+      <c r="BF38" s="5"/>
       <c r="BG38" s="4"/>
       <c r="BH38" s="4"/>
       <c r="BI38" s="4"/>
       <c r="BJ38" s="4"/>
-      <c r="BK38" s="5"/>
-    </row>
-    <row r="39" spans="1:63" ht="14" customHeight="1">
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+      <c r="BM38" s="5"/>
+    </row>
+    <row r="39" spans="1:65" ht="14" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -4091,34 +4163,36 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="5"/>
-      <c r="AL39" s="4"/>
+      <c r="AL39" s="3"/>
       <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="3"/>
+      <c r="AN39" s="5"/>
+      <c r="AO39" s="4"/>
       <c r="AP39" s="4"/>
       <c r="AQ39" s="4"/>
       <c r="AR39" s="3"/>
       <c r="AS39" s="4"/>
-      <c r="AT39" s="5"/>
+      <c r="AT39" s="4"/>
       <c r="AU39" s="3"/>
       <c r="AV39" s="4"/>
       <c r="AW39" s="5"/>
-      <c r="AX39" s="4"/>
+      <c r="AX39" s="3"/>
       <c r="AY39" s="4"/>
-      <c r="AZ39" s="4"/>
-      <c r="BA39" s="3"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="4"/>
       <c r="BB39" s="4"/>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="3"/>
       <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
+      <c r="BF39" s="5"/>
       <c r="BG39" s="4"/>
       <c r="BH39" s="4"/>
       <c r="BI39" s="4"/>
       <c r="BJ39" s="4"/>
-      <c r="BK39" s="5"/>
-    </row>
-    <row r="40" spans="1:63" ht="14" customHeight="1">
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="5"/>
+    </row>
+    <row r="40" spans="1:65" ht="14" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -4156,34 +4230,36 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="5"/>
-      <c r="AL40" s="4"/>
+      <c r="AL40" s="3"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="4"/>
-      <c r="AO40" s="3"/>
+      <c r="AN40" s="5"/>
+      <c r="AO40" s="4"/>
       <c r="AP40" s="4"/>
       <c r="AQ40" s="4"/>
       <c r="AR40" s="3"/>
       <c r="AS40" s="4"/>
-      <c r="AT40" s="5"/>
+      <c r="AT40" s="4"/>
       <c r="AU40" s="3"/>
       <c r="AV40" s="4"/>
       <c r="AW40" s="5"/>
-      <c r="AX40" s="4"/>
+      <c r="AX40" s="3"/>
       <c r="AY40" s="4"/>
-      <c r="AZ40" s="4"/>
-      <c r="BA40" s="3"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="4"/>
       <c r="BB40" s="4"/>
-      <c r="BC40" s="5"/>
-      <c r="BD40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="3"/>
       <c r="BE40" s="4"/>
-      <c r="BF40" s="4"/>
+      <c r="BF40" s="5"/>
       <c r="BG40" s="4"/>
       <c r="BH40" s="4"/>
       <c r="BI40" s="4"/>
       <c r="BJ40" s="4"/>
-      <c r="BK40" s="5"/>
-    </row>
-    <row r="41" spans="1:63" ht="14" customHeight="1">
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="5"/>
+    </row>
+    <row r="41" spans="1:65" ht="14" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
@@ -4221,34 +4297,36 @@
       <c r="AI41" s="3"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="5"/>
-      <c r="AL41" s="4"/>
+      <c r="AL41" s="3"/>
       <c r="AM41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="AO41" s="3"/>
+      <c r="AN41" s="5"/>
+      <c r="AO41" s="4"/>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="4"/>
       <c r="AR41" s="3"/>
       <c r="AS41" s="4"/>
-      <c r="AT41" s="5"/>
+      <c r="AT41" s="4"/>
       <c r="AU41" s="3"/>
       <c r="AV41" s="4"/>
       <c r="AW41" s="5"/>
-      <c r="AX41" s="4"/>
+      <c r="AX41" s="3"/>
       <c r="AY41" s="4"/>
-      <c r="AZ41" s="4"/>
-      <c r="BA41" s="3"/>
+      <c r="AZ41" s="5"/>
+      <c r="BA41" s="4"/>
       <c r="BB41" s="4"/>
-      <c r="BC41" s="5"/>
-      <c r="BD41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="3"/>
       <c r="BE41" s="4"/>
-      <c r="BF41" s="4"/>
+      <c r="BF41" s="5"/>
       <c r="BG41" s="4"/>
       <c r="BH41" s="4"/>
       <c r="BI41" s="4"/>
       <c r="BJ41" s="4"/>
-      <c r="BK41" s="5"/>
-    </row>
-    <row r="42" spans="1:63" ht="14" customHeight="1">
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="5"/>
+    </row>
+    <row r="42" spans="1:65" ht="14" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
@@ -4286,34 +4364,36 @@
       <c r="AI42" s="3"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="5"/>
-      <c r="AL42" s="4"/>
+      <c r="AL42" s="3"/>
       <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="3"/>
+      <c r="AN42" s="5"/>
+      <c r="AO42" s="4"/>
       <c r="AP42" s="4"/>
       <c r="AQ42" s="4"/>
       <c r="AR42" s="3"/>
       <c r="AS42" s="4"/>
-      <c r="AT42" s="5"/>
+      <c r="AT42" s="4"/>
       <c r="AU42" s="3"/>
       <c r="AV42" s="4"/>
       <c r="AW42" s="5"/>
-      <c r="AX42" s="4"/>
+      <c r="AX42" s="3"/>
       <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="3"/>
+      <c r="AZ42" s="5"/>
+      <c r="BA42" s="4"/>
       <c r="BB42" s="4"/>
-      <c r="BC42" s="5"/>
-      <c r="BD42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="3"/>
       <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
+      <c r="BF42" s="5"/>
       <c r="BG42" s="4"/>
       <c r="BH42" s="4"/>
       <c r="BI42" s="4"/>
       <c r="BJ42" s="4"/>
-      <c r="BK42" s="5"/>
-    </row>
-    <row r="43" spans="1:63" ht="14" customHeight="1">
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="5"/>
+    </row>
+    <row r="43" spans="1:65" ht="14" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
@@ -4351,34 +4431,36 @@
       <c r="AI43" s="3"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="5"/>
-      <c r="AL43" s="4"/>
+      <c r="AL43" s="3"/>
       <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="AO43" s="3"/>
+      <c r="AN43" s="5"/>
+      <c r="AO43" s="4"/>
       <c r="AP43" s="4"/>
       <c r="AQ43" s="4"/>
       <c r="AR43" s="3"/>
       <c r="AS43" s="4"/>
-      <c r="AT43" s="5"/>
+      <c r="AT43" s="4"/>
       <c r="AU43" s="3"/>
       <c r="AV43" s="4"/>
       <c r="AW43" s="5"/>
-      <c r="AX43" s="4"/>
+      <c r="AX43" s="3"/>
       <c r="AY43" s="4"/>
-      <c r="AZ43" s="4"/>
-      <c r="BA43" s="3"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="4"/>
       <c r="BB43" s="4"/>
-      <c r="BC43" s="5"/>
-      <c r="BD43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="3"/>
       <c r="BE43" s="4"/>
-      <c r="BF43" s="4"/>
+      <c r="BF43" s="5"/>
       <c r="BG43" s="4"/>
       <c r="BH43" s="4"/>
       <c r="BI43" s="4"/>
       <c r="BJ43" s="4"/>
-      <c r="BK43" s="5"/>
-    </row>
-    <row r="44" spans="1:63" ht="14" customHeight="1">
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="5"/>
+    </row>
+    <row r="44" spans="1:65" ht="14" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
@@ -4416,34 +4498,36 @@
       <c r="AI44" s="3"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="5"/>
-      <c r="AL44" s="4"/>
+      <c r="AL44" s="3"/>
       <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="3"/>
+      <c r="AN44" s="5"/>
+      <c r="AO44" s="4"/>
       <c r="AP44" s="4"/>
       <c r="AQ44" s="4"/>
       <c r="AR44" s="3"/>
       <c r="AS44" s="4"/>
-      <c r="AT44" s="5"/>
+      <c r="AT44" s="4"/>
       <c r="AU44" s="3"/>
       <c r="AV44" s="4"/>
       <c r="AW44" s="5"/>
-      <c r="AX44" s="4"/>
+      <c r="AX44" s="3"/>
       <c r="AY44" s="4"/>
-      <c r="AZ44" s="4"/>
-      <c r="BA44" s="3"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="4"/>
       <c r="BB44" s="4"/>
-      <c r="BC44" s="5"/>
-      <c r="BD44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="3"/>
       <c r="BE44" s="4"/>
-      <c r="BF44" s="4"/>
+      <c r="BF44" s="5"/>
       <c r="BG44" s="4"/>
       <c r="BH44" s="4"/>
       <c r="BI44" s="4"/>
       <c r="BJ44" s="4"/>
-      <c r="BK44" s="5"/>
-    </row>
-    <row r="45" spans="1:63" ht="14" customHeight="1">
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="5"/>
+    </row>
+    <row r="45" spans="1:65" ht="14" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="3"/>
@@ -4481,38 +4565,40 @@
       <c r="AI45" s="3"/>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="5"/>
-      <c r="AL45" s="4"/>
+      <c r="AL45" s="3"/>
       <c r="AM45" s="4"/>
-      <c r="AN45" s="4"/>
-      <c r="AO45" s="3"/>
+      <c r="AN45" s="5"/>
+      <c r="AO45" s="4"/>
       <c r="AP45" s="4"/>
       <c r="AQ45" s="4"/>
       <c r="AR45" s="3"/>
       <c r="AS45" s="4"/>
-      <c r="AT45" s="5"/>
+      <c r="AT45" s="4"/>
       <c r="AU45" s="3"/>
       <c r="AV45" s="4"/>
       <c r="AW45" s="5"/>
-      <c r="AX45" s="4"/>
+      <c r="AX45" s="3"/>
       <c r="AY45" s="4"/>
-      <c r="AZ45" s="4"/>
-      <c r="BA45" s="3"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="4"/>
       <c r="BB45" s="4"/>
-      <c r="BC45" s="5"/>
-      <c r="BD45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="3"/>
       <c r="BE45" s="4"/>
-      <c r="BF45" s="4"/>
+      <c r="BF45" s="5"/>
       <c r="BG45" s="4"/>
       <c r="BH45" s="4"/>
       <c r="BI45" s="4"/>
       <c r="BJ45" s="4"/>
-      <c r="BK45" s="5"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+      <c r="BM45" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
@@ -4521,11 +4607,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D788243-52D9-F642-B947-0B51E952DAC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25527C0D-35D5-C64B-9F7A-7BF3BD7D5A0C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BK45"/>
+  <dimension ref="A1:BM45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -4533,10 +4619,8 @@
     <col min="31" max="16384" width="2.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="14" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="1" spans="1:65" ht="14" customHeight="1">
+      <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4583,12 +4667,12 @@
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
       <c r="AW1" s="4"/>
       <c r="AX1" s="4"/>
@@ -4604,9 +4688,11 @@
       <c r="BH1" s="4"/>
       <c r="BI1" s="4"/>
       <c r="BJ1" s="4"/>
-      <c r="BK1" s="5"/>
-    </row>
-    <row r="2" spans="1:63" ht="14" customHeight="1">
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="5"/>
+    </row>
+    <row r="2" spans="1:65" ht="14" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -4656,10 +4742,10 @@
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="4"/>
-      <c r="AT2" s="4"/>
-      <c r="AU2" s="4"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="3"/>
       <c r="AV2" s="4"/>
       <c r="AW2" s="4"/>
       <c r="AX2" s="4"/>
@@ -4675,9 +4761,11 @@
       <c r="BH2" s="4"/>
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
-      <c r="BK2" s="5"/>
-    </row>
-    <row r="3" spans="1:63" ht="14" customHeight="1">
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="4"/>
+      <c r="BM2" s="5"/>
+    </row>
+    <row r="3" spans="1:65" ht="14" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -4727,10 +4815,10 @@
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2"/>
+      <c r="AU3" s="3"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="4"/>
       <c r="AX3" s="4"/>
@@ -4746,9 +4834,11 @@
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
-      <c r="BK3" s="5"/>
-    </row>
-    <row r="4" spans="1:63" ht="14" customHeight="1">
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="5"/>
+    </row>
+    <row r="4" spans="1:65" ht="14" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -4813,13 +4903,15 @@
       <c r="BH4" s="8"/>
       <c r="BI4" s="8"/>
       <c r="BJ4" s="8"/>
-      <c r="BK4" s="9"/>
-    </row>
-    <row r="5" spans="1:63" ht="14" customHeight="1">
+      <c r="BK4" s="8"/>
+      <c r="BL4" s="8"/>
+      <c r="BM4" s="9"/>
+    </row>
+    <row r="5" spans="1:65" ht="14" customHeight="1">
       <c r="A5" s="10"/>
-      <c r="BK5" s="11"/>
-    </row>
-    <row r="6" spans="1:63" ht="14" customHeight="1">
+      <c r="BM5" s="11"/>
+    </row>
+    <row r="6" spans="1:65" ht="14" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4882,9 +4974,11 @@
       <c r="BH6" s="13"/>
       <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="14"/>
-    </row>
-    <row r="8" spans="1:63" ht="14" customHeight="1">
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="14"/>
+    </row>
+    <row r="8" spans="1:65" ht="14" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
@@ -4927,12 +5021,12 @@
       <c r="AF8" s="17"/>
       <c r="AG8" s="17"/>
       <c r="AH8" s="17"/>
-      <c r="AI8" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
+      <c r="AL8" s="15" t="s">
+        <v>8</v>
+      </c>
       <c r="AM8" s="17"/>
       <c r="AN8" s="17"/>
       <c r="AO8" s="17"/>
@@ -4943,29 +5037,31 @@
       <c r="AT8" s="17"/>
       <c r="AU8" s="17"/>
       <c r="AV8" s="17"/>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="15" t="s">
+      <c r="AW8" s="17"/>
+      <c r="AX8" s="17"/>
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="15" t="s">
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="17"/>
+      <c r="BD8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="16"/>
-      <c r="BD8" s="17" t="s">
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="16"/>
+      <c r="BG8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="17"/>
       <c r="BH8" s="17"/>
       <c r="BI8" s="17"/>
       <c r="BJ8" s="17"/>
-      <c r="BK8" s="16"/>
-    </row>
-    <row r="9" spans="1:63" ht="14" customHeight="1">
+      <c r="BK8" s="17"/>
+      <c r="BL8" s="17"/>
+      <c r="BM8" s="16"/>
+    </row>
+    <row r="9" spans="1:65" ht="14" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="20"/>
       <c r="C9" s="18" t="s">
@@ -5021,46 +5117,50 @@
       <c r="AG9" s="20"/>
       <c r="AH9" s="20"/>
       <c r="AI9" s="18" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
-      <c r="AL9" s="20" t="s">
+      <c r="AL9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="AM9" s="20"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="18" t="s">
-        <v>27</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="20"/>
       <c r="AU9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AV9" s="20"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="18"/>
       <c r="AY9" s="20"/>
-      <c r="AZ9" s="20"/>
+      <c r="AZ9" s="19"/>
       <c r="BA9" s="18"/>
       <c r="BB9" s="20"/>
-      <c r="BC9" s="19"/>
-      <c r="BD9" s="20"/>
+      <c r="BC9" s="20"/>
+      <c r="BD9" s="18"/>
       <c r="BE9" s="20"/>
-      <c r="BF9" s="20"/>
+      <c r="BF9" s="19"/>
       <c r="BG9" s="20"/>
       <c r="BH9" s="20"/>
       <c r="BI9" s="20"/>
       <c r="BJ9" s="20"/>
-      <c r="BK9" s="19"/>
-    </row>
-    <row r="10" spans="1:63" ht="14" customHeight="1">
+      <c r="BK9" s="20"/>
+      <c r="BL9" s="20"/>
+      <c r="BM9" s="19"/>
+    </row>
+    <row r="10" spans="1:65" ht="14" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -5113,47 +5213,49 @@
       </c>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
-      <c r="AI10" s="18" t="s">
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="13"/>
+      <c r="AK10" s="14"/>
+      <c r="AL10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
-      <c r="AN10" s="4"/>
-      <c r="AO10" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="4"/>
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
-      <c r="AR10" s="3"/>
+      <c r="AR10" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AS10" s="4"/>
-      <c r="AT10" s="5"/>
+      <c r="AT10" s="4"/>
       <c r="AU10" s="3"/>
       <c r="AV10" s="4"/>
       <c r="AW10" s="5"/>
-      <c r="AX10" s="4" t="s">
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="5"/>
+      <c r="BA10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="4"/>
-      <c r="BA10" s="3" t="s">
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="BB10" s="4"/>
-      <c r="BC10" s="5"/>
-      <c r="BD10" s="4" t="s">
+      <c r="BE10" s="4"/>
+      <c r="BF10" s="5"/>
+      <c r="BG10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="BE10" s="4"/>
-      <c r="BF10" s="4"/>
-      <c r="BG10" s="4"/>
       <c r="BH10" s="4"/>
       <c r="BI10" s="4"/>
       <c r="BJ10" s="4"/>
-      <c r="BK10" s="5"/>
-    </row>
-    <row r="11" spans="1:63" ht="14" customHeight="1">
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+      <c r="BM10" s="5"/>
+    </row>
+    <row r="11" spans="1:65" ht="14" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -5204,47 +5306,47 @@
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
-      <c r="AI11" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="AI11" s="3"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5"/>
-      <c r="AL11" s="4"/>
+      <c r="AL11" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="AM11" s="4"/>
-      <c r="AN11" s="4"/>
-      <c r="AO11" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="4"/>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="3"/>
       <c r="AS11" s="4"/>
-      <c r="AT11" s="5"/>
+      <c r="AT11" s="4"/>
       <c r="AU11" s="3"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
-      <c r="AX11" s="4" t="s">
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="5"/>
+      <c r="BA11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="4"/>
-      <c r="BA11" s="3" t="s">
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="BB11" s="4"/>
-      <c r="BC11" s="5"/>
-      <c r="BD11" s="4" t="s">
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="5"/>
+      <c r="BG11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="BE11" s="4"/>
-      <c r="BF11" s="4"/>
-      <c r="BG11" s="4"/>
       <c r="BH11" s="4"/>
       <c r="BI11" s="4"/>
       <c r="BJ11" s="4"/>
-      <c r="BK11" s="5"/>
-    </row>
-    <row r="12" spans="1:63" ht="14" customHeight="1">
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+      <c r="BM11" s="5"/>
+    </row>
+    <row r="12" spans="1:65" ht="14" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -5293,43 +5395,45 @@
       </c>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
-      <c r="AI12" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="AI12" s="3"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5"/>
-      <c r="AL12" s="4"/>
+      <c r="AL12" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="AM12" s="4"/>
-      <c r="AN12" s="4"/>
-      <c r="AO12" s="3"/>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="4"/>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="3"/>
       <c r="AS12" s="4"/>
-      <c r="AT12" s="5"/>
+      <c r="AT12" s="4"/>
       <c r="AU12" s="3"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
-      <c r="AX12" s="4" t="s">
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="5"/>
+      <c r="BA12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="AY12" s="4"/>
-      <c r="AZ12" s="4"/>
-      <c r="BA12" s="3" t="s">
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+      <c r="BD12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="BB12" s="4"/>
-      <c r="BC12" s="5"/>
-      <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
-      <c r="BF12" s="4"/>
+      <c r="BF12" s="5"/>
       <c r="BG12" s="4"/>
       <c r="BH12" s="4"/>
       <c r="BI12" s="4"/>
       <c r="BJ12" s="4"/>
-      <c r="BK12" s="5"/>
-    </row>
-    <row r="13" spans="1:63" ht="14" customHeight="1">
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+      <c r="BM12" s="5"/>
+    </row>
+    <row r="13" spans="1:65" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -5372,45 +5476,41 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
-      <c r="AI13" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="AI13" s="3"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5"/>
-      <c r="AL13" s="4"/>
+      <c r="AL13" s="3"/>
       <c r="AM13" s="4"/>
-      <c r="AN13" s="4"/>
-      <c r="AO13" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="AN13" s="5"/>
+      <c r="AO13" s="4"/>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
-      <c r="AR13" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="AR13" s="3"/>
       <c r="AS13" s="4"/>
-      <c r="AT13" s="5"/>
+      <c r="AT13" s="4"/>
       <c r="AU13" s="3"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
-      <c r="AX13" s="4"/>
+      <c r="AX13" s="3"/>
       <c r="AY13" s="4"/>
-      <c r="AZ13" s="4"/>
-      <c r="BA13" s="3"/>
+      <c r="AZ13" s="5"/>
+      <c r="BA13" s="4"/>
       <c r="BB13" s="4"/>
-      <c r="BC13" s="5"/>
-      <c r="BD13" s="4" t="s">
+      <c r="BC13" s="4"/>
+      <c r="BD13" s="3"/>
+      <c r="BE13" s="4"/>
+      <c r="BF13" s="5"/>
+      <c r="BG13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BE13" s="4"/>
-      <c r="BF13" s="4"/>
-      <c r="BG13" s="4"/>
       <c r="BH13" s="4"/>
       <c r="BI13" s="4"/>
       <c r="BJ13" s="4"/>
-      <c r="BK13" s="5"/>
-    </row>
-    <row r="14" spans="1:63" ht="14" customHeight="1">
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+      <c r="BM13" s="5"/>
+    </row>
+    <row r="14" spans="1:65" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -5456,34 +5556,36 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5"/>
-      <c r="AL14" s="4"/>
+      <c r="AL14" s="3"/>
       <c r="AM14" s="4"/>
-      <c r="AN14" s="4"/>
-      <c r="AO14" s="3"/>
+      <c r="AN14" s="5"/>
+      <c r="AO14" s="4"/>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="3"/>
       <c r="AS14" s="4"/>
-      <c r="AT14" s="5"/>
+      <c r="AT14" s="4"/>
       <c r="AU14" s="3"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="5"/>
-      <c r="AX14" s="4"/>
+      <c r="AX14" s="3"/>
       <c r="AY14" s="4"/>
-      <c r="AZ14" s="4"/>
-      <c r="BA14" s="3"/>
+      <c r="AZ14" s="5"/>
+      <c r="BA14" s="4"/>
       <c r="BB14" s="4"/>
-      <c r="BC14" s="5"/>
-      <c r="BD14" s="4"/>
+      <c r="BC14" s="4"/>
+      <c r="BD14" s="3"/>
       <c r="BE14" s="4"/>
-      <c r="BF14" s="4"/>
+      <c r="BF14" s="5"/>
       <c r="BG14" s="4"/>
       <c r="BH14" s="4"/>
       <c r="BI14" s="4"/>
       <c r="BJ14" s="4"/>
-      <c r="BK14" s="5"/>
-    </row>
-    <row r="15" spans="1:63" ht="14" customHeight="1">
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+      <c r="BM14" s="5"/>
+    </row>
+    <row r="15" spans="1:65" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -5529,34 +5631,36 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5"/>
-      <c r="AL15" s="4"/>
+      <c r="AL15" s="3"/>
       <c r="AM15" s="4"/>
-      <c r="AN15" s="4"/>
-      <c r="AO15" s="3"/>
+      <c r="AN15" s="5"/>
+      <c r="AO15" s="4"/>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="3"/>
       <c r="AS15" s="4"/>
-      <c r="AT15" s="5"/>
+      <c r="AT15" s="4"/>
       <c r="AU15" s="3"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
-      <c r="AX15" s="4"/>
+      <c r="AX15" s="3"/>
       <c r="AY15" s="4"/>
-      <c r="AZ15" s="4"/>
-      <c r="BA15" s="3"/>
+      <c r="AZ15" s="5"/>
+      <c r="BA15" s="4"/>
       <c r="BB15" s="4"/>
-      <c r="BC15" s="5"/>
-      <c r="BD15" s="4"/>
+      <c r="BC15" s="4"/>
+      <c r="BD15" s="3"/>
       <c r="BE15" s="4"/>
-      <c r="BF15" s="4"/>
+      <c r="BF15" s="5"/>
       <c r="BG15" s="4"/>
       <c r="BH15" s="4"/>
       <c r="BI15" s="4"/>
       <c r="BJ15" s="4"/>
-      <c r="BK15" s="5"/>
-    </row>
-    <row r="16" spans="1:63" ht="14" customHeight="1">
+      <c r="BK15" s="4"/>
+      <c r="BL15" s="4"/>
+      <c r="BM15" s="5"/>
+    </row>
+    <row r="16" spans="1:65" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -5581,9 +5685,7 @@
       <c r="N16" s="3"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="Q16" s="3"/>
       <c r="R16" s="4"/>
       <c r="S16" s="5"/>
       <c r="T16" s="3"/>
@@ -5604,36 +5706,42 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5"/>
-      <c r="AL16" s="4"/>
+      <c r="AL16" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="AM16" s="4"/>
-      <c r="AN16" s="4"/>
-      <c r="AO16" s="3"/>
+      <c r="AN16" s="5"/>
+      <c r="AO16" s="4"/>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
-      <c r="AR16" s="3"/>
+      <c r="AR16" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="AS16" s="4"/>
-      <c r="AT16" s="5"/>
+      <c r="AT16" s="4"/>
       <c r="AU16" s="3"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
-      <c r="AX16" s="4"/>
+      <c r="AX16" s="3"/>
       <c r="AY16" s="4"/>
-      <c r="AZ16" s="4"/>
-      <c r="BA16" s="3"/>
+      <c r="AZ16" s="5"/>
+      <c r="BA16" s="4"/>
       <c r="BB16" s="4"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="4" t="s">
+      <c r="BC16" s="4"/>
+      <c r="BD16" s="3"/>
+      <c r="BE16" s="4"/>
+      <c r="BF16" s="5"/>
+      <c r="BG16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE16" s="4"/>
-      <c r="BF16" s="4"/>
-      <c r="BG16" s="4"/>
       <c r="BH16" s="4"/>
       <c r="BI16" s="4"/>
       <c r="BJ16" s="4"/>
-      <c r="BK16" s="5"/>
-    </row>
-    <row r="17" spans="1:63" ht="14" customHeight="1">
+      <c r="BK16" s="4"/>
+      <c r="BL16" s="4"/>
+      <c r="BM16" s="5"/>
+    </row>
+    <row r="17" spans="1:65" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -5656,9 +5764,7 @@
       <c r="N17" s="3"/>
       <c r="O17" s="4"/>
       <c r="P17" s="5"/>
-      <c r="Q17" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="Q17" s="3"/>
       <c r="R17" s="4"/>
       <c r="S17" s="5"/>
       <c r="T17" s="3"/>
@@ -5679,36 +5785,42 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5"/>
-      <c r="AL17" s="4"/>
+      <c r="AL17" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="AM17" s="4"/>
-      <c r="AN17" s="4"/>
-      <c r="AO17" s="3"/>
+      <c r="AN17" s="5"/>
+      <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
-      <c r="AR17" s="3"/>
+      <c r="AR17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="AS17" s="4"/>
-      <c r="AT17" s="5"/>
+      <c r="AT17" s="4"/>
       <c r="AU17" s="3"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="5"/>
-      <c r="AX17" s="4"/>
+      <c r="AX17" s="3"/>
       <c r="AY17" s="4"/>
-      <c r="AZ17" s="4"/>
-      <c r="BA17" s="3"/>
+      <c r="AZ17" s="5"/>
+      <c r="BA17" s="4"/>
       <c r="BB17" s="4"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="4" t="s">
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="3"/>
+      <c r="BE17" s="4"/>
+      <c r="BF17" s="5"/>
+      <c r="BG17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE17" s="4"/>
-      <c r="BF17" s="4"/>
-      <c r="BG17" s="4"/>
       <c r="BH17" s="4"/>
       <c r="BI17" s="4"/>
       <c r="BJ17" s="4"/>
-      <c r="BK17" s="5"/>
-    </row>
-    <row r="18" spans="1:63" ht="14" customHeight="1">
+      <c r="BK17" s="4"/>
+      <c r="BL17" s="4"/>
+      <c r="BM17" s="5"/>
+    </row>
+    <row r="18" spans="1:65" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -5752,36 +5864,38 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5"/>
-      <c r="AL18" s="4"/>
+      <c r="AL18" s="3"/>
       <c r="AM18" s="4"/>
-      <c r="AN18" s="4"/>
-      <c r="AO18" s="3"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="4"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="3"/>
       <c r="AS18" s="4"/>
-      <c r="AT18" s="5"/>
+      <c r="AT18" s="4"/>
       <c r="AU18" s="3"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
-      <c r="AX18" s="4"/>
+      <c r="AX18" s="3"/>
       <c r="AY18" s="4"/>
-      <c r="AZ18" s="4"/>
-      <c r="BA18" s="3"/>
+      <c r="AZ18" s="5"/>
+      <c r="BA18" s="4"/>
       <c r="BB18" s="4"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="4" t="s">
+      <c r="BC18" s="4"/>
+      <c r="BD18" s="3"/>
+      <c r="BE18" s="4"/>
+      <c r="BF18" s="5"/>
+      <c r="BG18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE18" s="4"/>
-      <c r="BF18" s="4"/>
-      <c r="BG18" s="4"/>
       <c r="BH18" s="4"/>
       <c r="BI18" s="4"/>
       <c r="BJ18" s="4"/>
-      <c r="BK18" s="5"/>
-    </row>
-    <row r="19" spans="1:63" ht="14" customHeight="1">
+      <c r="BK18" s="4"/>
+      <c r="BL18" s="4"/>
+      <c r="BM18" s="5"/>
+    </row>
+    <row r="19" spans="1:65" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -5825,36 +5939,38 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5"/>
-      <c r="AL19" s="4"/>
+      <c r="AL19" s="3"/>
       <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="3"/>
+      <c r="AN19" s="5"/>
+      <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="3"/>
       <c r="AS19" s="4"/>
-      <c r="AT19" s="5"/>
+      <c r="AT19" s="4"/>
       <c r="AU19" s="3"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
-      <c r="AX19" s="4"/>
+      <c r="AX19" s="3"/>
       <c r="AY19" s="4"/>
-      <c r="AZ19" s="4"/>
-      <c r="BA19" s="3"/>
+      <c r="AZ19" s="5"/>
+      <c r="BA19" s="4"/>
       <c r="BB19" s="4"/>
-      <c r="BC19" s="5"/>
-      <c r="BD19" s="4" t="s">
+      <c r="BC19" s="4"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="4"/>
+      <c r="BF19" s="5"/>
+      <c r="BG19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE19" s="4"/>
-      <c r="BF19" s="4"/>
-      <c r="BG19" s="4"/>
       <c r="BH19" s="4"/>
       <c r="BI19" s="4"/>
       <c r="BJ19" s="4"/>
-      <c r="BK19" s="5"/>
-    </row>
-    <row r="20" spans="1:63" ht="14" customHeight="1">
+      <c r="BK19" s="4"/>
+      <c r="BL19" s="4"/>
+      <c r="BM19" s="5"/>
+    </row>
+    <row r="20" spans="1:65" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
@@ -5898,36 +6014,38 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5"/>
-      <c r="AL20" s="4"/>
+      <c r="AL20" s="3"/>
       <c r="AM20" s="4"/>
-      <c r="AN20" s="4"/>
-      <c r="AO20" s="3"/>
+      <c r="AN20" s="5"/>
+      <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="3"/>
       <c r="AS20" s="4"/>
-      <c r="AT20" s="5"/>
+      <c r="AT20" s="4"/>
       <c r="AU20" s="3"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
-      <c r="AX20" s="4"/>
+      <c r="AX20" s="3"/>
       <c r="AY20" s="4"/>
-      <c r="AZ20" s="4"/>
-      <c r="BA20" s="3"/>
+      <c r="AZ20" s="5"/>
+      <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="4" t="s">
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="3"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="5"/>
+      <c r="BG20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE20" s="4"/>
-      <c r="BF20" s="4"/>
-      <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
       <c r="BJ20" s="4"/>
-      <c r="BK20" s="5"/>
-    </row>
-    <row r="21" spans="1:63" ht="14" customHeight="1">
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+      <c r="BM20" s="5"/>
+    </row>
+    <row r="21" spans="1:65" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
@@ -5971,36 +6089,38 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5"/>
-      <c r="AL21" s="4"/>
+      <c r="AL21" s="3"/>
       <c r="AM21" s="4"/>
-      <c r="AN21" s="4"/>
-      <c r="AO21" s="3"/>
+      <c r="AN21" s="5"/>
+      <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="3"/>
       <c r="AS21" s="4"/>
-      <c r="AT21" s="5"/>
+      <c r="AT21" s="4"/>
       <c r="AU21" s="3"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
-      <c r="AX21" s="4"/>
+      <c r="AX21" s="3"/>
       <c r="AY21" s="4"/>
-      <c r="AZ21" s="4"/>
-      <c r="BA21" s="3"/>
+      <c r="AZ21" s="5"/>
+      <c r="BA21" s="4"/>
       <c r="BB21" s="4"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="4" t="s">
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="3"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="5"/>
+      <c r="BG21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BE21" s="4"/>
-      <c r="BF21" s="4"/>
-      <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
       <c r="BJ21" s="4"/>
-      <c r="BK21" s="5"/>
-    </row>
-    <row r="22" spans="1:63" ht="14" customHeight="1">
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+      <c r="BM21" s="5"/>
+    </row>
+    <row r="22" spans="1:65" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -6048,36 +6168,38 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5"/>
-      <c r="AL22" s="4"/>
+      <c r="AL22" s="3"/>
       <c r="AM22" s="4"/>
-      <c r="AN22" s="4"/>
-      <c r="AO22" s="3"/>
+      <c r="AN22" s="5"/>
+      <c r="AO22" s="4"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="3"/>
       <c r="AS22" s="4"/>
-      <c r="AT22" s="5"/>
+      <c r="AT22" s="4"/>
       <c r="AU22" s="3"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
-      <c r="AX22" s="4"/>
+      <c r="AX22" s="3"/>
       <c r="AY22" s="4"/>
-      <c r="AZ22" s="4"/>
-      <c r="BA22" s="3"/>
+      <c r="AZ22" s="5"/>
+      <c r="BA22" s="4"/>
       <c r="BB22" s="4"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="4" t="s">
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="3"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="5"/>
+      <c r="BG22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BE22" s="4"/>
-      <c r="BF22" s="4"/>
-      <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
       <c r="BJ22" s="4"/>
-      <c r="BK22" s="5"/>
-    </row>
-    <row r="23" spans="1:63" ht="14" customHeight="1">
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="5"/>
+    </row>
+    <row r="23" spans="1:65" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -6125,36 +6247,38 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5"/>
-      <c r="AL23" s="4"/>
+      <c r="AL23" s="3"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="4"/>
-      <c r="AO23" s="3"/>
+      <c r="AN23" s="5"/>
+      <c r="AO23" s="4"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
-      <c r="AR23" s="24"/>
-      <c r="AS23" s="21"/>
-      <c r="AT23" s="5"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4"/>
       <c r="AU23" s="24"/>
       <c r="AV23" s="21"/>
       <c r="AW23" s="5"/>
-      <c r="AX23" s="4"/>
-      <c r="AY23" s="4"/>
-      <c r="AZ23" s="4"/>
-      <c r="BA23" s="3"/>
+      <c r="AX23" s="24"/>
+      <c r="AY23" s="21"/>
+      <c r="AZ23" s="5"/>
+      <c r="BA23" s="4"/>
       <c r="BB23" s="4"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="4" t="s">
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="3"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="5"/>
+      <c r="BG23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE23" s="4"/>
-      <c r="BF23" s="4"/>
-      <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
       <c r="BJ23" s="4"/>
-      <c r="BK23" s="5"/>
-    </row>
-    <row r="24" spans="1:63" ht="14" customHeight="1">
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+      <c r="BM23" s="5"/>
+    </row>
+    <row r="24" spans="1:65" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -6202,36 +6326,38 @@
       <c r="AI24" s="3"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5"/>
-      <c r="AL24" s="4"/>
+      <c r="AL24" s="3"/>
       <c r="AM24" s="4"/>
-      <c r="AN24" s="4"/>
-      <c r="AO24" s="3"/>
+      <c r="AN24" s="5"/>
+      <c r="AO24" s="4"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="4"/>
-      <c r="AT24" s="5"/>
+      <c r="AT24" s="4"/>
       <c r="AU24" s="3"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
-      <c r="AX24" s="4"/>
+      <c r="AX24" s="3"/>
       <c r="AY24" s="4"/>
-      <c r="AZ24" s="4"/>
-      <c r="BA24" s="3"/>
+      <c r="AZ24" s="5"/>
+      <c r="BA24" s="4"/>
       <c r="BB24" s="4"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="4" t="s">
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="3"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="5"/>
+      <c r="BG24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE24" s="4"/>
-      <c r="BF24" s="4"/>
-      <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
-      <c r="BK24" s="5"/>
-    </row>
-    <row r="25" spans="1:63" ht="14" customHeight="1">
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+      <c r="BM24" s="5"/>
+    </row>
+    <row r="25" spans="1:65" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -6279,36 +6405,38 @@
       <c r="AI25" s="3"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5"/>
-      <c r="AL25" s="4"/>
+      <c r="AL25" s="3"/>
       <c r="AM25" s="4"/>
-      <c r="AN25" s="4"/>
-      <c r="AO25" s="3"/>
+      <c r="AN25" s="5"/>
+      <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="4"/>
-      <c r="AT25" s="5"/>
+      <c r="AT25" s="4"/>
       <c r="AU25" s="3"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="5"/>
-      <c r="AX25" s="4"/>
+      <c r="AX25" s="3"/>
       <c r="AY25" s="4"/>
-      <c r="AZ25" s="4"/>
-      <c r="BA25" s="3"/>
+      <c r="AZ25" s="5"/>
+      <c r="BA25" s="4"/>
       <c r="BB25" s="4"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="4" t="s">
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="5"/>
+      <c r="BG25" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE25" s="4"/>
-      <c r="BF25" s="4"/>
-      <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
-      <c r="BK25" s="5"/>
-    </row>
-    <row r="26" spans="1:63" ht="14" customHeight="1">
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+      <c r="BM25" s="5"/>
+    </row>
+    <row r="26" spans="1:65" ht="14" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>78</v>
       </c>
@@ -6356,36 +6484,38 @@
       <c r="AI26" s="3"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5"/>
-      <c r="AL26" s="4"/>
+      <c r="AL26" s="3"/>
       <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="3"/>
+      <c r="AN26" s="5"/>
+      <c r="AO26" s="4"/>
       <c r="AP26" s="4"/>
       <c r="AQ26" s="4"/>
       <c r="AR26" s="3"/>
       <c r="AS26" s="4"/>
-      <c r="AT26" s="5"/>
+      <c r="AT26" s="4"/>
       <c r="AU26" s="3"/>
       <c r="AV26" s="4"/>
       <c r="AW26" s="5"/>
-      <c r="AX26" s="4"/>
+      <c r="AX26" s="3"/>
       <c r="AY26" s="4"/>
-      <c r="AZ26" s="4"/>
-      <c r="BA26" s="3"/>
+      <c r="AZ26" s="5"/>
+      <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="4" t="s">
+      <c r="BC26" s="4"/>
+      <c r="BD26" s="3"/>
+      <c r="BE26" s="4"/>
+      <c r="BF26" s="5"/>
+      <c r="BG26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BE26" s="4"/>
-      <c r="BF26" s="4"/>
-      <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
       <c r="BJ26" s="4"/>
-      <c r="BK26" s="5"/>
-    </row>
-    <row r="27" spans="1:63" ht="14" customHeight="1">
+      <c r="BK26" s="4"/>
+      <c r="BL26" s="4"/>
+      <c r="BM26" s="5"/>
+    </row>
+    <row r="27" spans="1:65" ht="14" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>79</v>
       </c>
@@ -6433,36 +6563,38 @@
       <c r="AI27" s="3"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5"/>
-      <c r="AL27" s="4"/>
+      <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="3"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="4"/>
       <c r="AP27" s="4"/>
       <c r="AQ27" s="4"/>
-      <c r="AR27" s="24"/>
-      <c r="AS27" s="21"/>
-      <c r="AT27" s="5"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="4"/>
+      <c r="AT27" s="4"/>
       <c r="AU27" s="24"/>
       <c r="AV27" s="21"/>
       <c r="AW27" s="5"/>
-      <c r="AX27" s="4"/>
-      <c r="AY27" s="4"/>
-      <c r="AZ27" s="4"/>
-      <c r="BA27" s="3"/>
+      <c r="AX27" s="24"/>
+      <c r="AY27" s="21"/>
+      <c r="AZ27" s="5"/>
+      <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="4" t="s">
+      <c r="BC27" s="4"/>
+      <c r="BD27" s="3"/>
+      <c r="BE27" s="4"/>
+      <c r="BF27" s="5"/>
+      <c r="BG27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE27" s="4"/>
-      <c r="BF27" s="4"/>
-      <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
       <c r="BJ27" s="4"/>
-      <c r="BK27" s="5"/>
-    </row>
-    <row r="28" spans="1:63" ht="14" customHeight="1">
+      <c r="BK27" s="4"/>
+      <c r="BL27" s="4"/>
+      <c r="BM27" s="5"/>
+    </row>
+    <row r="28" spans="1:65" ht="14" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>80</v>
       </c>
@@ -6510,36 +6642,38 @@
       <c r="AI28" s="3"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5"/>
-      <c r="AL28" s="4"/>
+      <c r="AL28" s="3"/>
       <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="3"/>
+      <c r="AN28" s="5"/>
+      <c r="AO28" s="4"/>
       <c r="AP28" s="4"/>
       <c r="AQ28" s="4"/>
       <c r="AR28" s="3"/>
       <c r="AS28" s="4"/>
-      <c r="AT28" s="5"/>
+      <c r="AT28" s="4"/>
       <c r="AU28" s="3"/>
       <c r="AV28" s="4"/>
       <c r="AW28" s="5"/>
-      <c r="AX28" s="4"/>
+      <c r="AX28" s="3"/>
       <c r="AY28" s="4"/>
-      <c r="AZ28" s="4"/>
-      <c r="BA28" s="3"/>
+      <c r="AZ28" s="5"/>
+      <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="4" t="s">
+      <c r="BC28" s="4"/>
+      <c r="BD28" s="3"/>
+      <c r="BE28" s="4"/>
+      <c r="BF28" s="5"/>
+      <c r="BG28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE28" s="4"/>
-      <c r="BF28" s="4"/>
-      <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
       <c r="BJ28" s="4"/>
-      <c r="BK28" s="5"/>
-    </row>
-    <row r="29" spans="1:63" ht="14" customHeight="1">
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+      <c r="BM28" s="5"/>
+    </row>
+    <row r="29" spans="1:65" ht="14" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>81</v>
       </c>
@@ -6587,36 +6721,38 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5"/>
-      <c r="AL29" s="4"/>
+      <c r="AL29" s="3"/>
       <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="3"/>
+      <c r="AN29" s="5"/>
+      <c r="AO29" s="4"/>
       <c r="AP29" s="4"/>
       <c r="AQ29" s="4"/>
       <c r="AR29" s="3"/>
       <c r="AS29" s="4"/>
-      <c r="AT29" s="5"/>
+      <c r="AT29" s="4"/>
       <c r="AU29" s="3"/>
       <c r="AV29" s="4"/>
       <c r="AW29" s="5"/>
-      <c r="AX29" s="4"/>
+      <c r="AX29" s="3"/>
       <c r="AY29" s="4"/>
-      <c r="AZ29" s="4"/>
-      <c r="BA29" s="3"/>
+      <c r="AZ29" s="5"/>
+      <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="4" t="s">
+      <c r="BC29" s="4"/>
+      <c r="BD29" s="3"/>
+      <c r="BE29" s="4"/>
+      <c r="BF29" s="5"/>
+      <c r="BG29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BE29" s="4"/>
-      <c r="BF29" s="4"/>
-      <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="4"/>
-      <c r="BK29" s="5"/>
-    </row>
-    <row r="30" spans="1:63" ht="14" customHeight="1">
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+      <c r="BM29" s="5"/>
+    </row>
+    <row r="30" spans="1:65" ht="14" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -6654,34 +6790,36 @@
       <c r="AI30" s="3"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5"/>
-      <c r="AL30" s="4"/>
+      <c r="AL30" s="3"/>
       <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="3"/>
+      <c r="AN30" s="5"/>
+      <c r="AO30" s="4"/>
       <c r="AP30" s="4"/>
       <c r="AQ30" s="4"/>
       <c r="AR30" s="3"/>
       <c r="AS30" s="4"/>
-      <c r="AT30" s="5"/>
+      <c r="AT30" s="4"/>
       <c r="AU30" s="3"/>
       <c r="AV30" s="4"/>
       <c r="AW30" s="5"/>
-      <c r="AX30" s="4"/>
+      <c r="AX30" s="3"/>
       <c r="AY30" s="4"/>
-      <c r="AZ30" s="4"/>
-      <c r="BA30" s="3"/>
+      <c r="AZ30" s="5"/>
+      <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="4"/>
+      <c r="BC30" s="4"/>
+      <c r="BD30" s="3"/>
       <c r="BE30" s="4"/>
-      <c r="BF30" s="4"/>
+      <c r="BF30" s="5"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="4"/>
-      <c r="BK30" s="5"/>
-    </row>
-    <row r="31" spans="1:63" ht="14" customHeight="1">
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+      <c r="BM30" s="5"/>
+    </row>
+    <row r="31" spans="1:65" ht="14" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -6719,34 +6857,36 @@
       <c r="AI31" s="3"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5"/>
-      <c r="AL31" s="4"/>
+      <c r="AL31" s="3"/>
       <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="3"/>
+      <c r="AN31" s="5"/>
+      <c r="AO31" s="4"/>
       <c r="AP31" s="4"/>
       <c r="AQ31" s="4"/>
       <c r="AR31" s="3"/>
       <c r="AS31" s="4"/>
-      <c r="AT31" s="5"/>
+      <c r="AT31" s="4"/>
       <c r="AU31" s="3"/>
       <c r="AV31" s="4"/>
       <c r="AW31" s="5"/>
-      <c r="AX31" s="4"/>
+      <c r="AX31" s="3"/>
       <c r="AY31" s="4"/>
-      <c r="AZ31" s="4"/>
-      <c r="BA31" s="3"/>
+      <c r="AZ31" s="5"/>
+      <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="4"/>
+      <c r="BC31" s="4"/>
+      <c r="BD31" s="3"/>
       <c r="BE31" s="4"/>
-      <c r="BF31" s="4"/>
+      <c r="BF31" s="5"/>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="4"/>
-      <c r="BK31" s="5"/>
-    </row>
-    <row r="32" spans="1:63" ht="14" customHeight="1">
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+      <c r="BM31" s="5"/>
+    </row>
+    <row r="32" spans="1:65" ht="14" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -6784,34 +6924,36 @@
       <c r="AI32" s="3"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="5"/>
-      <c r="AL32" s="4"/>
+      <c r="AL32" s="3"/>
       <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="3"/>
+      <c r="AN32" s="5"/>
+      <c r="AO32" s="4"/>
       <c r="AP32" s="4"/>
       <c r="AQ32" s="4"/>
       <c r="AR32" s="3"/>
       <c r="AS32" s="4"/>
-      <c r="AT32" s="5"/>
+      <c r="AT32" s="4"/>
       <c r="AU32" s="3"/>
       <c r="AV32" s="4"/>
       <c r="AW32" s="5"/>
-      <c r="AX32" s="4"/>
+      <c r="AX32" s="3"/>
       <c r="AY32" s="4"/>
-      <c r="AZ32" s="4"/>
-      <c r="BA32" s="3"/>
+      <c r="AZ32" s="5"/>
+      <c r="BA32" s="4"/>
       <c r="BB32" s="4"/>
-      <c r="BC32" s="5"/>
-      <c r="BD32" s="4"/>
+      <c r="BC32" s="4"/>
+      <c r="BD32" s="3"/>
       <c r="BE32" s="4"/>
-      <c r="BF32" s="4"/>
+      <c r="BF32" s="5"/>
       <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
       <c r="BJ32" s="4"/>
-      <c r="BK32" s="5"/>
-    </row>
-    <row r="33" spans="1:63" ht="14" customHeight="1">
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+      <c r="BM32" s="5"/>
+    </row>
+    <row r="33" spans="1:65" ht="14" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -6849,34 +6991,36 @@
       <c r="AI33" s="3"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="5"/>
-      <c r="AL33" s="4"/>
+      <c r="AL33" s="3"/>
       <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="3"/>
+      <c r="AN33" s="5"/>
+      <c r="AO33" s="4"/>
       <c r="AP33" s="4"/>
       <c r="AQ33" s="4"/>
       <c r="AR33" s="3"/>
       <c r="AS33" s="4"/>
-      <c r="AT33" s="5"/>
+      <c r="AT33" s="4"/>
       <c r="AU33" s="3"/>
       <c r="AV33" s="4"/>
       <c r="AW33" s="5"/>
-      <c r="AX33" s="4"/>
+      <c r="AX33" s="3"/>
       <c r="AY33" s="4"/>
-      <c r="AZ33" s="4"/>
-      <c r="BA33" s="3"/>
+      <c r="AZ33" s="5"/>
+      <c r="BA33" s="4"/>
       <c r="BB33" s="4"/>
-      <c r="BC33" s="5"/>
-      <c r="BD33" s="4"/>
+      <c r="BC33" s="4"/>
+      <c r="BD33" s="3"/>
       <c r="BE33" s="4"/>
-      <c r="BF33" s="4"/>
+      <c r="BF33" s="5"/>
       <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
       <c r="BJ33" s="4"/>
-      <c r="BK33" s="5"/>
-    </row>
-    <row r="34" spans="1:63" ht="14" customHeight="1">
+      <c r="BK33" s="4"/>
+      <c r="BL33" s="4"/>
+      <c r="BM33" s="5"/>
+    </row>
+    <row r="34" spans="1:65" ht="14" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -6914,34 +7058,36 @@
       <c r="AI34" s="3"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5"/>
-      <c r="AL34" s="4"/>
+      <c r="AL34" s="3"/>
       <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="3"/>
+      <c r="AN34" s="5"/>
+      <c r="AO34" s="4"/>
       <c r="AP34" s="4"/>
       <c r="AQ34" s="4"/>
       <c r="AR34" s="3"/>
       <c r="AS34" s="4"/>
-      <c r="AT34" s="5"/>
+      <c r="AT34" s="4"/>
       <c r="AU34" s="3"/>
       <c r="AV34" s="4"/>
       <c r="AW34" s="5"/>
-      <c r="AX34" s="4"/>
+      <c r="AX34" s="3"/>
       <c r="AY34" s="4"/>
-      <c r="AZ34" s="4"/>
-      <c r="BA34" s="3"/>
+      <c r="AZ34" s="5"/>
+      <c r="BA34" s="4"/>
       <c r="BB34" s="4"/>
-      <c r="BC34" s="5"/>
-      <c r="BD34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="3"/>
       <c r="BE34" s="4"/>
-      <c r="BF34" s="4"/>
+      <c r="BF34" s="5"/>
       <c r="BG34" s="4"/>
       <c r="BH34" s="4"/>
       <c r="BI34" s="4"/>
       <c r="BJ34" s="4"/>
-      <c r="BK34" s="5"/>
-    </row>
-    <row r="35" spans="1:63" ht="14" customHeight="1">
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+      <c r="BM34" s="5"/>
+    </row>
+    <row r="35" spans="1:65" ht="14" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -6979,34 +7125,36 @@
       <c r="AI35" s="3"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="5"/>
-      <c r="AL35" s="4"/>
+      <c r="AL35" s="3"/>
       <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="3"/>
+      <c r="AN35" s="5"/>
+      <c r="AO35" s="4"/>
       <c r="AP35" s="4"/>
       <c r="AQ35" s="4"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="4"/>
-      <c r="AT35" s="5"/>
+      <c r="AT35" s="4"/>
       <c r="AU35" s="3"/>
       <c r="AV35" s="4"/>
       <c r="AW35" s="5"/>
-      <c r="AX35" s="4"/>
+      <c r="AX35" s="3"/>
       <c r="AY35" s="4"/>
-      <c r="AZ35" s="4"/>
-      <c r="BA35" s="3"/>
+      <c r="AZ35" s="5"/>
+      <c r="BA35" s="4"/>
       <c r="BB35" s="4"/>
-      <c r="BC35" s="5"/>
-      <c r="BD35" s="4"/>
+      <c r="BC35" s="4"/>
+      <c r="BD35" s="3"/>
       <c r="BE35" s="4"/>
-      <c r="BF35" s="4"/>
+      <c r="BF35" s="5"/>
       <c r="BG35" s="4"/>
       <c r="BH35" s="4"/>
       <c r="BI35" s="4"/>
       <c r="BJ35" s="4"/>
-      <c r="BK35" s="5"/>
-    </row>
-    <row r="36" spans="1:63" ht="14" customHeight="1">
+      <c r="BK35" s="4"/>
+      <c r="BL35" s="4"/>
+      <c r="BM35" s="5"/>
+    </row>
+    <row r="36" spans="1:65" ht="14" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -7044,34 +7192,36 @@
       <c r="AI36" s="3"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="5"/>
-      <c r="AL36" s="4"/>
+      <c r="AL36" s="3"/>
       <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="3"/>
+      <c r="AN36" s="5"/>
+      <c r="AO36" s="4"/>
       <c r="AP36" s="4"/>
       <c r="AQ36" s="4"/>
       <c r="AR36" s="3"/>
       <c r="AS36" s="4"/>
-      <c r="AT36" s="5"/>
+      <c r="AT36" s="4"/>
       <c r="AU36" s="3"/>
       <c r="AV36" s="4"/>
       <c r="AW36" s="5"/>
-      <c r="AX36" s="4"/>
+      <c r="AX36" s="3"/>
       <c r="AY36" s="4"/>
-      <c r="AZ36" s="4"/>
-      <c r="BA36" s="3"/>
+      <c r="AZ36" s="5"/>
+      <c r="BA36" s="4"/>
       <c r="BB36" s="4"/>
-      <c r="BC36" s="5"/>
-      <c r="BD36" s="4"/>
+      <c r="BC36" s="4"/>
+      <c r="BD36" s="3"/>
       <c r="BE36" s="4"/>
-      <c r="BF36" s="4"/>
+      <c r="BF36" s="5"/>
       <c r="BG36" s="4"/>
       <c r="BH36" s="4"/>
       <c r="BI36" s="4"/>
       <c r="BJ36" s="4"/>
-      <c r="BK36" s="5"/>
-    </row>
-    <row r="37" spans="1:63" ht="14" customHeight="1">
+      <c r="BK36" s="4"/>
+      <c r="BL36" s="4"/>
+      <c r="BM36" s="5"/>
+    </row>
+    <row r="37" spans="1:65" ht="14" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -7109,34 +7259,36 @@
       <c r="AI37" s="3"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="5"/>
-      <c r="AL37" s="4"/>
+      <c r="AL37" s="3"/>
       <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="3"/>
+      <c r="AN37" s="5"/>
+      <c r="AO37" s="4"/>
       <c r="AP37" s="4"/>
       <c r="AQ37" s="4"/>
       <c r="AR37" s="3"/>
       <c r="AS37" s="4"/>
-      <c r="AT37" s="5"/>
+      <c r="AT37" s="4"/>
       <c r="AU37" s="3"/>
       <c r="AV37" s="4"/>
       <c r="AW37" s="5"/>
-      <c r="AX37" s="4"/>
+      <c r="AX37" s="3"/>
       <c r="AY37" s="4"/>
-      <c r="AZ37" s="4"/>
-      <c r="BA37" s="3"/>
+      <c r="AZ37" s="5"/>
+      <c r="BA37" s="4"/>
       <c r="BB37" s="4"/>
-      <c r="BC37" s="5"/>
-      <c r="BD37" s="4"/>
+      <c r="BC37" s="4"/>
+      <c r="BD37" s="3"/>
       <c r="BE37" s="4"/>
-      <c r="BF37" s="4"/>
+      <c r="BF37" s="5"/>
       <c r="BG37" s="4"/>
       <c r="BH37" s="4"/>
       <c r="BI37" s="4"/>
       <c r="BJ37" s="4"/>
-      <c r="BK37" s="5"/>
-    </row>
-    <row r="38" spans="1:63" ht="14" customHeight="1">
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+      <c r="BM37" s="5"/>
+    </row>
+    <row r="38" spans="1:65" ht="14" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -7174,34 +7326,36 @@
       <c r="AI38" s="3"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="5"/>
-      <c r="AL38" s="4"/>
+      <c r="AL38" s="3"/>
       <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="3"/>
+      <c r="AN38" s="5"/>
+      <c r="AO38" s="4"/>
       <c r="AP38" s="4"/>
       <c r="AQ38" s="4"/>
       <c r="AR38" s="3"/>
       <c r="AS38" s="4"/>
-      <c r="AT38" s="5"/>
+      <c r="AT38" s="4"/>
       <c r="AU38" s="3"/>
       <c r="AV38" s="4"/>
       <c r="AW38" s="5"/>
-      <c r="AX38" s="4"/>
+      <c r="AX38" s="3"/>
       <c r="AY38" s="4"/>
-      <c r="AZ38" s="4"/>
-      <c r="BA38" s="3"/>
+      <c r="AZ38" s="5"/>
+      <c r="BA38" s="4"/>
       <c r="BB38" s="4"/>
-      <c r="BC38" s="5"/>
-      <c r="BD38" s="4"/>
+      <c r="BC38" s="4"/>
+      <c r="BD38" s="3"/>
       <c r="BE38" s="4"/>
-      <c r="BF38" s="4"/>
+      <c r="BF38" s="5"/>
       <c r="BG38" s="4"/>
       <c r="BH38" s="4"/>
       <c r="BI38" s="4"/>
       <c r="BJ38" s="4"/>
-      <c r="BK38" s="5"/>
-    </row>
-    <row r="39" spans="1:63" ht="14" customHeight="1">
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+      <c r="BM38" s="5"/>
+    </row>
+    <row r="39" spans="1:65" ht="14" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -7239,34 +7393,36 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="5"/>
-      <c r="AL39" s="4"/>
+      <c r="AL39" s="3"/>
       <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="3"/>
+      <c r="AN39" s="5"/>
+      <c r="AO39" s="4"/>
       <c r="AP39" s="4"/>
       <c r="AQ39" s="4"/>
       <c r="AR39" s="3"/>
       <c r="AS39" s="4"/>
-      <c r="AT39" s="5"/>
+      <c r="AT39" s="4"/>
       <c r="AU39" s="3"/>
       <c r="AV39" s="4"/>
       <c r="AW39" s="5"/>
-      <c r="AX39" s="4"/>
+      <c r="AX39" s="3"/>
       <c r="AY39" s="4"/>
-      <c r="AZ39" s="4"/>
-      <c r="BA39" s="3"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="4"/>
       <c r="BB39" s="4"/>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="3"/>
       <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
+      <c r="BF39" s="5"/>
       <c r="BG39" s="4"/>
       <c r="BH39" s="4"/>
       <c r="BI39" s="4"/>
       <c r="BJ39" s="4"/>
-      <c r="BK39" s="5"/>
-    </row>
-    <row r="40" spans="1:63" ht="14" customHeight="1">
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="5"/>
+    </row>
+    <row r="40" spans="1:65" ht="14" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -7304,34 +7460,36 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="5"/>
-      <c r="AL40" s="4"/>
+      <c r="AL40" s="3"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="4"/>
-      <c r="AO40" s="3"/>
+      <c r="AN40" s="5"/>
+      <c r="AO40" s="4"/>
       <c r="AP40" s="4"/>
       <c r="AQ40" s="4"/>
       <c r="AR40" s="3"/>
       <c r="AS40" s="4"/>
-      <c r="AT40" s="5"/>
+      <c r="AT40" s="4"/>
       <c r="AU40" s="3"/>
       <c r="AV40" s="4"/>
       <c r="AW40" s="5"/>
-      <c r="AX40" s="4"/>
+      <c r="AX40" s="3"/>
       <c r="AY40" s="4"/>
-      <c r="AZ40" s="4"/>
-      <c r="BA40" s="3"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="4"/>
       <c r="BB40" s="4"/>
-      <c r="BC40" s="5"/>
-      <c r="BD40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="3"/>
       <c r="BE40" s="4"/>
-      <c r="BF40" s="4"/>
+      <c r="BF40" s="5"/>
       <c r="BG40" s="4"/>
       <c r="BH40" s="4"/>
       <c r="BI40" s="4"/>
       <c r="BJ40" s="4"/>
-      <c r="BK40" s="5"/>
-    </row>
-    <row r="41" spans="1:63" ht="14" customHeight="1">
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="5"/>
+    </row>
+    <row r="41" spans="1:65" ht="14" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
@@ -7369,34 +7527,36 @@
       <c r="AI41" s="3"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="5"/>
-      <c r="AL41" s="4"/>
+      <c r="AL41" s="3"/>
       <c r="AM41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="AO41" s="3"/>
+      <c r="AN41" s="5"/>
+      <c r="AO41" s="4"/>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="4"/>
       <c r="AR41" s="3"/>
       <c r="AS41" s="4"/>
-      <c r="AT41" s="5"/>
+      <c r="AT41" s="4"/>
       <c r="AU41" s="3"/>
       <c r="AV41" s="4"/>
       <c r="AW41" s="5"/>
-      <c r="AX41" s="4"/>
+      <c r="AX41" s="3"/>
       <c r="AY41" s="4"/>
-      <c r="AZ41" s="4"/>
-      <c r="BA41" s="3"/>
+      <c r="AZ41" s="5"/>
+      <c r="BA41" s="4"/>
       <c r="BB41" s="4"/>
-      <c r="BC41" s="5"/>
-      <c r="BD41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="3"/>
       <c r="BE41" s="4"/>
-      <c r="BF41" s="4"/>
+      <c r="BF41" s="5"/>
       <c r="BG41" s="4"/>
       <c r="BH41" s="4"/>
       <c r="BI41" s="4"/>
       <c r="BJ41" s="4"/>
-      <c r="BK41" s="5"/>
-    </row>
-    <row r="42" spans="1:63" ht="14" customHeight="1">
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="5"/>
+    </row>
+    <row r="42" spans="1:65" ht="14" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
@@ -7434,34 +7594,36 @@
       <c r="AI42" s="3"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="5"/>
-      <c r="AL42" s="4"/>
+      <c r="AL42" s="3"/>
       <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="3"/>
+      <c r="AN42" s="5"/>
+      <c r="AO42" s="4"/>
       <c r="AP42" s="4"/>
       <c r="AQ42" s="4"/>
       <c r="AR42" s="3"/>
       <c r="AS42" s="4"/>
-      <c r="AT42" s="5"/>
+      <c r="AT42" s="4"/>
       <c r="AU42" s="3"/>
       <c r="AV42" s="4"/>
       <c r="AW42" s="5"/>
-      <c r="AX42" s="4"/>
+      <c r="AX42" s="3"/>
       <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="3"/>
+      <c r="AZ42" s="5"/>
+      <c r="BA42" s="4"/>
       <c r="BB42" s="4"/>
-      <c r="BC42" s="5"/>
-      <c r="BD42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="3"/>
       <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
+      <c r="BF42" s="5"/>
       <c r="BG42" s="4"/>
       <c r="BH42" s="4"/>
       <c r="BI42" s="4"/>
       <c r="BJ42" s="4"/>
-      <c r="BK42" s="5"/>
-    </row>
-    <row r="43" spans="1:63" ht="14" customHeight="1">
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="5"/>
+    </row>
+    <row r="43" spans="1:65" ht="14" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
@@ -7499,34 +7661,36 @@
       <c r="AI43" s="3"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="5"/>
-      <c r="AL43" s="4"/>
+      <c r="AL43" s="3"/>
       <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="AO43" s="3"/>
+      <c r="AN43" s="5"/>
+      <c r="AO43" s="4"/>
       <c r="AP43" s="4"/>
       <c r="AQ43" s="4"/>
       <c r="AR43" s="3"/>
       <c r="AS43" s="4"/>
-      <c r="AT43" s="5"/>
+      <c r="AT43" s="4"/>
       <c r="AU43" s="3"/>
       <c r="AV43" s="4"/>
       <c r="AW43" s="5"/>
-      <c r="AX43" s="4"/>
+      <c r="AX43" s="3"/>
       <c r="AY43" s="4"/>
-      <c r="AZ43" s="4"/>
-      <c r="BA43" s="3"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="4"/>
       <c r="BB43" s="4"/>
-      <c r="BC43" s="5"/>
-      <c r="BD43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="3"/>
       <c r="BE43" s="4"/>
-      <c r="BF43" s="4"/>
+      <c r="BF43" s="5"/>
       <c r="BG43" s="4"/>
       <c r="BH43" s="4"/>
       <c r="BI43" s="4"/>
       <c r="BJ43" s="4"/>
-      <c r="BK43" s="5"/>
-    </row>
-    <row r="44" spans="1:63" ht="14" customHeight="1">
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="5"/>
+    </row>
+    <row r="44" spans="1:65" ht="14" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
@@ -7564,34 +7728,36 @@
       <c r="AI44" s="3"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="5"/>
-      <c r="AL44" s="4"/>
+      <c r="AL44" s="3"/>
       <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="3"/>
+      <c r="AN44" s="5"/>
+      <c r="AO44" s="4"/>
       <c r="AP44" s="4"/>
       <c r="AQ44" s="4"/>
       <c r="AR44" s="3"/>
       <c r="AS44" s="4"/>
-      <c r="AT44" s="5"/>
+      <c r="AT44" s="4"/>
       <c r="AU44" s="3"/>
       <c r="AV44" s="4"/>
       <c r="AW44" s="5"/>
-      <c r="AX44" s="4"/>
+      <c r="AX44" s="3"/>
       <c r="AY44" s="4"/>
-      <c r="AZ44" s="4"/>
-      <c r="BA44" s="3"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="4"/>
       <c r="BB44" s="4"/>
-      <c r="BC44" s="5"/>
-      <c r="BD44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="3"/>
       <c r="BE44" s="4"/>
-      <c r="BF44" s="4"/>
+      <c r="BF44" s="5"/>
       <c r="BG44" s="4"/>
       <c r="BH44" s="4"/>
       <c r="BI44" s="4"/>
       <c r="BJ44" s="4"/>
-      <c r="BK44" s="5"/>
-    </row>
-    <row r="45" spans="1:63" ht="14" customHeight="1">
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="5"/>
+    </row>
+    <row r="45" spans="1:65" ht="14" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="3"/>
@@ -7629,38 +7795,40 @@
       <c r="AI45" s="3"/>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="5"/>
-      <c r="AL45" s="4"/>
+      <c r="AL45" s="3"/>
       <c r="AM45" s="4"/>
-      <c r="AN45" s="4"/>
-      <c r="AO45" s="3"/>
+      <c r="AN45" s="5"/>
+      <c r="AO45" s="4"/>
       <c r="AP45" s="4"/>
       <c r="AQ45" s="4"/>
       <c r="AR45" s="3"/>
       <c r="AS45" s="4"/>
-      <c r="AT45" s="5"/>
+      <c r="AT45" s="4"/>
       <c r="AU45" s="3"/>
       <c r="AV45" s="4"/>
       <c r="AW45" s="5"/>
-      <c r="AX45" s="4"/>
+      <c r="AX45" s="3"/>
       <c r="AY45" s="4"/>
-      <c r="AZ45" s="4"/>
-      <c r="BA45" s="3"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="4"/>
       <c r="BB45" s="4"/>
-      <c r="BC45" s="5"/>
-      <c r="BD45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="3"/>
       <c r="BE45" s="4"/>
-      <c r="BF45" s="4"/>
+      <c r="BF45" s="5"/>
       <c r="BG45" s="4"/>
       <c r="BH45" s="4"/>
       <c r="BI45" s="4"/>
       <c r="BJ45" s="4"/>
-      <c r="BK45" s="5"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+      <c r="BM45" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
@@ -7669,11 +7837,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA7DE17-74C0-0647-8E2B-58F9351B9DA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D85CA3-9605-3140-9386-769E498AB943}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BK45"/>
+  <dimension ref="A1:BM45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.42578125" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="26" width="2.42578125" style="6"/>
@@ -7681,7 +7849,7 @@
     <col min="31" max="16384" width="2.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="14" customHeight="1">
+    <row r="1" spans="1:65" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -7729,12 +7897,12 @@
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
       <c r="AW1" s="4"/>
       <c r="AX1" s="4"/>
@@ -7750,9 +7918,11 @@
       <c r="BH1" s="4"/>
       <c r="BI1" s="4"/>
       <c r="BJ1" s="4"/>
-      <c r="BK1" s="5"/>
-    </row>
-    <row r="2" spans="1:63" ht="14" customHeight="1">
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="5"/>
+    </row>
+    <row r="2" spans="1:65" ht="14" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -7800,10 +7970,10 @@
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="4"/>
-      <c r="AT2" s="4"/>
-      <c r="AU2" s="4"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="3"/>
       <c r="AV2" s="4"/>
       <c r="AW2" s="4"/>
       <c r="AX2" s="4"/>
@@ -7819,9 +7989,11 @@
       <c r="BH2" s="4"/>
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
-      <c r="BK2" s="5"/>
-    </row>
-    <row r="3" spans="1:63" ht="14" customHeight="1">
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="4"/>
+      <c r="BM2" s="5"/>
+    </row>
+    <row r="3" spans="1:65" ht="14" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -7871,10 +8043,10 @@
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2"/>
+      <c r="AU3" s="3"/>
       <c r="AV3" s="4"/>
       <c r="AW3" s="4"/>
       <c r="AX3" s="4"/>
@@ -7890,9 +8062,11 @@
       <c r="BH3" s="4"/>
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
-      <c r="BK3" s="5"/>
-    </row>
-    <row r="4" spans="1:63" ht="14" customHeight="1">
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="5"/>
+    </row>
+    <row r="4" spans="1:65" ht="14" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -7957,13 +8131,15 @@
       <c r="BH4" s="8"/>
       <c r="BI4" s="8"/>
       <c r="BJ4" s="8"/>
-      <c r="BK4" s="9"/>
-    </row>
-    <row r="5" spans="1:63" ht="14" customHeight="1">
+      <c r="BK4" s="8"/>
+      <c r="BL4" s="8"/>
+      <c r="BM4" s="9"/>
+    </row>
+    <row r="5" spans="1:65" ht="14" customHeight="1">
       <c r="A5" s="10"/>
-      <c r="BK5" s="11"/>
-    </row>
-    <row r="6" spans="1:63" ht="14" customHeight="1">
+      <c r="BM5" s="11"/>
+    </row>
+    <row r="6" spans="1:65" ht="14" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -8026,9 +8202,11 @@
       <c r="BH6" s="13"/>
       <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="14"/>
-    </row>
-    <row r="8" spans="1:63" ht="14" customHeight="1">
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="14"/>
+    </row>
+    <row r="8" spans="1:65" ht="14" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
@@ -8071,12 +8249,12 @@
       <c r="AF8" s="17"/>
       <c r="AG8" s="17"/>
       <c r="AH8" s="17"/>
-      <c r="AI8" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
+      <c r="AL8" s="15" t="s">
+        <v>8</v>
+      </c>
       <c r="AM8" s="17"/>
       <c r="AN8" s="17"/>
       <c r="AO8" s="17"/>
@@ -8087,29 +8265,31 @@
       <c r="AT8" s="17"/>
       <c r="AU8" s="17"/>
       <c r="AV8" s="17"/>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="15" t="s">
+      <c r="AW8" s="17"/>
+      <c r="AX8" s="17"/>
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="15" t="s">
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="17"/>
+      <c r="BD8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="16"/>
-      <c r="BD8" s="17" t="s">
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="16"/>
+      <c r="BG8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="17"/>
       <c r="BH8" s="17"/>
       <c r="BI8" s="17"/>
       <c r="BJ8" s="17"/>
-      <c r="BK8" s="16"/>
-    </row>
-    <row r="9" spans="1:63" ht="14" customHeight="1">
+      <c r="BK8" s="17"/>
+      <c r="BL8" s="17"/>
+      <c r="BM8" s="16"/>
+    </row>
+    <row r="9" spans="1:65" ht="14" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="20"/>
       <c r="C9" s="18" t="s">
@@ -8165,46 +8345,50 @@
       <c r="AG9" s="20"/>
       <c r="AH9" s="20"/>
       <c r="AI9" s="18" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="19"/>
-      <c r="AL9" s="20" t="s">
+      <c r="AL9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="AM9" s="20"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="18" t="s">
-        <v>27</v>
       </c>
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="18" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="AS9" s="20"/>
       <c r="AT9" s="20"/>
       <c r="AU9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="AV9" s="20"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="18"/>
       <c r="AY9" s="20"/>
-      <c r="AZ9" s="20"/>
+      <c r="AZ9" s="19"/>
       <c r="BA9" s="18"/>
       <c r="BB9" s="20"/>
-      <c r="BC9" s="19"/>
-      <c r="BD9" s="20"/>
+      <c r="BC9" s="20"/>
+      <c r="BD9" s="18"/>
       <c r="BE9" s="20"/>
-      <c r="BF9" s="20"/>
+      <c r="BF9" s="19"/>
       <c r="BG9" s="20"/>
       <c r="BH9" s="20"/>
       <c r="BI9" s="20"/>
       <c r="BJ9" s="20"/>
-      <c r="BK9" s="19"/>
-    </row>
-    <row r="10" spans="1:63" ht="14" customHeight="1">
+      <c r="BK9" s="20"/>
+      <c r="BL9" s="20"/>
+      <c r="BM9" s="19"/>
+    </row>
+    <row r="10" spans="1:65" ht="14" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -8251,15 +8435,15 @@
       <c r="AF10" s="26"/>
       <c r="AG10" s="26"/>
       <c r="AH10" s="26"/>
-      <c r="AI10" s="25" t="s">
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="26"/>
+      <c r="AK10" s="28"/>
+      <c r="AL10" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="AJ10" s="26"/>
-      <c r="AK10" s="27"/>
-      <c r="AL10" s="26"/>
       <c r="AM10" s="26"/>
-      <c r="AN10" s="26"/>
-      <c r="AO10" s="25"/>
+      <c r="AN10" s="27"/>
+      <c r="AO10" s="26"/>
       <c r="AP10" s="26"/>
       <c r="AQ10" s="26"/>
       <c r="AR10" s="25"/>
@@ -8267,23 +8451,25 @@
       <c r="AT10" s="26"/>
       <c r="AU10" s="25"/>
       <c r="AV10" s="26"/>
-      <c r="AW10" s="28"/>
-      <c r="AX10" s="26"/>
+      <c r="AW10" s="26"/>
+      <c r="AX10" s="25"/>
       <c r="AY10" s="26"/>
-      <c r="AZ10" s="26"/>
-      <c r="BA10" s="25"/>
+      <c r="AZ10" s="28"/>
+      <c r="BA10" s="26"/>
       <c r="BB10" s="26"/>
-      <c r="BC10" s="28"/>
-      <c r="BD10" s="26"/>
+      <c r="BC10" s="26"/>
+      <c r="BD10" s="25"/>
       <c r="BE10" s="26"/>
-      <c r="BF10" s="26"/>
+      <c r="BF10" s="28"/>
       <c r="BG10" s="26"/>
       <c r="BH10" s="26"/>
       <c r="BI10" s="26"/>
       <c r="BJ10" s="26"/>
-      <c r="BK10" s="28"/>
-    </row>
-    <row r="11" spans="1:63" ht="14" customHeight="1">
+      <c r="BK10" s="26"/>
+      <c r="BL10" s="26"/>
+      <c r="BM10" s="28"/>
+    </row>
+    <row r="11" spans="1:65" ht="14" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -8328,39 +8514,41 @@
       <c r="AF11" s="30"/>
       <c r="AG11" s="29"/>
       <c r="AH11" s="29"/>
-      <c r="AI11" s="25" t="s">
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="AJ11" s="26"/>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="29"/>
-      <c r="AM11" s="29"/>
-      <c r="AN11" s="29"/>
-      <c r="AO11" s="30"/>
+      <c r="AM11" s="26"/>
+      <c r="AN11" s="27"/>
+      <c r="AO11" s="29"/>
       <c r="AP11" s="29"/>
       <c r="AQ11" s="29"/>
       <c r="AR11" s="30"/>
       <c r="AS11" s="29"/>
       <c r="AT11" s="29"/>
-      <c r="AU11" s="25"/>
-      <c r="AV11" s="26"/>
-      <c r="AW11" s="31"/>
-      <c r="AX11" s="29"/>
-      <c r="AY11" s="29"/>
-      <c r="AZ11" s="29"/>
-      <c r="BA11" s="30"/>
+      <c r="AU11" s="30"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="29"/>
+      <c r="AX11" s="25"/>
+      <c r="AY11" s="26"/>
+      <c r="AZ11" s="31"/>
+      <c r="BA11" s="29"/>
       <c r="BB11" s="29"/>
-      <c r="BC11" s="31"/>
-      <c r="BD11" s="29"/>
+      <c r="BC11" s="29"/>
+      <c r="BD11" s="30"/>
       <c r="BE11" s="29"/>
-      <c r="BF11" s="29"/>
+      <c r="BF11" s="31"/>
       <c r="BG11" s="29"/>
       <c r="BH11" s="29"/>
       <c r="BI11" s="29"/>
       <c r="BJ11" s="29"/>
-      <c r="BK11" s="31"/>
-    </row>
-    <row r="12" spans="1:63" ht="14" customHeight="1">
+      <c r="BK11" s="29"/>
+      <c r="BL11" s="29"/>
+      <c r="BM11" s="31"/>
+    </row>
+    <row r="12" spans="1:65" ht="14" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -8407,39 +8595,41 @@
       <c r="AF12" s="30"/>
       <c r="AG12" s="29"/>
       <c r="AH12" s="29"/>
-      <c r="AI12" s="25" t="s">
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="AJ12" s="26"/>
-      <c r="AK12" s="27"/>
-      <c r="AL12" s="29"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="30"/>
+      <c r="AM12" s="26"/>
+      <c r="AN12" s="27"/>
+      <c r="AO12" s="29"/>
       <c r="AP12" s="29"/>
       <c r="AQ12" s="29"/>
       <c r="AR12" s="30"/>
       <c r="AS12" s="29"/>
       <c r="AT12" s="29"/>
-      <c r="AU12" s="25"/>
-      <c r="AV12" s="26"/>
-      <c r="AW12" s="31"/>
-      <c r="AX12" s="29"/>
-      <c r="AY12" s="29"/>
-      <c r="AZ12" s="29"/>
-      <c r="BA12" s="30"/>
+      <c r="AU12" s="30"/>
+      <c r="AV12" s="29"/>
+      <c r="AW12" s="29"/>
+      <c r="AX12" s="25"/>
+      <c r="AY12" s="26"/>
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="29"/>
       <c r="BB12" s="29"/>
-      <c r="BC12" s="31"/>
-      <c r="BD12" s="29"/>
+      <c r="BC12" s="29"/>
+      <c r="BD12" s="30"/>
       <c r="BE12" s="29"/>
-      <c r="BF12" s="29"/>
+      <c r="BF12" s="31"/>
       <c r="BG12" s="29"/>
       <c r="BH12" s="29"/>
       <c r="BI12" s="29"/>
       <c r="BJ12" s="29"/>
-      <c r="BK12" s="31"/>
-    </row>
-    <row r="13" spans="1:63" ht="14" customHeight="1">
+      <c r="BK12" s="29"/>
+      <c r="BL12" s="29"/>
+      <c r="BM12" s="31"/>
+    </row>
+    <row r="13" spans="1:65" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -8484,39 +8674,41 @@
       <c r="AF13" s="30"/>
       <c r="AG13" s="29"/>
       <c r="AH13" s="29"/>
-      <c r="AI13" s="25" t="s">
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="AJ13" s="26"/>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="29"/>
-      <c r="AM13" s="29"/>
-      <c r="AN13" s="29"/>
-      <c r="AO13" s="30"/>
+      <c r="AM13" s="26"/>
+      <c r="AN13" s="27"/>
+      <c r="AO13" s="29"/>
       <c r="AP13" s="29"/>
       <c r="AQ13" s="29"/>
       <c r="AR13" s="30"/>
       <c r="AS13" s="29"/>
       <c r="AT13" s="29"/>
-      <c r="AU13" s="25"/>
-      <c r="AV13" s="26"/>
-      <c r="AW13" s="31"/>
-      <c r="AX13" s="29"/>
-      <c r="AY13" s="29"/>
-      <c r="AZ13" s="29"/>
-      <c r="BA13" s="30"/>
+      <c r="AU13" s="30"/>
+      <c r="AV13" s="29"/>
+      <c r="AW13" s="29"/>
+      <c r="AX13" s="25"/>
+      <c r="AY13" s="26"/>
+      <c r="AZ13" s="31"/>
+      <c r="BA13" s="29"/>
       <c r="BB13" s="29"/>
-      <c r="BC13" s="31"/>
-      <c r="BD13" s="29"/>
+      <c r="BC13" s="29"/>
+      <c r="BD13" s="30"/>
       <c r="BE13" s="29"/>
-      <c r="BF13" s="29"/>
+      <c r="BF13" s="31"/>
       <c r="BG13" s="29"/>
       <c r="BH13" s="29"/>
       <c r="BI13" s="29"/>
       <c r="BJ13" s="29"/>
-      <c r="BK13" s="31"/>
-    </row>
-    <row r="14" spans="1:63" ht="14" customHeight="1">
+      <c r="BK13" s="29"/>
+      <c r="BL13" s="29"/>
+      <c r="BM13" s="31"/>
+    </row>
+    <row r="14" spans="1:65" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -8563,41 +8755,45 @@
       <c r="AF14" s="30"/>
       <c r="AG14" s="29"/>
       <c r="AH14" s="29"/>
-      <c r="AI14" s="25" t="s">
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="31"/>
+      <c r="AL14" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="AJ14" s="26"/>
-      <c r="AK14" s="27"/>
-      <c r="AL14" s="29"/>
-      <c r="AM14" s="29"/>
-      <c r="AN14" s="29"/>
-      <c r="AO14" s="30"/>
+      <c r="AM14" s="26"/>
+      <c r="AN14" s="27"/>
+      <c r="AO14" s="29"/>
       <c r="AP14" s="29"/>
       <c r="AQ14" s="29"/>
-      <c r="AR14" s="30"/>
+      <c r="AR14" s="30" t="s">
+        <v>123</v>
+      </c>
       <c r="AS14" s="29"/>
       <c r="AT14" s="29"/>
-      <c r="AU14" s="25"/>
-      <c r="AV14" s="26"/>
-      <c r="AW14" s="31"/>
-      <c r="AX14" s="29"/>
-      <c r="AY14" s="29"/>
-      <c r="AZ14" s="29"/>
-      <c r="BA14" s="30"/>
+      <c r="AU14" s="30"/>
+      <c r="AV14" s="29"/>
+      <c r="AW14" s="29"/>
+      <c r="AX14" s="25"/>
+      <c r="AY14" s="26"/>
+      <c r="AZ14" s="31"/>
+      <c r="BA14" s="29"/>
       <c r="BB14" s="29"/>
-      <c r="BC14" s="31"/>
-      <c r="BD14" s="26" t="s">
+      <c r="BC14" s="29"/>
+      <c r="BD14" s="30"/>
+      <c r="BE14" s="29"/>
+      <c r="BF14" s="31"/>
+      <c r="BG14" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="BE14" s="26"/>
-      <c r="BF14" s="26"/>
-      <c r="BG14" s="26"/>
       <c r="BH14" s="26"/>
-      <c r="BI14" s="29"/>
-      <c r="BJ14" s="29"/>
-      <c r="BK14" s="31"/>
-    </row>
-    <row r="15" spans="1:63" ht="14" customHeight="1">
+      <c r="BI14" s="26"/>
+      <c r="BJ14" s="26"/>
+      <c r="BK14" s="29"/>
+      <c r="BL14" s="29"/>
+      <c r="BM14" s="31"/>
+    </row>
+    <row r="15" spans="1:65" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -8644,43 +8840,45 @@
       <c r="AF15" s="30"/>
       <c r="AG15" s="29"/>
       <c r="AH15" s="29"/>
-      <c r="AI15" s="25" t="s">
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="31"/>
+      <c r="AL15" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="AJ15" s="26"/>
-      <c r="AK15" s="27"/>
-      <c r="AL15" s="29"/>
-      <c r="AM15" s="29"/>
-      <c r="AN15" s="29"/>
-      <c r="AO15" s="30" t="s">
-        <v>123</v>
-      </c>
+      <c r="AM15" s="26"/>
+      <c r="AN15" s="27"/>
+      <c r="AO15" s="29"/>
       <c r="AP15" s="29"/>
       <c r="AQ15" s="29"/>
-      <c r="AR15" s="30"/>
+      <c r="AR15" s="30" t="s">
+        <v>123</v>
+      </c>
       <c r="AS15" s="29"/>
       <c r="AT15" s="29"/>
-      <c r="AU15" s="25"/>
-      <c r="AV15" s="26"/>
-      <c r="AW15" s="31"/>
-      <c r="AX15" s="29"/>
-      <c r="AY15" s="29"/>
-      <c r="AZ15" s="29"/>
-      <c r="BA15" s="30"/>
+      <c r="AU15" s="30"/>
+      <c r="AV15" s="29"/>
+      <c r="AW15" s="29"/>
+      <c r="AX15" s="25"/>
+      <c r="AY15" s="26"/>
+      <c r="AZ15" s="31"/>
+      <c r="BA15" s="29"/>
       <c r="BB15" s="29"/>
-      <c r="BC15" s="31"/>
-      <c r="BD15" s="26" t="s">
+      <c r="BC15" s="29"/>
+      <c r="BD15" s="30"/>
+      <c r="BE15" s="29"/>
+      <c r="BF15" s="31"/>
+      <c r="BG15" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="BE15" s="26"/>
-      <c r="BF15" s="26"/>
-      <c r="BG15" s="26"/>
-      <c r="BH15" s="29"/>
-      <c r="BI15" s="29"/>
-      <c r="BJ15" s="29"/>
-      <c r="BK15" s="31"/>
-    </row>
-    <row r="16" spans="1:63" ht="14" customHeight="1">
+      <c r="BH15" s="26"/>
+      <c r="BI15" s="26"/>
+      <c r="BJ15" s="26"/>
+      <c r="BK15" s="29"/>
+      <c r="BL15" s="29"/>
+      <c r="BM15" s="31"/>
+    </row>
+    <row r="16" spans="1:65" ht="14" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -8727,43 +8925,45 @@
       <c r="AF16" s="30"/>
       <c r="AG16" s="29"/>
       <c r="AH16" s="29"/>
-      <c r="AI16" s="25" t="s">
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="31"/>
+      <c r="AL16" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="AJ16" s="26"/>
-      <c r="AK16" s="27"/>
-      <c r="AL16" s="29"/>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="30" t="s">
-        <v>2</v>
-      </c>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="27"/>
+      <c r="AO16" s="29"/>
       <c r="AP16" s="29"/>
       <c r="AQ16" s="29"/>
-      <c r="AR16" s="30"/>
+      <c r="AR16" s="30" t="s">
+        <v>2</v>
+      </c>
       <c r="AS16" s="29"/>
       <c r="AT16" s="29"/>
-      <c r="AU16" s="25"/>
-      <c r="AV16" s="26"/>
-      <c r="AW16" s="31"/>
-      <c r="AX16" s="29"/>
-      <c r="AY16" s="29"/>
-      <c r="AZ16" s="29"/>
-      <c r="BA16" s="30"/>
+      <c r="AU16" s="30"/>
+      <c r="AV16" s="29"/>
+      <c r="AW16" s="29"/>
+      <c r="AX16" s="25"/>
+      <c r="AY16" s="26"/>
+      <c r="AZ16" s="31"/>
+      <c r="BA16" s="29"/>
       <c r="BB16" s="29"/>
-      <c r="BC16" s="31"/>
-      <c r="BD16" s="26" t="s">
+      <c r="BC16" s="29"/>
+      <c r="BD16" s="30"/>
+      <c r="BE16" s="29"/>
+      <c r="BF16" s="31"/>
+      <c r="BG16" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="BE16" s="26"/>
-      <c r="BF16" s="26"/>
-      <c r="BG16" s="26"/>
-      <c r="BH16" s="29"/>
-      <c r="BI16" s="29"/>
-      <c r="BJ16" s="29"/>
-      <c r="BK16" s="31"/>
-    </row>
-    <row r="17" spans="1:63" ht="14" customHeight="1">
+      <c r="BH16" s="26"/>
+      <c r="BI16" s="26"/>
+      <c r="BJ16" s="26"/>
+      <c r="BK16" s="29"/>
+      <c r="BL16" s="29"/>
+      <c r="BM16" s="31"/>
+    </row>
+    <row r="17" spans="1:65" ht="14" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -8809,34 +9009,36 @@
       <c r="AI17" s="30"/>
       <c r="AJ17" s="29"/>
       <c r="AK17" s="31"/>
-      <c r="AL17" s="32"/>
-      <c r="AM17" s="32"/>
-      <c r="AN17" s="32"/>
-      <c r="AO17" s="33"/>
-      <c r="AP17" s="29"/>
-      <c r="AQ17" s="29"/>
-      <c r="AR17" s="32"/>
+      <c r="AL17" s="30"/>
+      <c r="AM17" s="29"/>
+      <c r="AN17" s="31"/>
+      <c r="AO17" s="32"/>
+      <c r="AP17" s="32"/>
+      <c r="AQ17" s="32"/>
+      <c r="AR17" s="33"/>
       <c r="AS17" s="29"/>
       <c r="AT17" s="29"/>
-      <c r="AU17" s="25"/>
-      <c r="AV17" s="26"/>
-      <c r="AW17" s="31"/>
-      <c r="AX17" s="29"/>
-      <c r="AY17" s="29"/>
-      <c r="AZ17" s="29"/>
-      <c r="BA17" s="30"/>
+      <c r="AU17" s="32"/>
+      <c r="AV17" s="29"/>
+      <c r="AW17" s="29"/>
+      <c r="AX17" s="25"/>
+      <c r="AY17" s="26"/>
+      <c r="AZ17" s="31"/>
+      <c r="BA17" s="29"/>
       <c r="BB17" s="29"/>
-      <c r="BC17" s="31"/>
-      <c r="BD17" s="29"/>
+      <c r="BC17" s="29"/>
+      <c r="BD17" s="30"/>
       <c r="BE17" s="29"/>
-      <c r="BF17" s="29"/>
+      <c r="BF17" s="31"/>
       <c r="BG17" s="29"/>
       <c r="BH17" s="29"/>
       <c r="BI17" s="29"/>
       <c r="BJ17" s="29"/>
-      <c r="BK17" s="31"/>
-    </row>
-    <row r="18" spans="1:63" ht="14" customHeight="1">
+      <c r="BK17" s="29"/>
+      <c r="BL17" s="29"/>
+      <c r="BM17" s="31"/>
+    </row>
+    <row r="18" spans="1:65" ht="14" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -8883,43 +9085,45 @@
       <c r="AF18" s="30"/>
       <c r="AG18" s="29"/>
       <c r="AH18" s="29"/>
-      <c r="AI18" s="25" t="s">
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="31"/>
+      <c r="AL18" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="AJ18" s="26"/>
-      <c r="AK18" s="27"/>
-      <c r="AL18" s="26"/>
       <c r="AM18" s="26"/>
-      <c r="AN18" s="26"/>
-      <c r="AO18" s="25" t="s">
-        <v>130</v>
-      </c>
+      <c r="AN18" s="27"/>
+      <c r="AO18" s="26"/>
       <c r="AP18" s="26"/>
       <c r="AQ18" s="26"/>
-      <c r="AR18" s="25"/>
+      <c r="AR18" s="25" t="s">
+        <v>130</v>
+      </c>
       <c r="AS18" s="26"/>
       <c r="AT18" s="26"/>
-      <c r="AU18" s="25" t="s">
+      <c r="AU18" s="25"/>
+      <c r="AV18" s="26"/>
+      <c r="AW18" s="26"/>
+      <c r="AX18" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="AV18" s="26"/>
-      <c r="AW18" s="31"/>
-      <c r="AX18" s="29"/>
-      <c r="AY18" s="29"/>
-      <c r="AZ18" s="29"/>
-      <c r="BA18" s="30"/>
+      <c r="AY18" s="26"/>
+      <c r="AZ18" s="31"/>
+      <c r="BA18" s="29"/>
       <c r="BB18" s="29"/>
-      <c r="BC18" s="31"/>
-      <c r="BD18" s="29"/>
+      <c r="BC18" s="29"/>
+      <c r="BD18" s="30"/>
       <c r="BE18" s="29"/>
-      <c r="BF18" s="29"/>
+      <c r="BF18" s="31"/>
       <c r="BG18" s="29"/>
       <c r="BH18" s="29"/>
       <c r="BI18" s="29"/>
       <c r="BJ18" s="29"/>
-      <c r="BK18" s="31"/>
-    </row>
-    <row r="19" spans="1:63" ht="14" customHeight="1">
+      <c r="BK18" s="29"/>
+      <c r="BL18" s="29"/>
+      <c r="BM18" s="31"/>
+    </row>
+    <row r="19" spans="1:65" ht="14" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -8965,34 +9169,36 @@
       <c r="AI19" s="30"/>
       <c r="AJ19" s="29"/>
       <c r="AK19" s="31"/>
-      <c r="AL19" s="29"/>
-      <c r="AM19" s="29"/>
-      <c r="AN19" s="29"/>
-      <c r="AO19" s="30"/>
-      <c r="AP19" s="29"/>
-      <c r="AQ19" s="29"/>
-      <c r="AR19" s="30"/>
-      <c r="AS19" s="29"/>
-      <c r="AT19" s="29"/>
+      <c r="AL19" s="25"/>
+      <c r="AM19" s="26"/>
+      <c r="AN19" s="27"/>
+      <c r="AO19" s="26"/>
+      <c r="AP19" s="26"/>
+      <c r="AQ19" s="26"/>
+      <c r="AR19" s="25"/>
+      <c r="AS19" s="26"/>
+      <c r="AT19" s="26"/>
       <c r="AU19" s="25"/>
-      <c r="AV19" s="26"/>
-      <c r="AW19" s="31"/>
-      <c r="AX19" s="29"/>
-      <c r="AY19" s="29"/>
-      <c r="AZ19" s="29"/>
-      <c r="BA19" s="30"/>
+      <c r="AV19" s="29"/>
+      <c r="AW19" s="29"/>
+      <c r="AX19" s="25"/>
+      <c r="AY19" s="26"/>
+      <c r="AZ19" s="31"/>
+      <c r="BA19" s="29"/>
       <c r="BB19" s="29"/>
-      <c r="BC19" s="31"/>
-      <c r="BD19" s="29"/>
+      <c r="BC19" s="29"/>
+      <c r="BD19" s="30"/>
       <c r="BE19" s="29"/>
-      <c r="BF19" s="29"/>
+      <c r="BF19" s="31"/>
       <c r="BG19" s="29"/>
       <c r="BH19" s="29"/>
       <c r="BI19" s="29"/>
       <c r="BJ19" s="29"/>
-      <c r="BK19" s="31"/>
-    </row>
-    <row r="20" spans="1:63" ht="14" customHeight="1">
+      <c r="BK19" s="29"/>
+      <c r="BL19" s="29"/>
+      <c r="BM19" s="31"/>
+    </row>
+    <row r="20" spans="1:65" ht="14" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>132</v>
       </c>
@@ -9038,10 +9244,10 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5"/>
-      <c r="AL20" s="4"/>
+      <c r="AL20" s="3"/>
       <c r="AM20" s="4"/>
-      <c r="AN20" s="4"/>
-      <c r="AO20" s="3"/>
+      <c r="AN20" s="5"/>
+      <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="3"/>
@@ -9049,23 +9255,25 @@
       <c r="AT20" s="4"/>
       <c r="AU20" s="3"/>
       <c r="AV20" s="4"/>
-      <c r="AW20" s="5"/>
-      <c r="AX20" s="4"/>
+      <c r="AW20" s="4"/>
+      <c r="AX20" s="3"/>
       <c r="AY20" s="4"/>
-      <c r="AZ20" s="4"/>
-      <c r="BA20" s="3"/>
+      <c r="AZ20" s="5"/>
+      <c r="BA20" s="4"/>
       <c r="BB20" s="4"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="4"/>
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="3"/>
       <c r="BE20" s="4"/>
-      <c r="BF20" s="4"/>
+      <c r="BF20" s="5"/>
       <c r="BG20" s="4"/>
       <c r="BH20" s="4"/>
       <c r="BI20" s="4"/>
       <c r="BJ20" s="4"/>
-      <c r="BK20" s="5"/>
-    </row>
-    <row r="21" spans="1:63" ht="14" customHeight="1">
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+      <c r="BM20" s="5"/>
+    </row>
+    <row r="21" spans="1:65" ht="14" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>134</v>
       </c>
@@ -9111,10 +9319,10 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5"/>
-      <c r="AL21" s="4"/>
+      <c r="AL21" s="3"/>
       <c r="AM21" s="4"/>
-      <c r="AN21" s="4"/>
-      <c r="AO21" s="3"/>
+      <c r="AN21" s="5"/>
+      <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="3"/>
@@ -9122,27 +9330,29 @@
       <c r="AT21" s="4"/>
       <c r="AU21" s="3"/>
       <c r="AV21" s="4"/>
-      <c r="AW21" s="5"/>
-      <c r="AX21" s="4" t="s">
+      <c r="AW21" s="4"/>
+      <c r="AX21" s="3"/>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="5"/>
+      <c r="BA21" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AY21" s="4"/>
-      <c r="AZ21" s="4"/>
-      <c r="BA21" s="3" t="s">
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BB21" s="4"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
-      <c r="BF21" s="4"/>
+      <c r="BF21" s="5"/>
       <c r="BG21" s="4"/>
       <c r="BH21" s="4"/>
       <c r="BI21" s="4"/>
       <c r="BJ21" s="4"/>
-      <c r="BK21" s="5"/>
-    </row>
-    <row r="22" spans="1:63" ht="14" customHeight="1">
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+      <c r="BM21" s="5"/>
+    </row>
+    <row r="22" spans="1:65" ht="14" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>137</v>
       </c>
@@ -9188,10 +9398,10 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5"/>
-      <c r="AL22" s="4"/>
+      <c r="AL22" s="3"/>
       <c r="AM22" s="4"/>
-      <c r="AN22" s="4"/>
-      <c r="AO22" s="3"/>
+      <c r="AN22" s="5"/>
+      <c r="AO22" s="4"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="3"/>
@@ -9199,27 +9409,29 @@
       <c r="AT22" s="4"/>
       <c r="AU22" s="3"/>
       <c r="AV22" s="4"/>
-      <c r="AW22" s="5"/>
-      <c r="AX22" s="4" t="s">
+      <c r="AW22" s="4"/>
+      <c r="AX22" s="3"/>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="5"/>
+      <c r="BA22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AY22" s="4"/>
-      <c r="AZ22" s="4"/>
-      <c r="BA22" s="3" t="s">
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BB22" s="4"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
-      <c r="BF22" s="4"/>
+      <c r="BF22" s="5"/>
       <c r="BG22" s="4"/>
       <c r="BH22" s="4"/>
       <c r="BI22" s="4"/>
       <c r="BJ22" s="4"/>
-      <c r="BK22" s="5"/>
-    </row>
-    <row r="23" spans="1:63" ht="14" customHeight="1">
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="5"/>
+    </row>
+    <row r="23" spans="1:65" ht="14" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>139</v>
       </c>
@@ -9265,10 +9477,10 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5"/>
-      <c r="AL23" s="4"/>
+      <c r="AL23" s="3"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="4"/>
-      <c r="AO23" s="3"/>
+      <c r="AN23" s="5"/>
+      <c r="AO23" s="4"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="3"/>
@@ -9276,27 +9488,29 @@
       <c r="AT23" s="4"/>
       <c r="AU23" s="3"/>
       <c r="AV23" s="4"/>
-      <c r="AW23" s="5"/>
-      <c r="AX23" s="4" t="s">
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="3"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="5"/>
+      <c r="BA23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AY23" s="4"/>
-      <c r="AZ23" s="4"/>
-      <c r="BA23" s="3" t="s">
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BB23" s="4"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
-      <c r="BF23" s="4"/>
+      <c r="BF23" s="5"/>
       <c r="BG23" s="4"/>
       <c r="BH23" s="4"/>
       <c r="BI23" s="4"/>
       <c r="BJ23" s="4"/>
-      <c r="BK23" s="5"/>
-    </row>
-    <row r="24" spans="1:63" ht="14" customHeight="1">
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+      <c r="BM23" s="5"/>
+    </row>
+    <row r="24" spans="1:65" ht="14" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>141</v>
       </c>
@@ -9342,38 +9556,40 @@
       <c r="AI24" s="3"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5"/>
-      <c r="AL24" s="4"/>
+      <c r="AL24" s="3"/>
       <c r="AM24" s="4"/>
-      <c r="AN24" s="4"/>
-      <c r="AO24" s="3"/>
+      <c r="AN24" s="5"/>
+      <c r="AO24" s="4"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="3"/>
       <c r="AS24" s="4"/>
       <c r="AT24" s="4"/>
-      <c r="AU24" s="24"/>
-      <c r="AV24" s="21"/>
-      <c r="AW24" s="5"/>
-      <c r="AX24" s="4" t="s">
+      <c r="AU24" s="3"/>
+      <c r="AV24" s="4"/>
+      <c r="AW24" s="4"/>
+      <c r="AX24" s="24"/>
+      <c r="AY24" s="21"/>
+      <c r="AZ24" s="5"/>
+      <c r="BA24" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AY24" s="4"/>
-      <c r="AZ24" s="4"/>
-      <c r="BA24" s="3" t="s">
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BB24" s="4"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
-      <c r="BF24" s="4"/>
+      <c r="BF24" s="5"/>
       <c r="BG24" s="4"/>
       <c r="BH24" s="4"/>
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
-      <c r="BK24" s="5"/>
-    </row>
-    <row r="25" spans="1:63" ht="14" customHeight="1">
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+      <c r="BM24" s="5"/>
+    </row>
+    <row r="25" spans="1:65" ht="14" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -9419,10 +9635,10 @@
       <c r="AI25" s="3"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5"/>
-      <c r="AL25" s="4"/>
+      <c r="AL25" s="3"/>
       <c r="AM25" s="4"/>
-      <c r="AN25" s="4"/>
-      <c r="AO25" s="3"/>
+      <c r="AN25" s="5"/>
+      <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="3"/>
@@ -9430,27 +9646,29 @@
       <c r="AT25" s="4"/>
       <c r="AU25" s="3"/>
       <c r="AV25" s="4"/>
-      <c r="AW25" s="5"/>
-      <c r="AX25" s="4" t="s">
+      <c r="AW25" s="4"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="5"/>
+      <c r="BA25" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AY25" s="4"/>
-      <c r="AZ25" s="4"/>
-      <c r="BA25" s="3" t="s">
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="BB25" s="4"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
-      <c r="BF25" s="4"/>
+      <c r="BF25" s="5"/>
       <c r="BG25" s="4"/>
       <c r="BH25" s="4"/>
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
-      <c r="BK25" s="5"/>
-    </row>
-    <row r="26" spans="1:63" ht="14" customHeight="1">
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+      <c r="BM25" s="5"/>
+    </row>
+    <row r="26" spans="1:65" ht="14" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
@@ -9488,10 +9706,10 @@
       <c r="AI26" s="3"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5"/>
-      <c r="AL26" s="4"/>
+      <c r="AL26" s="3"/>
       <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="3"/>
+      <c r="AN26" s="5"/>
+      <c r="AO26" s="4"/>
       <c r="AP26" s="4"/>
       <c r="AQ26" s="4"/>
       <c r="AR26" s="3"/>
@@ -9499,23 +9717,25 @@
       <c r="AT26" s="4"/>
       <c r="AU26" s="3"/>
       <c r="AV26" s="4"/>
-      <c r="AW26" s="5"/>
-      <c r="AX26" s="4"/>
+      <c r="AW26" s="4"/>
+      <c r="AX26" s="3"/>
       <c r="AY26" s="4"/>
-      <c r="AZ26" s="4"/>
-      <c r="BA26" s="3"/>
+      <c r="AZ26" s="5"/>
+      <c r="BA26" s="4"/>
       <c r="BB26" s="4"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="4"/>
+      <c r="BC26" s="4"/>
+      <c r="BD26" s="3"/>
       <c r="BE26" s="4"/>
-      <c r="BF26" s="4"/>
+      <c r="BF26" s="5"/>
       <c r="BG26" s="4"/>
       <c r="BH26" s="4"/>
       <c r="BI26" s="4"/>
       <c r="BJ26" s="4"/>
-      <c r="BK26" s="5"/>
-    </row>
-    <row r="27" spans="1:63" ht="14" customHeight="1">
+      <c r="BK26" s="4"/>
+      <c r="BL26" s="4"/>
+      <c r="BM26" s="5"/>
+    </row>
+    <row r="27" spans="1:65" ht="14" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
       <c r="C27" s="3"/>
@@ -9553,10 +9773,10 @@
       <c r="AI27" s="3"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5"/>
-      <c r="AL27" s="4"/>
+      <c r="AL27" s="3"/>
       <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="3"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="4"/>
       <c r="AP27" s="4"/>
       <c r="AQ27" s="4"/>
       <c r="AR27" s="3"/>
@@ -9564,23 +9784,25 @@
       <c r="AT27" s="4"/>
       <c r="AU27" s="3"/>
       <c r="AV27" s="4"/>
-      <c r="AW27" s="5"/>
-      <c r="AX27" s="4"/>
+      <c r="AW27" s="4"/>
+      <c r="AX27" s="3"/>
       <c r="AY27" s="4"/>
-      <c r="AZ27" s="4"/>
-      <c r="BA27" s="3"/>
+      <c r="AZ27" s="5"/>
+      <c r="BA27" s="4"/>
       <c r="BB27" s="4"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="4"/>
+      <c r="BC27" s="4"/>
+      <c r="BD27" s="3"/>
       <c r="BE27" s="4"/>
-      <c r="BF27" s="4"/>
+      <c r="BF27" s="5"/>
       <c r="BG27" s="4"/>
       <c r="BH27" s="4"/>
       <c r="BI27" s="4"/>
       <c r="BJ27" s="4"/>
-      <c r="BK27" s="5"/>
-    </row>
-    <row r="28" spans="1:63" ht="14" customHeight="1">
+      <c r="BK27" s="4"/>
+      <c r="BL27" s="4"/>
+      <c r="BM27" s="5"/>
+    </row>
+    <row r="28" spans="1:65" ht="14" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="C28" s="3"/>
@@ -9618,10 +9840,10 @@
       <c r="AI28" s="3"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5"/>
-      <c r="AL28" s="4"/>
+      <c r="AL28" s="3"/>
       <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="3"/>
+      <c r="AN28" s="5"/>
+      <c r="AO28" s="4"/>
       <c r="AP28" s="4"/>
       <c r="AQ28" s="4"/>
       <c r="AR28" s="3"/>
@@ -9629,23 +9851,25 @@
       <c r="AT28" s="4"/>
       <c r="AU28" s="3"/>
       <c r="AV28" s="4"/>
-      <c r="AW28" s="5"/>
-      <c r="AX28" s="4"/>
+      <c r="AW28" s="4"/>
+      <c r="AX28" s="3"/>
       <c r="AY28" s="4"/>
-      <c r="AZ28" s="4"/>
-      <c r="BA28" s="3"/>
+      <c r="AZ28" s="5"/>
+      <c r="BA28" s="4"/>
       <c r="BB28" s="4"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="4"/>
+      <c r="BC28" s="4"/>
+      <c r="BD28" s="3"/>
       <c r="BE28" s="4"/>
-      <c r="BF28" s="4"/>
+      <c r="BF28" s="5"/>
       <c r="BG28" s="4"/>
       <c r="BH28" s="4"/>
       <c r="BI28" s="4"/>
       <c r="BJ28" s="4"/>
-      <c r="BK28" s="5"/>
-    </row>
-    <row r="29" spans="1:63" ht="14" customHeight="1">
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+      <c r="BM28" s="5"/>
+    </row>
+    <row r="29" spans="1:65" ht="14" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
@@ -9683,10 +9907,10 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5"/>
-      <c r="AL29" s="4"/>
+      <c r="AL29" s="3"/>
       <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="3"/>
+      <c r="AN29" s="5"/>
+      <c r="AO29" s="4"/>
       <c r="AP29" s="4"/>
       <c r="AQ29" s="4"/>
       <c r="AR29" s="3"/>
@@ -9694,23 +9918,25 @@
       <c r="AT29" s="4"/>
       <c r="AU29" s="3"/>
       <c r="AV29" s="4"/>
-      <c r="AW29" s="5"/>
-      <c r="AX29" s="4"/>
+      <c r="AW29" s="4"/>
+      <c r="AX29" s="3"/>
       <c r="AY29" s="4"/>
-      <c r="AZ29" s="4"/>
-      <c r="BA29" s="3"/>
+      <c r="AZ29" s="5"/>
+      <c r="BA29" s="4"/>
       <c r="BB29" s="4"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="4"/>
+      <c r="BC29" s="4"/>
+      <c r="BD29" s="3"/>
       <c r="BE29" s="4"/>
-      <c r="BF29" s="4"/>
+      <c r="BF29" s="5"/>
       <c r="BG29" s="4"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="4"/>
       <c r="BJ29" s="4"/>
-      <c r="BK29" s="5"/>
-    </row>
-    <row r="30" spans="1:63" ht="14" customHeight="1">
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+      <c r="BM29" s="5"/>
+    </row>
+    <row r="30" spans="1:65" ht="14" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -9748,10 +9974,10 @@
       <c r="AI30" s="3"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5"/>
-      <c r="AL30" s="4"/>
+      <c r="AL30" s="3"/>
       <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="3"/>
+      <c r="AN30" s="5"/>
+      <c r="AO30" s="4"/>
       <c r="AP30" s="4"/>
       <c r="AQ30" s="4"/>
       <c r="AR30" s="3"/>
@@ -9759,23 +9985,25 @@
       <c r="AT30" s="4"/>
       <c r="AU30" s="3"/>
       <c r="AV30" s="4"/>
-      <c r="AW30" s="5"/>
-      <c r="AX30" s="4"/>
+      <c r="AW30" s="4"/>
+      <c r="AX30" s="3"/>
       <c r="AY30" s="4"/>
-      <c r="AZ30" s="4"/>
-      <c r="BA30" s="3"/>
+      <c r="AZ30" s="5"/>
+      <c r="BA30" s="4"/>
       <c r="BB30" s="4"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="4"/>
+      <c r="BC30" s="4"/>
+      <c r="BD30" s="3"/>
       <c r="BE30" s="4"/>
-      <c r="BF30" s="4"/>
+      <c r="BF30" s="5"/>
       <c r="BG30" s="4"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="4"/>
       <c r="BJ30" s="4"/>
-      <c r="BK30" s="5"/>
-    </row>
-    <row r="31" spans="1:63" ht="14" customHeight="1">
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+      <c r="BM30" s="5"/>
+    </row>
+    <row r="31" spans="1:65" ht="14" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -9813,10 +10041,10 @@
       <c r="AI31" s="3"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5"/>
-      <c r="AL31" s="4"/>
+      <c r="AL31" s="3"/>
       <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="3"/>
+      <c r="AN31" s="5"/>
+      <c r="AO31" s="4"/>
       <c r="AP31" s="4"/>
       <c r="AQ31" s="4"/>
       <c r="AR31" s="3"/>
@@ -9824,23 +10052,25 @@
       <c r="AT31" s="4"/>
       <c r="AU31" s="3"/>
       <c r="AV31" s="4"/>
-      <c r="AW31" s="5"/>
-      <c r="AX31" s="4"/>
+      <c r="AW31" s="4"/>
+      <c r="AX31" s="3"/>
       <c r="AY31" s="4"/>
-      <c r="AZ31" s="4"/>
-      <c r="BA31" s="3"/>
+      <c r="AZ31" s="5"/>
+      <c r="BA31" s="4"/>
       <c r="BB31" s="4"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="4"/>
+      <c r="BC31" s="4"/>
+      <c r="BD31" s="3"/>
       <c r="BE31" s="4"/>
-      <c r="BF31" s="4"/>
+      <c r="BF31" s="5"/>
       <c r="BG31" s="4"/>
       <c r="BH31" s="4"/>
       <c r="BI31" s="4"/>
       <c r="BJ31" s="4"/>
-      <c r="BK31" s="5"/>
-    </row>
-    <row r="32" spans="1:63" ht="14" customHeight="1">
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+      <c r="BM31" s="5"/>
+    </row>
+    <row r="32" spans="1:65" ht="14" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="3"/>
@@ -9878,10 +10108,10 @@
       <c r="AI32" s="3"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="5"/>
-      <c r="AL32" s="4"/>
+      <c r="AL32" s="3"/>
       <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="3"/>
+      <c r="AN32" s="5"/>
+      <c r="AO32" s="4"/>
       <c r="AP32" s="4"/>
       <c r="AQ32" s="4"/>
       <c r="AR32" s="3"/>
@@ -9889,23 +10119,25 @@
       <c r="AT32" s="4"/>
       <c r="AU32" s="3"/>
       <c r="AV32" s="4"/>
-      <c r="AW32" s="5"/>
-      <c r="AX32" s="4"/>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="3"/>
       <c r="AY32" s="4"/>
-      <c r="AZ32" s="4"/>
-      <c r="BA32" s="3"/>
+      <c r="AZ32" s="5"/>
+      <c r="BA32" s="4"/>
       <c r="BB32" s="4"/>
-      <c r="BC32" s="5"/>
-      <c r="BD32" s="4"/>
+      <c r="BC32" s="4"/>
+      <c r="BD32" s="3"/>
       <c r="BE32" s="4"/>
-      <c r="BF32" s="4"/>
+      <c r="BF32" s="5"/>
       <c r="BG32" s="4"/>
       <c r="BH32" s="4"/>
       <c r="BI32" s="4"/>
       <c r="BJ32" s="4"/>
-      <c r="BK32" s="5"/>
-    </row>
-    <row r="33" spans="1:63" ht="14" customHeight="1">
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+      <c r="BM32" s="5"/>
+    </row>
+    <row r="33" spans="1:65" ht="14" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="3"/>
@@ -9943,10 +10175,10 @@
       <c r="AI33" s="3"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="5"/>
-      <c r="AL33" s="4"/>
+      <c r="AL33" s="3"/>
       <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="3"/>
+      <c r="AN33" s="5"/>
+      <c r="AO33" s="4"/>
       <c r="AP33" s="4"/>
       <c r="AQ33" s="4"/>
       <c r="AR33" s="3"/>
@@ -9954,23 +10186,25 @@
       <c r="AT33" s="4"/>
       <c r="AU33" s="3"/>
       <c r="AV33" s="4"/>
-      <c r="AW33" s="5"/>
-      <c r="AX33" s="4"/>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="3"/>
       <c r="AY33" s="4"/>
-      <c r="AZ33" s="4"/>
-      <c r="BA33" s="3"/>
+      <c r="AZ33" s="5"/>
+      <c r="BA33" s="4"/>
       <c r="BB33" s="4"/>
-      <c r="BC33" s="5"/>
-      <c r="BD33" s="4"/>
+      <c r="BC33" s="4"/>
+      <c r="BD33" s="3"/>
       <c r="BE33" s="4"/>
-      <c r="BF33" s="4"/>
+      <c r="BF33" s="5"/>
       <c r="BG33" s="4"/>
       <c r="BH33" s="4"/>
       <c r="BI33" s="4"/>
       <c r="BJ33" s="4"/>
-      <c r="BK33" s="5"/>
-    </row>
-    <row r="34" spans="1:63" ht="14" customHeight="1">
+      <c r="BK33" s="4"/>
+      <c r="BL33" s="4"/>
+      <c r="BM33" s="5"/>
+    </row>
+    <row r="34" spans="1:65" ht="14" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="3"/>
@@ -10008,10 +10242,10 @@
       <c r="AI34" s="3"/>
       <c r="AJ34" s="4"/>
       <c r="AK34" s="5"/>
-      <c r="AL34" s="4"/>
+      <c r="AL34" s="3"/>
       <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="3"/>
+      <c r="AN34" s="5"/>
+      <c r="AO34" s="4"/>
       <c r="AP34" s="4"/>
       <c r="AQ34" s="4"/>
       <c r="AR34" s="3"/>
@@ -10019,23 +10253,25 @@
       <c r="AT34" s="4"/>
       <c r="AU34" s="3"/>
       <c r="AV34" s="4"/>
-      <c r="AW34" s="5"/>
-      <c r="AX34" s="4"/>
+      <c r="AW34" s="4"/>
+      <c r="AX34" s="3"/>
       <c r="AY34" s="4"/>
-      <c r="AZ34" s="4"/>
-      <c r="BA34" s="3"/>
+      <c r="AZ34" s="5"/>
+      <c r="BA34" s="4"/>
       <c r="BB34" s="4"/>
-      <c r="BC34" s="5"/>
-      <c r="BD34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="3"/>
       <c r="BE34" s="4"/>
-      <c r="BF34" s="4"/>
+      <c r="BF34" s="5"/>
       <c r="BG34" s="4"/>
       <c r="BH34" s="4"/>
       <c r="BI34" s="4"/>
       <c r="BJ34" s="4"/>
-      <c r="BK34" s="5"/>
-    </row>
-    <row r="35" spans="1:63" ht="14" customHeight="1">
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+      <c r="BM34" s="5"/>
+    </row>
+    <row r="35" spans="1:65" ht="14" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="3"/>
@@ -10073,10 +10309,10 @@
       <c r="AI35" s="3"/>
       <c r="AJ35" s="4"/>
       <c r="AK35" s="5"/>
-      <c r="AL35" s="4"/>
+      <c r="AL35" s="3"/>
       <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="3"/>
+      <c r="AN35" s="5"/>
+      <c r="AO35" s="4"/>
       <c r="AP35" s="4"/>
       <c r="AQ35" s="4"/>
       <c r="AR35" s="3"/>
@@ -10084,23 +10320,25 @@
       <c r="AT35" s="4"/>
       <c r="AU35" s="3"/>
       <c r="AV35" s="4"/>
-      <c r="AW35" s="5"/>
-      <c r="AX35" s="4"/>
+      <c r="AW35" s="4"/>
+      <c r="AX35" s="3"/>
       <c r="AY35" s="4"/>
-      <c r="AZ35" s="4"/>
-      <c r="BA35" s="3"/>
+      <c r="AZ35" s="5"/>
+      <c r="BA35" s="4"/>
       <c r="BB35" s="4"/>
-      <c r="BC35" s="5"/>
-      <c r="BD35" s="4"/>
+      <c r="BC35" s="4"/>
+      <c r="BD35" s="3"/>
       <c r="BE35" s="4"/>
-      <c r="BF35" s="4"/>
+      <c r="BF35" s="5"/>
       <c r="BG35" s="4"/>
       <c r="BH35" s="4"/>
       <c r="BI35" s="4"/>
       <c r="BJ35" s="4"/>
-      <c r="BK35" s="5"/>
-    </row>
-    <row r="36" spans="1:63" ht="14" customHeight="1">
+      <c r="BK35" s="4"/>
+      <c r="BL35" s="4"/>
+      <c r="BM35" s="5"/>
+    </row>
+    <row r="36" spans="1:65" ht="14" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="3"/>
@@ -10138,10 +10376,10 @@
       <c r="AI36" s="3"/>
       <c r="AJ36" s="4"/>
       <c r="AK36" s="5"/>
-      <c r="AL36" s="4"/>
+      <c r="AL36" s="3"/>
       <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="3"/>
+      <c r="AN36" s="5"/>
+      <c r="AO36" s="4"/>
       <c r="AP36" s="4"/>
       <c r="AQ36" s="4"/>
       <c r="AR36" s="3"/>
@@ -10149,23 +10387,25 @@
       <c r="AT36" s="4"/>
       <c r="AU36" s="3"/>
       <c r="AV36" s="4"/>
-      <c r="AW36" s="5"/>
-      <c r="AX36" s="4"/>
+      <c r="AW36" s="4"/>
+      <c r="AX36" s="3"/>
       <c r="AY36" s="4"/>
-      <c r="AZ36" s="4"/>
-      <c r="BA36" s="3"/>
+      <c r="AZ36" s="5"/>
+      <c r="BA36" s="4"/>
       <c r="BB36" s="4"/>
-      <c r="BC36" s="5"/>
-      <c r="BD36" s="4"/>
+      <c r="BC36" s="4"/>
+      <c r="BD36" s="3"/>
       <c r="BE36" s="4"/>
-      <c r="BF36" s="4"/>
+      <c r="BF36" s="5"/>
       <c r="BG36" s="4"/>
       <c r="BH36" s="4"/>
       <c r="BI36" s="4"/>
       <c r="BJ36" s="4"/>
-      <c r="BK36" s="5"/>
-    </row>
-    <row r="37" spans="1:63" ht="14" customHeight="1">
+      <c r="BK36" s="4"/>
+      <c r="BL36" s="4"/>
+      <c r="BM36" s="5"/>
+    </row>
+    <row r="37" spans="1:65" ht="14" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3"/>
@@ -10203,10 +10443,10 @@
       <c r="AI37" s="3"/>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="5"/>
-      <c r="AL37" s="4"/>
+      <c r="AL37" s="3"/>
       <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="3"/>
+      <c r="AN37" s="5"/>
+      <c r="AO37" s="4"/>
       <c r="AP37" s="4"/>
       <c r="AQ37" s="4"/>
       <c r="AR37" s="3"/>
@@ -10214,23 +10454,25 @@
       <c r="AT37" s="4"/>
       <c r="AU37" s="3"/>
       <c r="AV37" s="4"/>
-      <c r="AW37" s="5"/>
-      <c r="AX37" s="4"/>
+      <c r="AW37" s="4"/>
+      <c r="AX37" s="3"/>
       <c r="AY37" s="4"/>
-      <c r="AZ37" s="4"/>
-      <c r="BA37" s="3"/>
+      <c r="AZ37" s="5"/>
+      <c r="BA37" s="4"/>
       <c r="BB37" s="4"/>
-      <c r="BC37" s="5"/>
-      <c r="BD37" s="4"/>
+      <c r="BC37" s="4"/>
+      <c r="BD37" s="3"/>
       <c r="BE37" s="4"/>
-      <c r="BF37" s="4"/>
+      <c r="BF37" s="5"/>
       <c r="BG37" s="4"/>
       <c r="BH37" s="4"/>
       <c r="BI37" s="4"/>
       <c r="BJ37" s="4"/>
-      <c r="BK37" s="5"/>
-    </row>
-    <row r="38" spans="1:63" ht="14" customHeight="1">
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+      <c r="BM37" s="5"/>
+    </row>
+    <row r="38" spans="1:65" ht="14" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3"/>
@@ -10268,10 +10510,10 @@
       <c r="AI38" s="3"/>
       <c r="AJ38" s="4"/>
       <c r="AK38" s="5"/>
-      <c r="AL38" s="4"/>
+      <c r="AL38" s="3"/>
       <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="3"/>
+      <c r="AN38" s="5"/>
+      <c r="AO38" s="4"/>
       <c r="AP38" s="4"/>
       <c r="AQ38" s="4"/>
       <c r="AR38" s="3"/>
@@ -10279,23 +10521,25 @@
       <c r="AT38" s="4"/>
       <c r="AU38" s="3"/>
       <c r="AV38" s="4"/>
-      <c r="AW38" s="5"/>
-      <c r="AX38" s="4"/>
+      <c r="AW38" s="4"/>
+      <c r="AX38" s="3"/>
       <c r="AY38" s="4"/>
-      <c r="AZ38" s="4"/>
-      <c r="BA38" s="3"/>
+      <c r="AZ38" s="5"/>
+      <c r="BA38" s="4"/>
       <c r="BB38" s="4"/>
-      <c r="BC38" s="5"/>
-      <c r="BD38" s="4"/>
+      <c r="BC38" s="4"/>
+      <c r="BD38" s="3"/>
       <c r="BE38" s="4"/>
-      <c r="BF38" s="4"/>
+      <c r="BF38" s="5"/>
       <c r="BG38" s="4"/>
       <c r="BH38" s="4"/>
       <c r="BI38" s="4"/>
       <c r="BJ38" s="4"/>
-      <c r="BK38" s="5"/>
-    </row>
-    <row r="39" spans="1:63" ht="14" customHeight="1">
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+      <c r="BM38" s="5"/>
+    </row>
+    <row r="39" spans="1:65" ht="14" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3"/>
@@ -10333,10 +10577,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="5"/>
-      <c r="AL39" s="4"/>
+      <c r="AL39" s="3"/>
       <c r="AM39" s="4"/>
-      <c r="AN39" s="4"/>
-      <c r="AO39" s="3"/>
+      <c r="AN39" s="5"/>
+      <c r="AO39" s="4"/>
       <c r="AP39" s="4"/>
       <c r="AQ39" s="4"/>
       <c r="AR39" s="3"/>
@@ -10344,23 +10588,25 @@
       <c r="AT39" s="4"/>
       <c r="AU39" s="3"/>
       <c r="AV39" s="4"/>
-      <c r="AW39" s="5"/>
-      <c r="AX39" s="4"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="3"/>
       <c r="AY39" s="4"/>
-      <c r="AZ39" s="4"/>
-      <c r="BA39" s="3"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="4"/>
       <c r="BB39" s="4"/>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="3"/>
       <c r="BE39" s="4"/>
-      <c r="BF39" s="4"/>
+      <c r="BF39" s="5"/>
       <c r="BG39" s="4"/>
       <c r="BH39" s="4"/>
       <c r="BI39" s="4"/>
       <c r="BJ39" s="4"/>
-      <c r="BK39" s="5"/>
-    </row>
-    <row r="40" spans="1:63" ht="14" customHeight="1">
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="5"/>
+    </row>
+    <row r="40" spans="1:65" ht="14" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
@@ -10398,10 +10644,10 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="5"/>
-      <c r="AL40" s="4"/>
+      <c r="AL40" s="3"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="4"/>
-      <c r="AO40" s="3"/>
+      <c r="AN40" s="5"/>
+      <c r="AO40" s="4"/>
       <c r="AP40" s="4"/>
       <c r="AQ40" s="4"/>
       <c r="AR40" s="3"/>
@@ -10409,23 +10655,25 @@
       <c r="AT40" s="4"/>
       <c r="AU40" s="3"/>
       <c r="AV40" s="4"/>
-      <c r="AW40" s="5"/>
-      <c r="AX40" s="4"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="3"/>
       <c r="AY40" s="4"/>
-      <c r="AZ40" s="4"/>
-      <c r="BA40" s="3"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="4"/>
       <c r="BB40" s="4"/>
-      <c r="BC40" s="5"/>
-      <c r="BD40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="3"/>
       <c r="BE40" s="4"/>
-      <c r="BF40" s="4"/>
+      <c r="BF40" s="5"/>
       <c r="BG40" s="4"/>
       <c r="BH40" s="4"/>
       <c r="BI40" s="4"/>
       <c r="BJ40" s="4"/>
-      <c r="BK40" s="5"/>
-    </row>
-    <row r="41" spans="1:63" ht="14" customHeight="1">
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="5"/>
+    </row>
+    <row r="41" spans="1:65" ht="14" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3"/>
@@ -10463,10 +10711,10 @@
       <c r="AI41" s="3"/>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="5"/>
-      <c r="AL41" s="4"/>
+      <c r="AL41" s="3"/>
       <c r="AM41" s="4"/>
-      <c r="AN41" s="4"/>
-      <c r="AO41" s="3"/>
+      <c r="AN41" s="5"/>
+      <c r="AO41" s="4"/>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="4"/>
       <c r="AR41" s="3"/>
@@ -10474,23 +10722,25 @@
       <c r="AT41" s="4"/>
       <c r="AU41" s="3"/>
       <c r="AV41" s="4"/>
-      <c r="AW41" s="5"/>
-      <c r="AX41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="3"/>
       <c r="AY41" s="4"/>
-      <c r="AZ41" s="4"/>
-      <c r="BA41" s="3"/>
+      <c r="AZ41" s="5"/>
+      <c r="BA41" s="4"/>
       <c r="BB41" s="4"/>
-      <c r="BC41" s="5"/>
-      <c r="BD41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="3"/>
       <c r="BE41" s="4"/>
-      <c r="BF41" s="4"/>
+      <c r="BF41" s="5"/>
       <c r="BG41" s="4"/>
       <c r="BH41" s="4"/>
       <c r="BI41" s="4"/>
       <c r="BJ41" s="4"/>
-      <c r="BK41" s="5"/>
-    </row>
-    <row r="42" spans="1:63" ht="14" customHeight="1">
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="5"/>
+    </row>
+    <row r="42" spans="1:65" ht="14" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3"/>
@@ -10528,10 +10778,10 @@
       <c r="AI42" s="3"/>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="5"/>
-      <c r="AL42" s="4"/>
+      <c r="AL42" s="3"/>
       <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
-      <c r="AO42" s="3"/>
+      <c r="AN42" s="5"/>
+      <c r="AO42" s="4"/>
       <c r="AP42" s="4"/>
       <c r="AQ42" s="4"/>
       <c r="AR42" s="3"/>
@@ -10539,23 +10789,25 @@
       <c r="AT42" s="4"/>
       <c r="AU42" s="3"/>
       <c r="AV42" s="4"/>
-      <c r="AW42" s="5"/>
-      <c r="AX42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="3"/>
       <c r="AY42" s="4"/>
-      <c r="AZ42" s="4"/>
-      <c r="BA42" s="3"/>
+      <c r="AZ42" s="5"/>
+      <c r="BA42" s="4"/>
       <c r="BB42" s="4"/>
-      <c r="BC42" s="5"/>
-      <c r="BD42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="3"/>
       <c r="BE42" s="4"/>
-      <c r="BF42" s="4"/>
+      <c r="BF42" s="5"/>
       <c r="BG42" s="4"/>
       <c r="BH42" s="4"/>
       <c r="BI42" s="4"/>
       <c r="BJ42" s="4"/>
-      <c r="BK42" s="5"/>
-    </row>
-    <row r="43" spans="1:63" ht="14" customHeight="1">
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="5"/>
+    </row>
+    <row r="43" spans="1:65" ht="14" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3"/>
@@ -10593,10 +10845,10 @@
       <c r="AI43" s="3"/>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="5"/>
-      <c r="AL43" s="4"/>
+      <c r="AL43" s="3"/>
       <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
-      <c r="AO43" s="3"/>
+      <c r="AN43" s="5"/>
+      <c r="AO43" s="4"/>
       <c r="AP43" s="4"/>
       <c r="AQ43" s="4"/>
       <c r="AR43" s="3"/>
@@ -10604,23 +10856,25 @@
       <c r="AT43" s="4"/>
       <c r="AU43" s="3"/>
       <c r="AV43" s="4"/>
-      <c r="AW43" s="5"/>
-      <c r="AX43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="3"/>
       <c r="AY43" s="4"/>
-      <c r="AZ43" s="4"/>
-      <c r="BA43" s="3"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="4"/>
       <c r="BB43" s="4"/>
-      <c r="BC43" s="5"/>
-      <c r="BD43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="3"/>
       <c r="BE43" s="4"/>
-      <c r="BF43" s="4"/>
+      <c r="BF43" s="5"/>
       <c r="BG43" s="4"/>
       <c r="BH43" s="4"/>
       <c r="BI43" s="4"/>
       <c r="BJ43" s="4"/>
-      <c r="BK43" s="5"/>
-    </row>
-    <row r="44" spans="1:63" ht="14" customHeight="1">
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="5"/>
+    </row>
+    <row r="44" spans="1:65" ht="14" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
@@ -10658,10 +10912,10 @@
       <c r="AI44" s="3"/>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="5"/>
-      <c r="AL44" s="4"/>
+      <c r="AL44" s="3"/>
       <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="3"/>
+      <c r="AN44" s="5"/>
+      <c r="AO44" s="4"/>
       <c r="AP44" s="4"/>
       <c r="AQ44" s="4"/>
       <c r="AR44" s="3"/>
@@ -10669,23 +10923,25 @@
       <c r="AT44" s="4"/>
       <c r="AU44" s="3"/>
       <c r="AV44" s="4"/>
-      <c r="AW44" s="5"/>
-      <c r="AX44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="3"/>
       <c r="AY44" s="4"/>
-      <c r="AZ44" s="4"/>
-      <c r="BA44" s="3"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="4"/>
       <c r="BB44" s="4"/>
-      <c r="BC44" s="5"/>
-      <c r="BD44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="3"/>
       <c r="BE44" s="4"/>
-      <c r="BF44" s="4"/>
+      <c r="BF44" s="5"/>
       <c r="BG44" s="4"/>
       <c r="BH44" s="4"/>
       <c r="BI44" s="4"/>
       <c r="BJ44" s="4"/>
-      <c r="BK44" s="5"/>
-    </row>
-    <row r="45" spans="1:63" ht="14" customHeight="1">
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="5"/>
+    </row>
+    <row r="45" spans="1:65" ht="14" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="3"/>
@@ -10723,10 +10979,10 @@
       <c r="AI45" s="3"/>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="5"/>
-      <c r="AL45" s="4"/>
+      <c r="AL45" s="3"/>
       <c r="AM45" s="4"/>
-      <c r="AN45" s="4"/>
-      <c r="AO45" s="3"/>
+      <c r="AN45" s="5"/>
+      <c r="AO45" s="4"/>
       <c r="AP45" s="4"/>
       <c r="AQ45" s="4"/>
       <c r="AR45" s="3"/>
@@ -10734,27 +10990,29 @@
       <c r="AT45" s="4"/>
       <c r="AU45" s="3"/>
       <c r="AV45" s="4"/>
-      <c r="AW45" s="5"/>
-      <c r="AX45" s="4"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="3"/>
       <c r="AY45" s="4"/>
-      <c r="AZ45" s="4"/>
-      <c r="BA45" s="3"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="4"/>
       <c r="BB45" s="4"/>
-      <c r="BC45" s="5"/>
-      <c r="BD45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="3"/>
       <c r="BE45" s="4"/>
-      <c r="BF45" s="4"/>
+      <c r="BF45" s="5"/>
       <c r="BG45" s="4"/>
       <c r="BH45" s="4"/>
       <c r="BI45" s="4"/>
       <c r="BJ45" s="4"/>
-      <c r="BK45" s="5"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+      <c r="BM45" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>

--- a/build/Sample.xlsx
+++ b/build/Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/Documents/Repos/golang/generateTables/build/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8797DC-EDDC-DC45-BB60-0013B5012075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F3C44F-03E8-D74D-A64A-01D2BD937851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="600" windowWidth="27600" windowHeight="22820" activeTab="2" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
+    <workbookView xWindow="80" yWindow="600" windowWidth="27600" windowHeight="22820" activeTab="2" xr2:uid="{5AFB18EF-3D68-834C-8DD2-1F3014CEF5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="#SAMPLE" sheetId="19" r:id="rId1"/>
@@ -11017,5 +11017,23 @@
     <oddHeader>&amp;L&amp;"ＭＳ Ｐゴシック,標準"&amp;10Confidential information 機密情報&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;K000000&amp;D　&amp;T</oddHeader>
     <oddFooter>&amp;C&amp;"ＭＳ Ｐゴシック,標準"&amp;10&amp;P&amp;R&amp;"ＭＳ Ｐゴシック,標準"&amp;10Genecom, Inc.</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BDD81053-EA0C-BB42-9608-11CF2F5FBBDA}">
+          <x14:formula1>
+            <xm:f>'#SAMPLE'!$K$10:$K$50</xm:f>
+          </x14:formula1>
+          <xm:sqref>K10:K50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33E3CD64-F9EF-C844-90F4-9F773FFF1DC7}">
+          <x14:formula1>
+            <xm:f>'#SAMPLE'!$H$10:$H$50</xm:f>
+          </x14:formula1>
+          <xm:sqref>H10:H50</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>